--- a/WC - Rona.xlsx
+++ b/WC - Rona.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aa146fe2527b5e46/Desktop/Personal/World Cup 26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7209" documentId="8_{039B2390-A828-4A39-BFA9-7EF21B63ED3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12AF8DEE-638B-4753-AAF0-4A30E2CA70D1}"/>
+  <xr:revisionPtr revIDLastSave="7223" documentId="8_{039B2390-A828-4A39-BFA9-7EF21B63ED3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93F014CA-061E-4759-8545-1606CBDF4FD2}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2505" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{AEB89C08-5595-43EA-9CD5-774FAA1DB4BC}"/>
+    <workbookView xWindow="-28920" yWindow="2505" windowWidth="29040" windowHeight="15720" xr2:uid="{AEB89C08-5595-43EA-9CD5-774FAA1DB4BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Score" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="121">
   <si>
     <t>Date</t>
   </si>
@@ -423,6 +423,12 @@
   </si>
   <si>
     <t>rayanzaibag18@gmail.com</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>=</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1056,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1434,6 +1440,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2011,7 +2020,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2022,7 +2031,95 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF0070C0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2044,95 +2141,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF000000"/>
+          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2880,6 +2889,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3030,11 +3049,45 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FFFFFFFF"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3051,12 +3104,56 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF0070C0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3078,95 +3175,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF000000"/>
+          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3687,10 +3696,10 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="162" t="s">
+      <c r="E1" s="165" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="162"/>
+      <c r="F1" s="165"/>
       <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
@@ -3908,15 +3917,19 @@
       <c r="D4" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="54"/>
-      <c r="F4" s="55"/>
+      <c r="E4" s="54">
+        <v>1</v>
+      </c>
+      <c r="F4" s="55">
+        <v>1</v>
+      </c>
       <c r="G4" s="61" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="H4" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>67</v>
@@ -5680,7 +5693,7 @@
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H74">
         <f>SUM(H2:H73)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5775,7 +5788,7 @@
       </c>
       <c r="D82" cm="1">
         <f t="array" ref="D82">SUMPRODUCT((($C$2:$C$73=C82)*($G$2:$G$73=1))*3) + SUMPRODUCT((($D$2:$D$73=C82)*($G$2:$G$73=2))*3) + SUMPRODUCT((($C$2:$C$73=C82)+($D$2:$D$73=C82))*($G$2:$G$73="X"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" cm="1">
         <f t="array" ref="E82">SUMPRODUCT(($C$2:$C$73=C82)*$E$2:$E$73)+SUMPRODUCT(($D$2:$D$73=C82)*$F$2:$F$73)-SUMPRODUCT(($C$2:$C$73=C82)*$F$2:$F$73)-SUMPRODUCT(($D$2:$D$73=C82)*$E$2:$E$73)</f>
@@ -5792,7 +5805,7 @@
       </c>
       <c r="D83" cm="1">
         <f t="array" ref="D83">SUMPRODUCT((($C$2:$C$73=C83)*($G$2:$G$73=1))*3) + SUMPRODUCT((($D$2:$D$73=C83)*($G$2:$G$73=2))*3) + SUMPRODUCT((($C$2:$C$73=C83)+($D$2:$D$73=C83))*($G$2:$G$73="X"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" cm="1">
         <f t="array" ref="E83">SUMPRODUCT(($C$2:$C$73=C83)*$E$2:$E$73)+SUMPRODUCT(($D$2:$D$73=C83)*$F$2:$F$73)-SUMPRODUCT(($C$2:$C$73=C83)*$F$2:$F$73)-SUMPRODUCT(($D$2:$D$73=C83)*$E$2:$E$73)</f>
@@ -6670,7 +6683,7 @@
       </c>
       <c r="H3" s="122">
         <f>SUM(I4:I75)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="123">
         <f>SUM(I78:I125)</f>
@@ -6686,7 +6699,7 @@
       </c>
       <c r="L3" s="122">
         <f>SUM(M4:M75)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="123">
         <f>SUM(M78:M125)</f>
@@ -6822,42 +6835,42 @@
       </c>
       <c r="E6" s="67" t="str">
         <f>'Master Score'!G4</f>
-        <v/>
+        <v>X</v>
       </c>
       <c r="F6" s="126">
         <v>1</v>
       </c>
-      <c r="G6" s="125" t="str">
+      <c r="G6" s="125">
         <f t="shared" si="0"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="H6" s="126" t="s">
         <v>94</v>
       </c>
-      <c r="I6" s="125" t="str">
+      <c r="I6" s="125">
         <f t="shared" ref="I6" si="5">IF($E6="","",IF(H6=$E6,1,0))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J6" s="126">
         <v>2</v>
       </c>
-      <c r="K6" s="125" t="str">
+      <c r="K6" s="125">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="L6" s="126" t="s">
         <v>94</v>
       </c>
-      <c r="M6" s="125" t="str">
+      <c r="M6" s="125">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N6" s="117">
         <v>1</v>
       </c>
-      <c r="O6" t="str">
+      <c r="O6">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -13019,41 +13032,41 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="C78:C125">
-    <cfRule type="cellIs" dxfId="168" priority="229" operator="equal">
-      <formula>"A"</formula>
+    <cfRule type="cellIs" dxfId="168" priority="239" operator="equal">
+      <formula>"K"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="167" priority="230" operator="equal">
-      <formula>"B"</formula>
+    <cfRule type="cellIs" dxfId="167" priority="238" operator="equal">
+      <formula>"J"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="231" operator="equal">
-      <formula>"C"</formula>
+    <cfRule type="cellIs" dxfId="166" priority="237" operator="equal">
+      <formula>"I"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="165" priority="232" operator="equal">
-      <formula>"D"</formula>
+    <cfRule type="cellIs" dxfId="165" priority="236" operator="equal">
+      <formula>"H"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="164" priority="233" operator="equal">
-      <formula>"E"</formula>
+    <cfRule type="cellIs" dxfId="164" priority="235" operator="equal">
+      <formula>"G"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="163" priority="234" operator="equal">
       <formula>"F"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="235" operator="equal">
-      <formula>"G"</formula>
+    <cfRule type="cellIs" dxfId="162" priority="233" operator="equal">
+      <formula>"E"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="161" priority="236" operator="equal">
-      <formula>"H"</formula>
+    <cfRule type="cellIs" dxfId="161" priority="240" operator="equal">
+      <formula>"L"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="237" operator="equal">
-      <formula>"I"</formula>
+    <cfRule type="cellIs" dxfId="160" priority="232" operator="equal">
+      <formula>"D"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="238" operator="equal">
-      <formula>"J"</formula>
+    <cfRule type="cellIs" dxfId="159" priority="231" operator="equal">
+      <formula>"C"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="239" operator="equal">
-      <formula>"K"</formula>
+    <cfRule type="cellIs" dxfId="158" priority="229" operator="equal">
+      <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="240" operator="equal">
-      <formula>"L"</formula>
+    <cfRule type="cellIs" dxfId="157" priority="230" operator="equal">
+      <formula>"B"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F78:F85">
@@ -13063,11 +13076,11 @@
     <cfRule type="duplicateValues" dxfId="155" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G78:G125">
-    <cfRule type="cellIs" dxfId="154" priority="163" operator="equal">
+    <cfRule type="cellIs" dxfId="154" priority="164" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="153" priority="163" operator="equal">
       <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="164" operator="equal">
-      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H78:H85">
@@ -13077,23 +13090,23 @@
     <cfRule type="duplicateValues" dxfId="151" priority="179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I78:I125">
-    <cfRule type="cellIs" dxfId="150" priority="161" operator="equal">
+    <cfRule type="cellIs" dxfId="150" priority="162" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="149" priority="161" operator="equal">
       <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="149" priority="162" operator="equal">
-      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J78:J125">
-    <cfRule type="duplicateValues" dxfId="148" priority="223"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="223"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K78:K125">
-    <cfRule type="cellIs" dxfId="146" priority="159" operator="equal">
+    <cfRule type="cellIs" dxfId="146" priority="160" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="145" priority="159" operator="equal">
       <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="160" operator="equal">
-      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L78:L125">
@@ -13101,28 +13114,28 @@
     <cfRule type="duplicateValues" dxfId="143" priority="222"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M78:M125">
-    <cfRule type="cellIs" dxfId="142" priority="157" operator="equal">
+    <cfRule type="cellIs" dxfId="142" priority="158" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="141" priority="157" operator="equal">
       <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="158" operator="equal">
-      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N78">
-    <cfRule type="duplicateValues" dxfId="140" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N79">
     <cfRule type="duplicateValues" dxfId="138" priority="55"/>
     <cfRule type="duplicateValues" dxfId="137" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N80">
-    <cfRule type="duplicateValues" dxfId="136" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N81">
-    <cfRule type="duplicateValues" dxfId="134" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N82">
     <cfRule type="duplicateValues" dxfId="132" priority="49"/>
@@ -13137,8 +13150,8 @@
     <cfRule type="duplicateValues" dxfId="127" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N85">
-    <cfRule type="duplicateValues" dxfId="126" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N86">
     <cfRule type="duplicateValues" dxfId="124" priority="41"/>
@@ -13424,7 +13437,7 @@
       </c>
       <c r="K2" s="56">
         <f>Stats!D2</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>70</v>
@@ -13439,15 +13452,15 @@
       </c>
       <c r="P2">
         <f>Stats!B2</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q2">
         <f>72-P2</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R2">
         <f>'Master Score'!H74</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -13467,7 +13480,7 @@
       </c>
       <c r="F3">
         <f>Predictions!H3</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <f>Predictions!I3</f>
@@ -13475,7 +13488,7 @@
       </c>
       <c r="H3">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" s="59">
         <v>180</v>
@@ -13485,14 +13498,14 @@
       </c>
       <c r="K3" s="56">
         <f>Stats!D3</f>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>71</v>
       </c>
       <c r="M3" s="161" t="str" cm="1">
         <f t="array" ref="M3">IFERROR(INDEX(_xlfn.SORTBY($C$2:$C$6,$F$2:$F$6,-1),2),"")</f>
-        <v>Arion Aliu</v>
+        <v>Aaron Twiss</v>
       </c>
       <c r="N3" s="1">
         <f>IFERROR(_xlfn.XLOOKUP(M3,$C$2:$C$6,$F$2:$F$6),"")</f>
@@ -13534,14 +13547,14 @@
       </c>
       <c r="K4" s="56">
         <f>Stats!D4</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>67</v>
       </c>
       <c r="M4" s="161" t="str" cm="1">
         <f t="array" ref="M4">IFERROR(INDEX(_xlfn.SORTBY($C$2:$C$6,$F$2:$F$6,-1),3),"")</f>
-        <v>Jorge Lopez</v>
+        <v>Arion Aliu</v>
       </c>
       <c r="N4" s="1">
         <f>IFERROR(_xlfn.XLOOKUP(M4,$C$2:$C$6,$F$2:$F$6),"")</f>
@@ -13565,7 +13578,7 @@
       </c>
       <c r="F5">
         <f>Predictions!L3</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <f>Predictions!M3</f>
@@ -13573,7 +13586,7 @@
       </c>
       <c r="H5">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" s="59">
         <v>180</v>
@@ -13583,18 +13596,18 @@
       </c>
       <c r="K5" s="56">
         <f>Stats!D5</f>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>68</v>
       </c>
       <c r="M5" s="161" t="str" cm="1">
         <f t="array" ref="M5">IFERROR(INDEX(_xlfn.SORTBY($C$2:$C$6,$F$2:$F$6,-1),4),"")</f>
-        <v>Aaron Twiss</v>
+        <v>Rayan Zaibag</v>
       </c>
       <c r="N5" s="1">
         <f>IFERROR(_xlfn.XLOOKUP(M5,$C$2:$C$6,$F$2:$F$6),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -13632,18 +13645,18 @@
       </c>
       <c r="K6" s="56">
         <f>Stats!D6</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>69</v>
       </c>
       <c r="M6" s="161" t="str" cm="1">
         <f t="array" ref="M6">IFERROR(INDEX(_xlfn.SORTBY($C$2:$C$6,$F$2:$F$6,-1),5),"")</f>
-        <v>Rayan Zaibag</v>
+        <v>Jorge Lopez</v>
       </c>
       <c r="N6" s="1">
         <f>IFERROR(_xlfn.XLOOKUP(M6,$C$2:$C$6,$F$2:$F$6),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -13767,7 +13780,7 @@
       </c>
       <c r="B2">
         <f>COUNT('Master Score'!$G$2:$G$73)+COUNTIF('Master Score'!$G$2:$G$73,"X")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <f>Leaderboard!F2</f>
@@ -13775,11 +13788,11 @@
       </c>
       <c r="D2" s="21">
         <f>IF(B2&gt;0,C2/B2,0)</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E2" s="22">
         <f>IF(B2&gt;0,C2/B2,0)</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F2" s="22" cm="1">
         <f t="array" ref="F2">IF(A2="","",IFERROR(_xlfn.STDEV.P(IF(Predictions!F$4:F$75&lt;&gt;"",IF(Predictions!F$4:F$75='Master Score'!$G$2:$G$73,1,0))),0))</f>
@@ -13791,19 +13804,19 @@
       </c>
       <c r="H2" s="22" cm="1">
         <f t="array" ref="H2">IF(A2="","",IFERROR((D2/(1+G2))/SUMPRODUCT(($A$2:$A$20&lt;&gt;"")*($D$2:$D$20/(1+$G$2:$G$20))),0))</f>
-        <v>0.24918203802930441</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="I2" s="22" cm="1">
         <f t="array" ref="I2">IF(A2="","",IFERROR((D2-AVERAGEIF($A$2:$A$20,"&lt;&gt;",$D$2:$D$20))/_xlfn.STDEV.P(IF($A$2:$A$20&lt;&gt;"",$D$2:$D$20)),0))</f>
-        <v>0.81649658092772592</v>
+        <v>0</v>
       </c>
       <c r="J2" s="22">
         <f>IF(A2="","",ROUND((L2*25)+((1-D2)*30)+(G2*25)+((1-MIN(1,MAX(0,(I2+2)/4)))*20),1))</f>
-        <v>20.100000000000001</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="K2" s="22">
         <f>IF(A2="","",IFERROR(D2*100*(1-F2),0))</f>
-        <v>83.566445046945518</v>
+        <v>55.710963364630338</v>
       </c>
       <c r="L2" s="22" cm="1">
         <f t="array" ref="L2">IF(A2="","",IFERROR(SUMPRODUCT((U$2:U$73&lt;&gt;"")*1*(U$2:U$73&lt;&gt;_xlfn.MODE.SNGL(U$2:Y$73)))/COUNTA(U$2:U$73),0))</f>
@@ -13949,43 +13962,43 @@
       </c>
       <c r="B3">
         <f>COUNT('Master Score'!$G$2:$G$73)+COUNTIF('Master Score'!$G$2:$G$73,"X")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <f>Leaderboard!F3</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="21">
         <f>IFERROR(C3/B3,0)</f>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E3" s="22">
         <f>IFERROR(C3/B3,0)</f>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F3" s="22" cm="1">
         <f t="array" ref="F3">IF(A3="","",IFERROR(_xlfn.STDEV.P(IF(Predictions!H$4:H$75&lt;&gt;"",IF(Predictions!H$4:H$75='Master Score'!$G$2:$G$73,1,0))),0))</f>
-        <v>0.11702985796078276</v>
+        <v>0.16433554953054488</v>
       </c>
       <c r="G3" s="22">
         <f t="shared" si="0"/>
-        <v>1.3695987654320988E-2</v>
+        <v>2.7006172839506171E-2</v>
       </c>
       <c r="H3" s="22" cm="1">
         <f t="array" ref="H3">IF(A3="","",IFERROR((D3/(1+G3))/SUMPRODUCT(($A$2:$A$20&lt;&gt;"")*($D$2:$D$20/(1+$G$2:$G$20))),0))</f>
-        <v>0.12622694295604342</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="I3" s="22" cm="1">
         <f t="array" ref="I3">IF(A3="","",IFERROR((D3-AVERAGEIF($A$2:$A$20,"&lt;&gt;",$D$2:$D$20))/_xlfn.STDEV.P(IF($A$2:$A$20&lt;&gt;"",$D$2:$D$20)),0))</f>
-        <v>-1.2247448713915894</v>
+        <v>0</v>
       </c>
       <c r="J3" s="22">
         <f t="shared" ref="J3:J6" si="4">IF(A3="","",ROUND((L3*25)+((1-D3)*30)+(G3*25)+((1-MIN(1,MAX(0,(I3+2)/4)))*20),1))</f>
-        <v>44.7</v>
+        <v>33.9</v>
       </c>
       <c r="K3" s="22">
         <f t="shared" ref="K3:K6" si="5">IF(A3="","",IFERROR(D3*100*(1-F3),0))</f>
-        <v>44.14850710196086</v>
+        <v>55.710963364630338</v>
       </c>
       <c r="L3" s="22" cm="1">
         <f t="array" ref="L3">IF(A3="","",IFERROR(SUMPRODUCT((V$2:V$73&lt;&gt;"")*1*(V$2:V$73&lt;&gt;_xlfn.MODE.SNGL(U$2:Y$73)))/COUNTA(V$2:V$73),0))</f>
@@ -14096,7 +14109,7 @@
       </c>
       <c r="B4">
         <f>COUNT('Master Score'!$G$2:$G$73)+COUNTIF('Master Score'!$G$2:$G$73,"X")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <f>Leaderboard!F4</f>
@@ -14104,11 +14117,11 @@
       </c>
       <c r="D4" s="21">
         <f>IFERROR(C4/B4,0)</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E4" s="22">
         <f>IFERROR(C4/B4,0)</f>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F4" s="22" cm="1">
         <f t="array" ref="F4">IF(A4="","",IFERROR(_xlfn.STDEV.P(IF(Predictions!J$4:J$75&lt;&gt;"",IF(Predictions!J$4:J$75='Master Score'!$G$2:$G$73,1,0))),0))</f>
@@ -14120,19 +14133,19 @@
       </c>
       <c r="H4" s="22" cm="1">
         <f t="array" ref="H4">IF(A4="","",IFERROR((D4/(1+G4))/SUMPRODUCT(($A$2:$A$20&lt;&gt;"")*($D$2:$D$20/(1+$G$2:$G$20))),0))</f>
-        <v>0.24918203802930441</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="I4" s="22" cm="1">
         <f t="array" ref="I4">IF(A4="","",IFERROR((D4-AVERAGEIF($A$2:$A$20,"&lt;&gt;",$D$2:$D$20))/_xlfn.STDEV.P(IF($A$2:$A$20&lt;&gt;"",$D$2:$D$20)),0))</f>
-        <v>0.81649658092772592</v>
+        <v>0</v>
       </c>
       <c r="J4" s="22">
         <f t="shared" si="4"/>
-        <v>18.7</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="K4" s="22">
         <f t="shared" si="5"/>
-        <v>83.566445046945518</v>
+        <v>55.710963364630338</v>
       </c>
       <c r="L4" s="22" cm="1">
         <f t="array" ref="L4">IF(A4="","",IFERROR(SUMPRODUCT((W$2:W$73&lt;&gt;"")*1*(W$2:W$73&lt;&gt;_xlfn.MODE.SNGL(U$2:Y$73)))/COUNTA(W$2:W$73),0))</f>
@@ -14243,43 +14256,43 @@
       </c>
       <c r="B5">
         <f>COUNT('Master Score'!$G$2:$G$73)+COUNTIF('Master Score'!$G$2:$G$73,"X")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <f>Leaderboard!F5</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="21">
         <f t="shared" ref="D5:D6" si="6">IFERROR(C5/B5,0)</f>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E5" s="22">
         <f t="shared" ref="E5:E6" si="7">IFERROR(C5/B5,0)</f>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F5" s="22" cm="1">
         <f t="array" ref="F5">IF(A5="","",IFERROR(_xlfn.STDEV.P(IF(Predictions!L$4:L$75&lt;&gt;"",IF(Predictions!L$4:L$75='Master Score'!$G$2:$G$73,1,0))),0))</f>
-        <v>0.11702985796078276</v>
+        <v>0.16433554953054488</v>
       </c>
       <c r="G5" s="22">
         <f t="shared" si="0"/>
-        <v>1.3695987654320988E-2</v>
+        <v>2.7006172839506171E-2</v>
       </c>
       <c r="H5" s="22" cm="1">
         <f t="array" ref="H5">IF(A5="","",IFERROR((D5/(1+G5))/SUMPRODUCT(($A$2:$A$20&lt;&gt;"")*($D$2:$D$20/(1+$G$2:$G$20))),0))</f>
-        <v>0.12622694295604342</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="I5" s="22" cm="1">
         <f t="array" ref="I5">IF(A5="","",IFERROR((D5-AVERAGEIF($A$2:$A$20,"&lt;&gt;",$D$2:$D$20))/_xlfn.STDEV.P(IF($A$2:$A$20&lt;&gt;"",$D$2:$D$20)),0))</f>
-        <v>-1.2247448713915894</v>
+        <v>0</v>
       </c>
       <c r="J5" s="22">
         <f t="shared" si="4"/>
-        <v>43.3</v>
+        <v>32.5</v>
       </c>
       <c r="K5" s="22">
         <f t="shared" si="5"/>
-        <v>44.14850710196086</v>
+        <v>55.710963364630338</v>
       </c>
       <c r="L5" s="22" cm="1">
         <f t="array" ref="L5">IF(A5="","",IFERROR(SUMPRODUCT((X$2:X$73&lt;&gt;"")*1*(X$2:X$73&lt;&gt;_xlfn.MODE.SNGL(U$2:Y$73)))/COUNTA(X$2:X$73),0))</f>
@@ -14390,7 +14403,7 @@
       </c>
       <c r="B6">
         <f>COUNT('Master Score'!$G$2:$G$73)+COUNTIF('Master Score'!$G$2:$G$73,"X")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <f>Leaderboard!F6</f>
@@ -14398,11 +14411,11 @@
       </c>
       <c r="D6" s="21">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E6" s="22">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F6" s="22" cm="1">
         <f t="array" ref="F6">IF(A6="","",IFERROR(_xlfn.STDEV.P(IF(Predictions!N$4:N$75&lt;&gt;"",IF(Predictions!N$4:N$75='Master Score'!$G$2:$G$73,1,0))),0))</f>
@@ -14414,19 +14427,19 @@
       </c>
       <c r="H6" s="22" cm="1">
         <f t="array" ref="H6">IF(A6="","",IFERROR((D6/(1+G6))/SUMPRODUCT(($A$2:$A$20&lt;&gt;"")*($D$2:$D$20/(1+$G$2:$G$20))),0))</f>
-        <v>0.24918203802930441</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="I6" s="22" cm="1">
         <f t="array" ref="I6">IF(A6="","",IFERROR((D6-AVERAGEIF($A$2:$A$20,"&lt;&gt;",$D$2:$D$20))/_xlfn.STDEV.P(IF($A$2:$A$20&lt;&gt;"",$D$2:$D$20)),0))</f>
-        <v>0.81649658092772592</v>
+        <v>0</v>
       </c>
       <c r="J6" s="22">
         <f t="shared" si="4"/>
-        <v>17.7</v>
+        <v>31.8</v>
       </c>
       <c r="K6" s="22">
         <f t="shared" si="5"/>
-        <v>83.566445046945518</v>
+        <v>55.710963364630338</v>
       </c>
       <c r="L6" s="22" cm="1">
         <f t="array" ref="L6">IF(A6="","",IFERROR(SUMPRODUCT((Y$2:Y$73&lt;&gt;"")*1*(Y$2:Y$73&lt;&gt;_xlfn.MODE.SNGL(U$2:Y$73)))/COUNTA(Y$2:Y$73),0))</f>
@@ -23241,2495 +23254,2791 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E1021FC-FA78-4BCF-AE17-3AEE79D229AF}">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="114" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="114" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="114" t="s">
-        <v>2</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="C1" s="114"/>
       <c r="D1" s="114" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="114" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="114" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="str">
+      <c r="G1" s="16" t="str">
         <f>Predictions!F1</f>
         <v>Matthew O'Brien</v>
       </c>
-      <c r="F1" s="16" t="str">
+      <c r="H1" s="16" t="str">
         <f>Predictions!H1</f>
         <v>Aaron Twiss</v>
       </c>
-      <c r="G1" s="16" t="str">
+      <c r="I1" s="16" t="str">
         <f>Predictions!J1</f>
         <v>Arion Aliu</v>
       </c>
-      <c r="H1" s="16" t="str">
+      <c r="J1" s="16" t="str">
         <f>Predictions!L1</f>
         <v>Rayan Zaibag</v>
       </c>
-      <c r="I1" s="16" t="str">
+      <c r="K1" s="16" t="str">
         <f>Predictions!N1</f>
         <v>Jorge Lopez</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="29">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="164">
         <v>46184</v>
       </c>
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="162">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C2" s="162" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="E2" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="F2" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="str" cm="1">
-        <f t="array" ref="E2">_xlfn.IFS(Predictions!F4=1,$C2,Predictions!F4="X","Draw",Predictions!F4=2,$D2)</f>
+      <c r="G2" s="1" t="str" cm="1">
+        <f t="array" ref="G2">_xlfn.IFS(Predictions!F4=1,$E2,Predictions!F4="X","Draw",Predictions!F4=2,$F2)</f>
         <v>Mexico</v>
       </c>
-      <c r="F2" s="1" t="str" cm="1">
-        <f t="array" ref="F2">_xlfn.IFS(Predictions!H4=1,$C2,Predictions!H4="X","Draw",Predictions!H4=2,$D2)</f>
+      <c r="H2" s="1" t="str" cm="1">
+        <f t="array" ref="H2">_xlfn.IFS(Predictions!H4=1,$E2,Predictions!H4="X","Draw",Predictions!H4=2,$F2)</f>
         <v>Mexico</v>
       </c>
-      <c r="G2" s="1" t="str" cm="1">
-        <f t="array" ref="G2">_xlfn.IFS(Predictions!J4=1,$C2,Predictions!J4="X","Draw",Predictions!J4=2,$D2)</f>
+      <c r="I2" s="1" t="str" cm="1">
+        <f t="array" ref="I2">_xlfn.IFS(Predictions!J4=1,$E2,Predictions!J4="X","Draw",Predictions!J4=2,$F2)</f>
         <v>Mexico</v>
       </c>
-      <c r="H2" s="1" t="str" cm="1">
-        <f t="array" ref="H2">_xlfn.IFS(Predictions!L4=1,$C2,Predictions!L4="X","Draw",Predictions!L4=2,$D2)</f>
+      <c r="J2" s="1" t="str" cm="1">
+        <f t="array" ref="J2">_xlfn.IFS(Predictions!L4=1,$E2,Predictions!L4="X","Draw",Predictions!L4=2,$F2)</f>
         <v>Mexico</v>
       </c>
-      <c r="I2" s="1" t="str" cm="1">
-        <f t="array" ref="I2">_xlfn.IFS(Predictions!N4=1,$C2,Predictions!N4="X","Draw",Predictions!N4=2,$D2)</f>
+      <c r="K2" s="1" t="str" cm="1">
+        <f t="array" ref="K2">_xlfn.IFS(Predictions!N4=1,$E2,Predictions!N4="X","Draw",Predictions!N4=2,$F2)</f>
         <v>Mexico</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="26">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="164">
         <v>46185</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="163">
+        <v>0.125</v>
+      </c>
+      <c r="C3" s="163"/>
+      <c r="D3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="E3" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="F3" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="str" cm="1">
-        <f t="array" ref="E3">_xlfn.IFS(Predictions!F5=1,$C3,Predictions!F5="X","Draw",Predictions!F5=2,$D3)</f>
+      <c r="G3" s="1" t="str" cm="1">
+        <f t="array" ref="G3">_xlfn.IFS(Predictions!F5=1,$E3,Predictions!F5="X","Draw",Predictions!F5=2,$F3)</f>
         <v>South Korea</v>
       </c>
-      <c r="F3" s="1" t="str" cm="1">
-        <f t="array" ref="F3">_xlfn.IFS(Predictions!H5=1,$C3,Predictions!H5="X","Draw",Predictions!H5=2,$D3)</f>
+      <c r="H3" s="1" t="str" cm="1">
+        <f t="array" ref="H3">_xlfn.IFS(Predictions!H5=1,$E3,Predictions!H5="X","Draw",Predictions!H5=2,$F3)</f>
         <v>Draw</v>
       </c>
-      <c r="G3" s="1" t="str" cm="1">
-        <f t="array" ref="G3">_xlfn.IFS(Predictions!J5=1,$C3,Predictions!J5="X","Draw",Predictions!J5=2,$D3)</f>
+      <c r="I3" s="1" t="str" cm="1">
+        <f t="array" ref="I3">_xlfn.IFS(Predictions!J5=1,$E3,Predictions!J5="X","Draw",Predictions!J5=2,$F3)</f>
         <v>South Korea</v>
       </c>
-      <c r="H3" s="1" t="str" cm="1">
-        <f t="array" ref="H3">_xlfn.IFS(Predictions!L5=1,$C3,Predictions!L5="X","Draw",Predictions!L5=2,$D3)</f>
+      <c r="J3" s="1" t="str" cm="1">
+        <f t="array" ref="J3">_xlfn.IFS(Predictions!L5=1,$E3,Predictions!L5="X","Draw",Predictions!L5=2,$F3)</f>
         <v>Draw</v>
       </c>
-      <c r="I3" s="1" t="str" cm="1">
-        <f t="array" ref="I3">_xlfn.IFS(Predictions!N5=1,$C3,Predictions!N5="X","Draw",Predictions!N5=2,$D3)</f>
+      <c r="K3" s="1" t="str" cm="1">
+        <f t="array" ref="K3">_xlfn.IFS(Predictions!N5=1,$E3,Predictions!N5="X","Draw",Predictions!N5=2,$F3)</f>
         <v>South Korea</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="29">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="164">
         <v>46185</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="162">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C4" s="162"/>
+      <c r="D4" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="E4" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="F4" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="1" t="str" cm="1">
-        <f t="array" ref="E4">_xlfn.IFS(Predictions!F6=1,$C4,Predictions!F6="X","Draw",Predictions!F6=2,$D4)</f>
+      <c r="G4" s="1" t="str" cm="1">
+        <f t="array" ref="G4">_xlfn.IFS(Predictions!F6=1,$E4,Predictions!F6="X","Draw",Predictions!F6=2,$F4)</f>
         <v>Canada</v>
       </c>
-      <c r="F4" s="1" t="str" cm="1">
-        <f t="array" ref="F4">_xlfn.IFS(Predictions!H6=1,$C4,Predictions!H6="X","Draw",Predictions!H6=2,$D4)</f>
+      <c r="H4" s="1" t="str" cm="1">
+        <f t="array" ref="H4">_xlfn.IFS(Predictions!H6=1,$E4,Predictions!H6="X","Draw",Predictions!H6=2,$F4)</f>
         <v>Draw</v>
       </c>
-      <c r="G4" s="1" t="str" cm="1">
-        <f t="array" ref="G4">_xlfn.IFS(Predictions!J6=1,$C4,Predictions!J6="X","Draw",Predictions!J6=2,$D4)</f>
+      <c r="I4" s="1" t="str" cm="1">
+        <f t="array" ref="I4">_xlfn.IFS(Predictions!J6=1,$E4,Predictions!J6="X","Draw",Predictions!J6=2,$F4)</f>
         <v>Bosnia and Herzegovina</v>
       </c>
-      <c r="H4" s="1" t="str" cm="1">
-        <f t="array" ref="H4">_xlfn.IFS(Predictions!L6=1,$C4,Predictions!L6="X","Draw",Predictions!L6=2,$D4)</f>
+      <c r="J4" s="1" t="str" cm="1">
+        <f t="array" ref="J4">_xlfn.IFS(Predictions!L6=1,$E4,Predictions!L6="X","Draw",Predictions!L6=2,$F4)</f>
         <v>Draw</v>
       </c>
-      <c r="I4" s="1" t="str" cm="1">
-        <f t="array" ref="I4">_xlfn.IFS(Predictions!N6=1,$C4,Predictions!N6="X","Draw",Predictions!N6=2,$D4)</f>
+      <c r="K4" s="1" t="str" cm="1">
+        <f t="array" ref="K4">_xlfn.IFS(Predictions!N6=1,$E4,Predictions!N6="X","Draw",Predictions!N6=2,$F4)</f>
         <v>Canada</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="164">
         <v>46186</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="163">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="C5" s="163"/>
+      <c r="D5" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="E5" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="F5" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1" t="str" cm="1">
-        <f t="array" ref="E5">_xlfn.IFS(Predictions!F7=1,$C5,Predictions!F7="X","Draw",Predictions!F7=2,$D5)</f>
+      <c r="G5" s="1" t="str" cm="1">
+        <f t="array" ref="G5">_xlfn.IFS(Predictions!F7=1,$E5,Predictions!F7="X","Draw",Predictions!F7=2,$F5)</f>
         <v>USA</v>
       </c>
-      <c r="F5" s="1" t="str" cm="1">
-        <f t="array" ref="F5">_xlfn.IFS(Predictions!H7=1,$C5,Predictions!H7="X","Draw",Predictions!H7=2,$D5)</f>
+      <c r="H5" s="1" t="str" cm="1">
+        <f t="array" ref="H5">_xlfn.IFS(Predictions!H7=1,$E5,Predictions!H7="X","Draw",Predictions!H7=2,$F5)</f>
         <v>Paraguay</v>
       </c>
-      <c r="G5" s="1" t="str" cm="1">
-        <f t="array" ref="G5">_xlfn.IFS(Predictions!J7=1,$C5,Predictions!J7="X","Draw",Predictions!J7=2,$D5)</f>
+      <c r="I5" s="1" t="str" cm="1">
+        <f t="array" ref="I5">_xlfn.IFS(Predictions!J7=1,$E5,Predictions!J7="X","Draw",Predictions!J7=2,$F5)</f>
         <v>USA</v>
       </c>
-      <c r="H5" s="1" t="str" cm="1">
-        <f t="array" ref="H5">_xlfn.IFS(Predictions!L7=1,$C5,Predictions!L7="X","Draw",Predictions!L7=2,$D5)</f>
+      <c r="J5" s="1" t="str" cm="1">
+        <f t="array" ref="J5">_xlfn.IFS(Predictions!L7=1,$E5,Predictions!L7="X","Draw",Predictions!L7=2,$F5)</f>
         <v>USA</v>
       </c>
-      <c r="I5" s="1" t="str" cm="1">
-        <f t="array" ref="I5">_xlfn.IFS(Predictions!N7=1,$C5,Predictions!N7="X","Draw",Predictions!N7=2,$D5)</f>
+      <c r="K5" s="1" t="str" cm="1">
+        <f t="array" ref="K5">_xlfn.IFS(Predictions!N7=1,$E5,Predictions!N7="X","Draw",Predictions!N7=2,$F5)</f>
         <v>USA</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="26">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="164">
         <v>46186</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C6" s="163"/>
+      <c r="D6" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="E6" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="F6" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="1" t="str" cm="1">
-        <f t="array" ref="E6">_xlfn.IFS(Predictions!F8=1,$C6,Predictions!F8="X","Draw",Predictions!F8=2,$D6)</f>
+      <c r="G6" s="1" t="str" cm="1">
+        <f t="array" ref="G6">_xlfn.IFS(Predictions!F8=1,$E6,Predictions!F8="X","Draw",Predictions!F8=2,$F6)</f>
         <v>Switzerland</v>
       </c>
-      <c r="F6" s="1" t="str" cm="1">
-        <f t="array" ref="F6">_xlfn.IFS(Predictions!H8=1,$C6,Predictions!H8="X","Draw",Predictions!H8=2,$D6)</f>
+      <c r="H6" s="1" t="str" cm="1">
+        <f t="array" ref="H6">_xlfn.IFS(Predictions!H8=1,$E6,Predictions!H8="X","Draw",Predictions!H8=2,$F6)</f>
         <v>Switzerland</v>
       </c>
-      <c r="G6" s="1" t="str" cm="1">
-        <f t="array" ref="G6">_xlfn.IFS(Predictions!J8=1,$C6,Predictions!J8="X","Draw",Predictions!J8=2,$D6)</f>
+      <c r="I6" s="1" t="str" cm="1">
+        <f t="array" ref="I6">_xlfn.IFS(Predictions!J8=1,$E6,Predictions!J8="X","Draw",Predictions!J8=2,$F6)</f>
         <v>Switzerland</v>
       </c>
-      <c r="H6" s="1" t="str" cm="1">
-        <f t="array" ref="H6">_xlfn.IFS(Predictions!L8=1,$C6,Predictions!L8="X","Draw",Predictions!L8=2,$D6)</f>
+      <c r="J6" s="1" t="str" cm="1">
+        <f t="array" ref="J6">_xlfn.IFS(Predictions!L8=1,$E6,Predictions!L8="X","Draw",Predictions!L8=2,$F6)</f>
         <v>Switzerland</v>
       </c>
-      <c r="I6" s="1" t="str" cm="1">
-        <f t="array" ref="I6">_xlfn.IFS(Predictions!N8=1,$C6,Predictions!N8="X","Draw",Predictions!N8=2,$D6)</f>
+      <c r="K6" s="1" t="str" cm="1">
+        <f t="array" ref="K6">_xlfn.IFS(Predictions!N8=1,$E6,Predictions!N8="X","Draw",Predictions!N8=2,$F6)</f>
         <v>Switzerland</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="29">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="164">
         <v>46186</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="162">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C7" s="162"/>
+      <c r="D7" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="E7" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="F7" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="1" t="str" cm="1">
-        <f t="array" ref="E7">_xlfn.IFS(Predictions!F9=1,$C7,Predictions!F9="X","Draw",Predictions!F9=2,$D7)</f>
+      <c r="G7" s="1" t="str" cm="1">
+        <f t="array" ref="G7">_xlfn.IFS(Predictions!F9=1,$E7,Predictions!F9="X","Draw",Predictions!F9=2,$F7)</f>
         <v>Brazil</v>
       </c>
-      <c r="F7" s="1" t="str" cm="1">
-        <f t="array" ref="F7">_xlfn.IFS(Predictions!H9=1,$C7,Predictions!H9="X","Draw",Predictions!H9=2,$D7)</f>
+      <c r="H7" s="1" t="str" cm="1">
+        <f t="array" ref="H7">_xlfn.IFS(Predictions!H9=1,$E7,Predictions!H9="X","Draw",Predictions!H9=2,$F7)</f>
         <v>Morocco</v>
       </c>
-      <c r="G7" s="1" t="str" cm="1">
-        <f t="array" ref="G7">_xlfn.IFS(Predictions!J9=1,$C7,Predictions!J9="X","Draw",Predictions!J9=2,$D7)</f>
+      <c r="I7" s="1" t="str" cm="1">
+        <f t="array" ref="I7">_xlfn.IFS(Predictions!J9=1,$E7,Predictions!J9="X","Draw",Predictions!J9=2,$F7)</f>
         <v>Brazil</v>
       </c>
-      <c r="H7" s="1" t="str" cm="1">
-        <f t="array" ref="H7">_xlfn.IFS(Predictions!L9=1,$C7,Predictions!L9="X","Draw",Predictions!L9=2,$D7)</f>
+      <c r="J7" s="1" t="str" cm="1">
+        <f t="array" ref="J7">_xlfn.IFS(Predictions!L9=1,$E7,Predictions!L9="X","Draw",Predictions!L9=2,$F7)</f>
         <v>Brazil</v>
       </c>
-      <c r="I7" s="1" t="str" cm="1">
-        <f t="array" ref="I7">_xlfn.IFS(Predictions!N9=1,$C7,Predictions!N9="X","Draw",Predictions!N9=2,$D7)</f>
+      <c r="K7" s="1" t="str" cm="1">
+        <f t="array" ref="K7">_xlfn.IFS(Predictions!N9=1,$E7,Predictions!N9="X","Draw",Predictions!N9=2,$F7)</f>
         <v>Brazil</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="164">
         <v>46187</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="163">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="C8" s="163"/>
+      <c r="D8" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="E8" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="F8" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="1" t="str" cm="1">
-        <f t="array" ref="E8">_xlfn.IFS(Predictions!F10=1,$C8,Predictions!F10="X","Draw",Predictions!F10=2,$D8)</f>
+      <c r="G8" s="1" t="str" cm="1">
+        <f t="array" ref="G8">_xlfn.IFS(Predictions!F10=1,$E8,Predictions!F10="X","Draw",Predictions!F10=2,$F8)</f>
         <v>Scotland</v>
       </c>
-      <c r="F8" s="1" t="str" cm="1">
-        <f t="array" ref="F8">_xlfn.IFS(Predictions!H10=1,$C8,Predictions!H10="X","Draw",Predictions!H10=2,$D8)</f>
+      <c r="H8" s="1" t="str" cm="1">
+        <f t="array" ref="H8">_xlfn.IFS(Predictions!H10=1,$E8,Predictions!H10="X","Draw",Predictions!H10=2,$F8)</f>
         <v>Scotland</v>
       </c>
-      <c r="G8" s="1" t="str" cm="1">
-        <f t="array" ref="G8">_xlfn.IFS(Predictions!J10=1,$C8,Predictions!J10="X","Draw",Predictions!J10=2,$D8)</f>
+      <c r="I8" s="1" t="str" cm="1">
+        <f t="array" ref="I8">_xlfn.IFS(Predictions!J10=1,$E8,Predictions!J10="X","Draw",Predictions!J10=2,$F8)</f>
         <v>Scotland</v>
       </c>
-      <c r="H8" s="1" t="str" cm="1">
-        <f t="array" ref="H8">_xlfn.IFS(Predictions!L10=1,$C8,Predictions!L10="X","Draw",Predictions!L10=2,$D8)</f>
+      <c r="J8" s="1" t="str" cm="1">
+        <f t="array" ref="J8">_xlfn.IFS(Predictions!L10=1,$E8,Predictions!L10="X","Draw",Predictions!L10=2,$F8)</f>
         <v>Scotland</v>
       </c>
-      <c r="I8" s="1" t="str" cm="1">
-        <f t="array" ref="I8">_xlfn.IFS(Predictions!N10=1,$C8,Predictions!N10="X","Draw",Predictions!N10=2,$D8)</f>
+      <c r="K8" s="1" t="str" cm="1">
+        <f t="array" ref="K8">_xlfn.IFS(Predictions!N10=1,$E8,Predictions!N10="X","Draw",Predictions!N10=2,$F8)</f>
         <v>Scotland</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="26">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="164">
         <v>46187</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="163">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="C9" s="163"/>
+      <c r="D9" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="E9" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="F9" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="1" t="str" cm="1">
-        <f t="array" ref="E9">_xlfn.IFS(Predictions!F11=1,$C9,Predictions!F11="X","Draw",Predictions!F11=2,$D9)</f>
+      <c r="G9" s="1" t="str" cm="1">
+        <f t="array" ref="G9">_xlfn.IFS(Predictions!F11=1,$E9,Predictions!F11="X","Draw",Predictions!F11=2,$F9)</f>
         <v>Türkiye</v>
       </c>
-      <c r="F9" s="1" t="str" cm="1">
-        <f t="array" ref="F9">_xlfn.IFS(Predictions!H11=1,$C9,Predictions!H11="X","Draw",Predictions!H11=2,$D9)</f>
+      <c r="H9" s="1" t="str" cm="1">
+        <f t="array" ref="H9">_xlfn.IFS(Predictions!H11=1,$E9,Predictions!H11="X","Draw",Predictions!H11=2,$F9)</f>
         <v>Türkiye</v>
       </c>
-      <c r="G9" s="1" t="str" cm="1">
-        <f t="array" ref="G9">_xlfn.IFS(Predictions!J11=1,$C9,Predictions!J11="X","Draw",Predictions!J11=2,$D9)</f>
+      <c r="I9" s="1" t="str" cm="1">
+        <f t="array" ref="I9">_xlfn.IFS(Predictions!J11=1,$E9,Predictions!J11="X","Draw",Predictions!J11=2,$F9)</f>
         <v>Türkiye</v>
       </c>
-      <c r="H9" s="1" t="str" cm="1">
-        <f t="array" ref="H9">_xlfn.IFS(Predictions!L11=1,$C9,Predictions!L11="X","Draw",Predictions!L11=2,$D9)</f>
+      <c r="J9" s="1" t="str" cm="1">
+        <f t="array" ref="J9">_xlfn.IFS(Predictions!L11=1,$E9,Predictions!L11="X","Draw",Predictions!L11=2,$F9)</f>
         <v>Türkiye</v>
       </c>
-      <c r="I9" s="1" t="str" cm="1">
-        <f t="array" ref="I9">_xlfn.IFS(Predictions!N11=1,$C9,Predictions!N11="X","Draw",Predictions!N11=2,$D9)</f>
+      <c r="K9" s="1" t="str" cm="1">
+        <f t="array" ref="K9">_xlfn.IFS(Predictions!N11=1,$E9,Predictions!N11="X","Draw",Predictions!N11=2,$F9)</f>
         <v>Türkiye</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="26">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="164">
         <v>46187</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="163">
+        <v>0.75</v>
+      </c>
+      <c r="C10" s="163"/>
+      <c r="D10" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="E10" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="F10" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="1" t="str" cm="1">
-        <f t="array" ref="E10">_xlfn.IFS(Predictions!F12=1,$C10,Predictions!F12="X","Draw",Predictions!F12=2,$D10)</f>
+      <c r="G10" s="1" t="str" cm="1">
+        <f t="array" ref="G10">_xlfn.IFS(Predictions!F12=1,$E10,Predictions!F12="X","Draw",Predictions!F12=2,$F10)</f>
         <v>Germany</v>
       </c>
-      <c r="F10" s="1" t="str" cm="1">
-        <f t="array" ref="F10">_xlfn.IFS(Predictions!H12=1,$C10,Predictions!H12="X","Draw",Predictions!H12=2,$D10)</f>
+      <c r="H10" s="1" t="str" cm="1">
+        <f t="array" ref="H10">_xlfn.IFS(Predictions!H12=1,$E10,Predictions!H12="X","Draw",Predictions!H12=2,$F10)</f>
         <v>Germany</v>
       </c>
-      <c r="G10" s="1" t="str" cm="1">
-        <f t="array" ref="G10">_xlfn.IFS(Predictions!J12=1,$C10,Predictions!J12="X","Draw",Predictions!J12=2,$D10)</f>
+      <c r="I10" s="1" t="str" cm="1">
+        <f t="array" ref="I10">_xlfn.IFS(Predictions!J12=1,$E10,Predictions!J12="X","Draw",Predictions!J12=2,$F10)</f>
         <v>Germany</v>
       </c>
-      <c r="H10" s="1" t="str" cm="1">
-        <f t="array" ref="H10">_xlfn.IFS(Predictions!L12=1,$C10,Predictions!L12="X","Draw",Predictions!L12=2,$D10)</f>
+      <c r="J10" s="1" t="str" cm="1">
+        <f t="array" ref="J10">_xlfn.IFS(Predictions!L12=1,$E10,Predictions!L12="X","Draw",Predictions!L12=2,$F10)</f>
         <v>Germany</v>
       </c>
-      <c r="I10" s="1" t="str" cm="1">
-        <f t="array" ref="I10">_xlfn.IFS(Predictions!N12=1,$C10,Predictions!N12="X","Draw",Predictions!N12=2,$D10)</f>
+      <c r="K10" s="1" t="str" cm="1">
+        <f t="array" ref="K10">_xlfn.IFS(Predictions!N12=1,$E10,Predictions!N12="X","Draw",Predictions!N12=2,$F10)</f>
         <v>Germany</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="29">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="164">
         <v>46187</v>
       </c>
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="162">
+        <v>0.875</v>
+      </c>
+      <c r="C11" s="162"/>
+      <c r="D11" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="E11" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="F11" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="1" t="str" cm="1">
-        <f t="array" ref="E11">_xlfn.IFS(Predictions!F13=1,$C11,Predictions!F13="X","Draw",Predictions!F13=2,$D11)</f>
+      <c r="G11" s="1" t="str" cm="1">
+        <f t="array" ref="G11">_xlfn.IFS(Predictions!F13=1,$E11,Predictions!F13="X","Draw",Predictions!F13=2,$F11)</f>
         <v>Draw</v>
       </c>
-      <c r="F11" s="1" t="str" cm="1">
-        <f t="array" ref="F11">_xlfn.IFS(Predictions!H13=1,$C11,Predictions!H13="X","Draw",Predictions!H13=2,$D11)</f>
+      <c r="H11" s="1" t="str" cm="1">
+        <f t="array" ref="H11">_xlfn.IFS(Predictions!H13=1,$E11,Predictions!H13="X","Draw",Predictions!H13=2,$F11)</f>
         <v>Netherlands</v>
       </c>
-      <c r="G11" s="1" t="str" cm="1">
-        <f t="array" ref="G11">_xlfn.IFS(Predictions!J13=1,$C11,Predictions!J13="X","Draw",Predictions!J13=2,$D11)</f>
+      <c r="I11" s="1" t="str" cm="1">
+        <f t="array" ref="I11">_xlfn.IFS(Predictions!J13=1,$E11,Predictions!J13="X","Draw",Predictions!J13=2,$F11)</f>
         <v>Netherlands</v>
       </c>
-      <c r="H11" s="1" t="str" cm="1">
-        <f t="array" ref="H11">_xlfn.IFS(Predictions!L13=1,$C11,Predictions!L13="X","Draw",Predictions!L13=2,$D11)</f>
+      <c r="J11" s="1" t="str" cm="1">
+        <f t="array" ref="J11">_xlfn.IFS(Predictions!L13=1,$E11,Predictions!L13="X","Draw",Predictions!L13=2,$F11)</f>
         <v>Draw</v>
       </c>
-      <c r="I11" s="1" t="str" cm="1">
-        <f t="array" ref="I11">_xlfn.IFS(Predictions!N13=1,$C11,Predictions!N13="X","Draw",Predictions!N13=2,$D11)</f>
+      <c r="K11" s="1" t="str" cm="1">
+        <f t="array" ref="K11">_xlfn.IFS(Predictions!N13=1,$E11,Predictions!N13="X","Draw",Predictions!N13=2,$F11)</f>
         <v>Draw</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="26">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="164">
         <v>46188</v>
       </c>
-      <c r="B12" s="36" t="s">
+      <c r="B12" s="163">
+        <v>0</v>
+      </c>
+      <c r="C12" s="163"/>
+      <c r="D12" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="E12" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="F12" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="1" t="str" cm="1">
-        <f t="array" ref="E12">_xlfn.IFS(Predictions!F14=1,$C12,Predictions!F14="X","Draw",Predictions!F14=2,$D12)</f>
+      <c r="G12" s="1" t="str" cm="1">
+        <f t="array" ref="G12">_xlfn.IFS(Predictions!F14=1,$E12,Predictions!F14="X","Draw",Predictions!F14=2,$F12)</f>
         <v>Côte d'Ivoire</v>
       </c>
-      <c r="F12" s="1" t="str" cm="1">
-        <f t="array" ref="F12">_xlfn.IFS(Predictions!H14=1,$C12,Predictions!H14="X","Draw",Predictions!H14=2,$D12)</f>
+      <c r="H12" s="1" t="str" cm="1">
+        <f t="array" ref="H12">_xlfn.IFS(Predictions!H14=1,$E12,Predictions!H14="X","Draw",Predictions!H14=2,$F12)</f>
         <v>Draw</v>
       </c>
-      <c r="G12" s="1" t="str" cm="1">
-        <f t="array" ref="G12">_xlfn.IFS(Predictions!J14=1,$C12,Predictions!J14="X","Draw",Predictions!J14=2,$D12)</f>
+      <c r="I12" s="1" t="str" cm="1">
+        <f t="array" ref="I12">_xlfn.IFS(Predictions!J14=1,$E12,Predictions!J14="X","Draw",Predictions!J14=2,$F12)</f>
         <v>Côte d'Ivoire</v>
       </c>
-      <c r="H12" s="1" t="str" cm="1">
-        <f t="array" ref="H12">_xlfn.IFS(Predictions!L14=1,$C12,Predictions!L14="X","Draw",Predictions!L14=2,$D12)</f>
+      <c r="J12" s="1" t="str" cm="1">
+        <f t="array" ref="J12">_xlfn.IFS(Predictions!L14=1,$E12,Predictions!L14="X","Draw",Predictions!L14=2,$F12)</f>
         <v>Draw</v>
       </c>
-      <c r="I12" s="1" t="str" cm="1">
-        <f t="array" ref="I12">_xlfn.IFS(Predictions!N14=1,$C12,Predictions!N14="X","Draw",Predictions!N14=2,$D12)</f>
+      <c r="K12" s="1" t="str" cm="1">
+        <f t="array" ref="K12">_xlfn.IFS(Predictions!N14=1,$E12,Predictions!N14="X","Draw",Predictions!N14=2,$F12)</f>
         <v>Ecuador</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="26">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="164">
         <v>46188</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="163">
+        <v>0.125</v>
+      </c>
+      <c r="C13" s="163"/>
+      <c r="D13" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="E13" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="F13" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="1" t="str" cm="1">
-        <f t="array" ref="E13">_xlfn.IFS(Predictions!F15=1,$C13,Predictions!F15="X","Draw",Predictions!F15=2,$D13)</f>
+      <c r="G13" s="1" t="str" cm="1">
+        <f t="array" ref="G13">_xlfn.IFS(Predictions!F15=1,$E13,Predictions!F15="X","Draw",Predictions!F15=2,$F13)</f>
         <v>Sweden</v>
       </c>
-      <c r="F13" s="1" t="str" cm="1">
-        <f t="array" ref="F13">_xlfn.IFS(Predictions!H15=1,$C13,Predictions!H15="X","Draw",Predictions!H15=2,$D13)</f>
+      <c r="H13" s="1" t="str" cm="1">
+        <f t="array" ref="H13">_xlfn.IFS(Predictions!H15=1,$E13,Predictions!H15="X","Draw",Predictions!H15=2,$F13)</f>
         <v>Draw</v>
       </c>
-      <c r="G13" s="1" t="str" cm="1">
-        <f t="array" ref="G13">_xlfn.IFS(Predictions!J15=1,$C13,Predictions!J15="X","Draw",Predictions!J15=2,$D13)</f>
+      <c r="I13" s="1" t="str" cm="1">
+        <f t="array" ref="I13">_xlfn.IFS(Predictions!J15=1,$E13,Predictions!J15="X","Draw",Predictions!J15=2,$F13)</f>
         <v>Sweden</v>
       </c>
-      <c r="H13" s="1" t="str" cm="1">
-        <f t="array" ref="H13">_xlfn.IFS(Predictions!L15=1,$C13,Predictions!L15="X","Draw",Predictions!L15=2,$D13)</f>
+      <c r="J13" s="1" t="str" cm="1">
+        <f t="array" ref="J13">_xlfn.IFS(Predictions!L15=1,$E13,Predictions!L15="X","Draw",Predictions!L15=2,$F13)</f>
         <v>Sweden</v>
       </c>
-      <c r="I13" s="1" t="str" cm="1">
-        <f t="array" ref="I13">_xlfn.IFS(Predictions!N15=1,$C13,Predictions!N15="X","Draw",Predictions!N15=2,$D13)</f>
+      <c r="K13" s="1" t="str" cm="1">
+        <f t="array" ref="K13">_xlfn.IFS(Predictions!N15=1,$E13,Predictions!N15="X","Draw",Predictions!N15=2,$F13)</f>
         <v>Tunisia</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="26">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="164">
         <v>46188</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="163">
+        <v>0.75</v>
+      </c>
+      <c r="C14" s="163"/>
+      <c r="D14" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="E14" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="F14" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="1" t="str" cm="1">
-        <f t="array" ref="E14">_xlfn.IFS(Predictions!F16=1,$C14,Predictions!F16="X","Draw",Predictions!F16=2,$D14)</f>
+      <c r="G14" s="1" t="str" cm="1">
+        <f t="array" ref="G14">_xlfn.IFS(Predictions!F16=1,$E14,Predictions!F16="X","Draw",Predictions!F16=2,$F14)</f>
         <v>Belgium</v>
       </c>
-      <c r="F14" s="1" t="str" cm="1">
-        <f t="array" ref="F14">_xlfn.IFS(Predictions!H16=1,$C14,Predictions!H16="X","Draw",Predictions!H16=2,$D14)</f>
+      <c r="H14" s="1" t="str" cm="1">
+        <f t="array" ref="H14">_xlfn.IFS(Predictions!H16=1,$E14,Predictions!H16="X","Draw",Predictions!H16=2,$F14)</f>
         <v>Belgium</v>
       </c>
-      <c r="G14" s="1" t="str" cm="1">
-        <f t="array" ref="G14">_xlfn.IFS(Predictions!J16=1,$C14,Predictions!J16="X","Draw",Predictions!J16=2,$D14)</f>
+      <c r="I14" s="1" t="str" cm="1">
+        <f t="array" ref="I14">_xlfn.IFS(Predictions!J16=1,$E14,Predictions!J16="X","Draw",Predictions!J16=2,$F14)</f>
         <v>Belgium</v>
       </c>
-      <c r="H14" s="1" t="str" cm="1">
-        <f t="array" ref="H14">_xlfn.IFS(Predictions!L16=1,$C14,Predictions!L16="X","Draw",Predictions!L16=2,$D14)</f>
+      <c r="J14" s="1" t="str" cm="1">
+        <f t="array" ref="J14">_xlfn.IFS(Predictions!L16=1,$E14,Predictions!L16="X","Draw",Predictions!L16=2,$F14)</f>
         <v>Belgium</v>
       </c>
-      <c r="I14" s="1" t="str" cm="1">
-        <f t="array" ref="I14">_xlfn.IFS(Predictions!N16=1,$C14,Predictions!N16="X","Draw",Predictions!N16=2,$D14)</f>
+      <c r="K14" s="1" t="str" cm="1">
+        <f t="array" ref="K14">_xlfn.IFS(Predictions!N16=1,$E14,Predictions!N16="X","Draw",Predictions!N16=2,$F14)</f>
         <v>Belgium</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="26">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="164">
         <v>46188</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="163">
+        <v>0.875</v>
+      </c>
+      <c r="C15" s="163"/>
+      <c r="D15" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="E15" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="F15" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="1" t="str" cm="1">
-        <f t="array" ref="E15">_xlfn.IFS(Predictions!F17=1,$C15,Predictions!F17="X","Draw",Predictions!F17=2,$D15)</f>
+      <c r="G15" s="1" t="str" cm="1">
+        <f t="array" ref="G15">_xlfn.IFS(Predictions!F17=1,$E15,Predictions!F17="X","Draw",Predictions!F17=2,$F15)</f>
         <v>Spain</v>
       </c>
-      <c r="F15" s="1" t="str" cm="1">
-        <f t="array" ref="F15">_xlfn.IFS(Predictions!H17=1,$C15,Predictions!H17="X","Draw",Predictions!H17=2,$D15)</f>
+      <c r="H15" s="1" t="str" cm="1">
+        <f t="array" ref="H15">_xlfn.IFS(Predictions!H17=1,$E15,Predictions!H17="X","Draw",Predictions!H17=2,$F15)</f>
         <v>Spain</v>
       </c>
-      <c r="G15" s="1" t="str" cm="1">
-        <f t="array" ref="G15">_xlfn.IFS(Predictions!J17=1,$C15,Predictions!J17="X","Draw",Predictions!J17=2,$D15)</f>
+      <c r="I15" s="1" t="str" cm="1">
+        <f t="array" ref="I15">_xlfn.IFS(Predictions!J17=1,$E15,Predictions!J17="X","Draw",Predictions!J17=2,$F15)</f>
         <v>Spain</v>
       </c>
-      <c r="H15" s="1" t="str" cm="1">
-        <f t="array" ref="H15">_xlfn.IFS(Predictions!L17=1,$C15,Predictions!L17="X","Draw",Predictions!L17=2,$D15)</f>
+      <c r="J15" s="1" t="str" cm="1">
+        <f t="array" ref="J15">_xlfn.IFS(Predictions!L17=1,$E15,Predictions!L17="X","Draw",Predictions!L17=2,$F15)</f>
         <v>Spain</v>
       </c>
-      <c r="I15" s="1" t="str" cm="1">
-        <f t="array" ref="I15">_xlfn.IFS(Predictions!N17=1,$C15,Predictions!N17="X","Draw",Predictions!N17=2,$D15)</f>
+      <c r="K15" s="1" t="str" cm="1">
+        <f t="array" ref="K15">_xlfn.IFS(Predictions!N17=1,$E15,Predictions!N17="X","Draw",Predictions!N17=2,$F15)</f>
         <v>Spain</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="29">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="164">
         <v>46188</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="162">
+        <v>0</v>
+      </c>
+      <c r="C16" s="162"/>
+      <c r="D16" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="E16" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="F16" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="1" t="str" cm="1">
-        <f t="array" ref="E16">_xlfn.IFS(Predictions!F18=1,$C16,Predictions!F18="X","Draw",Predictions!F18=2,$D16)</f>
+      <c r="G16" s="1" t="str" cm="1">
+        <f t="array" ref="G16">_xlfn.IFS(Predictions!F18=1,$E16,Predictions!F18="X","Draw",Predictions!F18=2,$F16)</f>
         <v>Uruguay</v>
       </c>
-      <c r="F16" s="1" t="str" cm="1">
-        <f t="array" ref="F16">_xlfn.IFS(Predictions!H18=1,$C16,Predictions!H18="X","Draw",Predictions!H18=2,$D16)</f>
+      <c r="H16" s="1" t="str" cm="1">
+        <f t="array" ref="H16">_xlfn.IFS(Predictions!H18=1,$E16,Predictions!H18="X","Draw",Predictions!H18=2,$F16)</f>
         <v>Uruguay</v>
       </c>
-      <c r="G16" s="1" t="str" cm="1">
-        <f t="array" ref="G16">_xlfn.IFS(Predictions!J18=1,$C16,Predictions!J18="X","Draw",Predictions!J18=2,$D16)</f>
+      <c r="I16" s="1" t="str" cm="1">
+        <f t="array" ref="I16">_xlfn.IFS(Predictions!J18=1,$E16,Predictions!J18="X","Draw",Predictions!J18=2,$F16)</f>
         <v>Uruguay</v>
       </c>
-      <c r="H16" s="1" t="str" cm="1">
-        <f t="array" ref="H16">_xlfn.IFS(Predictions!L18=1,$C16,Predictions!L18="X","Draw",Predictions!L18=2,$D16)</f>
+      <c r="J16" s="1" t="str" cm="1">
+        <f t="array" ref="J16">_xlfn.IFS(Predictions!L18=1,$E16,Predictions!L18="X","Draw",Predictions!L18=2,$F16)</f>
         <v>Uruguay</v>
       </c>
-      <c r="I16" s="1" t="str" cm="1">
-        <f t="array" ref="I16">_xlfn.IFS(Predictions!N18=1,$C16,Predictions!N18="X","Draw",Predictions!N18=2,$D16)</f>
+      <c r="K16" s="1" t="str" cm="1">
+        <f t="array" ref="K16">_xlfn.IFS(Predictions!N18=1,$E16,Predictions!N18="X","Draw",Predictions!N18=2,$F16)</f>
         <v>Uruguay</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="26">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="164">
         <v>46189</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="163">
+        <v>0.125</v>
+      </c>
+      <c r="C17" s="163"/>
+      <c r="D17" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="E17" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="F17" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="1" t="str" cm="1">
-        <f t="array" ref="E17">_xlfn.IFS(Predictions!F19=1,$C17,Predictions!F19="X","Draw",Predictions!F19=2,$D17)</f>
+      <c r="G17" s="1" t="str" cm="1">
+        <f t="array" ref="G17">_xlfn.IFS(Predictions!F19=1,$E17,Predictions!F19="X","Draw",Predictions!F19=2,$F17)</f>
         <v>Draw</v>
       </c>
-      <c r="F17" s="1" t="str" cm="1">
-        <f t="array" ref="F17">_xlfn.IFS(Predictions!H19=1,$C17,Predictions!H19="X","Draw",Predictions!H19=2,$D17)</f>
+      <c r="H17" s="1" t="str" cm="1">
+        <f t="array" ref="H17">_xlfn.IFS(Predictions!H19=1,$E17,Predictions!H19="X","Draw",Predictions!H19=2,$F17)</f>
         <v>IR Iran</v>
       </c>
-      <c r="G17" s="1" t="str" cm="1">
-        <f t="array" ref="G17">_xlfn.IFS(Predictions!J19=1,$C17,Predictions!J19="X","Draw",Predictions!J19=2,$D17)</f>
+      <c r="I17" s="1" t="str" cm="1">
+        <f t="array" ref="I17">_xlfn.IFS(Predictions!J19=1,$E17,Predictions!J19="X","Draw",Predictions!J19=2,$F17)</f>
         <v>New Zealand</v>
       </c>
-      <c r="H17" s="1" t="str" cm="1">
-        <f t="array" ref="H17">_xlfn.IFS(Predictions!L19=1,$C17,Predictions!L19="X","Draw",Predictions!L19=2,$D17)</f>
+      <c r="J17" s="1" t="str" cm="1">
+        <f t="array" ref="J17">_xlfn.IFS(Predictions!L19=1,$E17,Predictions!L19="X","Draw",Predictions!L19=2,$F17)</f>
         <v>IR Iran</v>
       </c>
-      <c r="I17" s="1" t="str" cm="1">
-        <f t="array" ref="I17">_xlfn.IFS(Predictions!N19=1,$C17,Predictions!N19="X","Draw",Predictions!N19=2,$D17)</f>
+      <c r="K17" s="1" t="str" cm="1">
+        <f t="array" ref="K17">_xlfn.IFS(Predictions!N19=1,$E17,Predictions!N19="X","Draw",Predictions!N19=2,$F17)</f>
         <v>IR Iran</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="26">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="164">
         <v>46189</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="163">
+        <v>0.75</v>
+      </c>
+      <c r="C18" s="163"/>
+      <c r="D18" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="E18" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="F18" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="1" t="str" cm="1">
-        <f t="array" ref="E18">_xlfn.IFS(Predictions!F20=1,$C18,Predictions!F20="X","Draw",Predictions!F20=2,$D18)</f>
+      <c r="G18" s="1" t="str" cm="1">
+        <f t="array" ref="G18">_xlfn.IFS(Predictions!F20=1,$E18,Predictions!F20="X","Draw",Predictions!F20=2,$F18)</f>
         <v>France</v>
       </c>
-      <c r="F18" s="1" t="str" cm="1">
-        <f t="array" ref="F18">_xlfn.IFS(Predictions!H20=1,$C18,Predictions!H20="X","Draw",Predictions!H20=2,$D18)</f>
+      <c r="H18" s="1" t="str" cm="1">
+        <f t="array" ref="H18">_xlfn.IFS(Predictions!H20=1,$E18,Predictions!H20="X","Draw",Predictions!H20=2,$F18)</f>
         <v>France</v>
       </c>
-      <c r="G18" s="1" t="str" cm="1">
-        <f t="array" ref="G18">_xlfn.IFS(Predictions!J20=1,$C18,Predictions!J20="X","Draw",Predictions!J20=2,$D18)</f>
+      <c r="I18" s="1" t="str" cm="1">
+        <f t="array" ref="I18">_xlfn.IFS(Predictions!J20=1,$E18,Predictions!J20="X","Draw",Predictions!J20=2,$F18)</f>
         <v>France</v>
       </c>
-      <c r="H18" s="1" t="str" cm="1">
-        <f t="array" ref="H18">_xlfn.IFS(Predictions!L20=1,$C18,Predictions!L20="X","Draw",Predictions!L20=2,$D18)</f>
+      <c r="J18" s="1" t="str" cm="1">
+        <f t="array" ref="J18">_xlfn.IFS(Predictions!L20=1,$E18,Predictions!L20="X","Draw",Predictions!L20=2,$F18)</f>
         <v>France</v>
       </c>
-      <c r="I18" s="1" t="str" cm="1">
-        <f t="array" ref="I18">_xlfn.IFS(Predictions!N20=1,$C18,Predictions!N20="X","Draw",Predictions!N20=2,$D18)</f>
+      <c r="K18" s="1" t="str" cm="1">
+        <f t="array" ref="K18">_xlfn.IFS(Predictions!N20=1,$E18,Predictions!N20="X","Draw",Predictions!N20=2,$F18)</f>
         <v>France</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="29">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="164">
         <v>46189</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="162">
+        <v>0.875</v>
+      </c>
+      <c r="C19" s="162"/>
+      <c r="D19" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="E19" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="F19" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="1" t="str" cm="1">
-        <f t="array" ref="E19">_xlfn.IFS(Predictions!F21=1,$C19,Predictions!F21="X","Draw",Predictions!F21=2,$D19)</f>
+      <c r="G19" s="1" t="str" cm="1">
+        <f t="array" ref="G19">_xlfn.IFS(Predictions!F21=1,$E19,Predictions!F21="X","Draw",Predictions!F21=2,$F19)</f>
         <v>Norway</v>
       </c>
-      <c r="F19" s="1" t="str" cm="1">
-        <f t="array" ref="F19">_xlfn.IFS(Predictions!H21=1,$C19,Predictions!H21="X","Draw",Predictions!H21=2,$D19)</f>
+      <c r="H19" s="1" t="str" cm="1">
+        <f t="array" ref="H19">_xlfn.IFS(Predictions!H21=1,$E19,Predictions!H21="X","Draw",Predictions!H21=2,$F19)</f>
         <v>Norway</v>
       </c>
-      <c r="G19" s="1" t="str" cm="1">
-        <f t="array" ref="G19">_xlfn.IFS(Predictions!J21=1,$C19,Predictions!J21="X","Draw",Predictions!J21=2,$D19)</f>
+      <c r="I19" s="1" t="str" cm="1">
+        <f t="array" ref="I19">_xlfn.IFS(Predictions!J21=1,$E19,Predictions!J21="X","Draw",Predictions!J21=2,$F19)</f>
         <v>Norway</v>
       </c>
-      <c r="H19" s="1" t="str" cm="1">
-        <f t="array" ref="H19">_xlfn.IFS(Predictions!L21=1,$C19,Predictions!L21="X","Draw",Predictions!L21=2,$D19)</f>
+      <c r="J19" s="1" t="str" cm="1">
+        <f t="array" ref="J19">_xlfn.IFS(Predictions!L21=1,$E19,Predictions!L21="X","Draw",Predictions!L21=2,$F19)</f>
         <v>Norway</v>
       </c>
-      <c r="I19" s="1" t="str" cm="1">
-        <f t="array" ref="I19">_xlfn.IFS(Predictions!N21=1,$C19,Predictions!N21="X","Draw",Predictions!N21=2,$D19)</f>
+      <c r="K19" s="1" t="str" cm="1">
+        <f t="array" ref="K19">_xlfn.IFS(Predictions!N21=1,$E19,Predictions!N21="X","Draw",Predictions!N21=2,$F19)</f>
         <v>Norway</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="26">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="164">
         <v>46190</v>
       </c>
-      <c r="B20" s="44" t="s">
+      <c r="B20" s="163">
+        <v>0</v>
+      </c>
+      <c r="C20" s="163"/>
+      <c r="D20" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="E20" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="F20" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E20" s="1" t="str" cm="1">
-        <f t="array" ref="E20">_xlfn.IFS(Predictions!F22=1,$C20,Predictions!F22="X","Draw",Predictions!F22=2,$D20)</f>
+      <c r="G20" s="1" t="str" cm="1">
+        <f t="array" ref="G20">_xlfn.IFS(Predictions!F22=1,$E20,Predictions!F22="X","Draw",Predictions!F22=2,$F20)</f>
         <v>Argentina</v>
       </c>
-      <c r="F20" s="1" t="str" cm="1">
-        <f t="array" ref="F20">_xlfn.IFS(Predictions!H22=1,$C20,Predictions!H22="X","Draw",Predictions!H22=2,$D20)</f>
+      <c r="H20" s="1" t="str" cm="1">
+        <f t="array" ref="H20">_xlfn.IFS(Predictions!H22=1,$E20,Predictions!H22="X","Draw",Predictions!H22=2,$F20)</f>
         <v>Argentina</v>
       </c>
-      <c r="G20" s="1" t="str" cm="1">
-        <f t="array" ref="G20">_xlfn.IFS(Predictions!J22=1,$C20,Predictions!J22="X","Draw",Predictions!J22=2,$D20)</f>
+      <c r="I20" s="1" t="str" cm="1">
+        <f t="array" ref="I20">_xlfn.IFS(Predictions!J22=1,$E20,Predictions!J22="X","Draw",Predictions!J22=2,$F20)</f>
         <v>Argentina</v>
       </c>
-      <c r="H20" s="1" t="str" cm="1">
-        <f t="array" ref="H20">_xlfn.IFS(Predictions!L22=1,$C20,Predictions!L22="X","Draw",Predictions!L22=2,$D20)</f>
+      <c r="J20" s="1" t="str" cm="1">
+        <f t="array" ref="J20">_xlfn.IFS(Predictions!L22=1,$E20,Predictions!L22="X","Draw",Predictions!L22=2,$F20)</f>
         <v>Argentina</v>
       </c>
-      <c r="I20" s="1" t="str" cm="1">
-        <f t="array" ref="I20">_xlfn.IFS(Predictions!N22=1,$C20,Predictions!N22="X","Draw",Predictions!N22=2,$D20)</f>
+      <c r="K20" s="1" t="str" cm="1">
+        <f t="array" ref="K20">_xlfn.IFS(Predictions!N22=1,$E20,Predictions!N22="X","Draw",Predictions!N22=2,$F20)</f>
         <v>Argentina</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="26">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="164">
         <v>46190</v>
       </c>
-      <c r="B21" s="44" t="s">
+      <c r="B21" s="163">
+        <v>0.125</v>
+      </c>
+      <c r="C21" s="163"/>
+      <c r="D21" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="E21" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="F21" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="1" t="str" cm="1">
-        <f t="array" ref="E21">_xlfn.IFS(Predictions!F23=1,$C21,Predictions!F23="X","Draw",Predictions!F23=2,$D21)</f>
+      <c r="G21" s="1" t="str" cm="1">
+        <f t="array" ref="G21">_xlfn.IFS(Predictions!F23=1,$E21,Predictions!F23="X","Draw",Predictions!F23=2,$F21)</f>
         <v>Austria</v>
       </c>
-      <c r="F21" s="1" t="str" cm="1">
-        <f t="array" ref="F21">_xlfn.IFS(Predictions!H23=1,$C21,Predictions!H23="X","Draw",Predictions!H23=2,$D21)</f>
+      <c r="H21" s="1" t="str" cm="1">
+        <f t="array" ref="H21">_xlfn.IFS(Predictions!H23=1,$E21,Predictions!H23="X","Draw",Predictions!H23=2,$F21)</f>
         <v>Austria</v>
       </c>
-      <c r="G21" s="1" t="str" cm="1">
-        <f t="array" ref="G21">_xlfn.IFS(Predictions!J23=1,$C21,Predictions!J23="X","Draw",Predictions!J23=2,$D21)</f>
+      <c r="I21" s="1" t="str" cm="1">
+        <f t="array" ref="I21">_xlfn.IFS(Predictions!J23=1,$E21,Predictions!J23="X","Draw",Predictions!J23=2,$F21)</f>
         <v>Austria</v>
       </c>
-      <c r="H21" s="1" t="str" cm="1">
-        <f t="array" ref="H21">_xlfn.IFS(Predictions!L23=1,$C21,Predictions!L23="X","Draw",Predictions!L23=2,$D21)</f>
+      <c r="J21" s="1" t="str" cm="1">
+        <f t="array" ref="J21">_xlfn.IFS(Predictions!L23=1,$E21,Predictions!L23="X","Draw",Predictions!L23=2,$F21)</f>
         <v>Austria</v>
       </c>
-      <c r="I21" s="1" t="str" cm="1">
-        <f t="array" ref="I21">_xlfn.IFS(Predictions!N23=1,$C21,Predictions!N23="X","Draw",Predictions!N23=2,$D21)</f>
+      <c r="K21" s="1" t="str" cm="1">
+        <f t="array" ref="K21">_xlfn.IFS(Predictions!N23=1,$E21,Predictions!N23="X","Draw",Predictions!N23=2,$F21)</f>
         <v>Austria</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="26">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="164">
         <v>46190</v>
       </c>
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="163">
+        <v>0.75</v>
+      </c>
+      <c r="C22" s="163"/>
+      <c r="D22" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="E22" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="F22" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="E22" s="1" t="str" cm="1">
-        <f t="array" ref="E22">_xlfn.IFS(Predictions!F24=1,$C22,Predictions!F24="X","Draw",Predictions!F24=2,$D22)</f>
+      <c r="G22" s="1" t="str" cm="1">
+        <f t="array" ref="G22">_xlfn.IFS(Predictions!F24=1,$E22,Predictions!F24="X","Draw",Predictions!F24=2,$F22)</f>
         <v>Portugal</v>
       </c>
-      <c r="F22" s="1" t="str" cm="1">
-        <f t="array" ref="F22">_xlfn.IFS(Predictions!H24=1,$C22,Predictions!H24="X","Draw",Predictions!H24=2,$D22)</f>
+      <c r="H22" s="1" t="str" cm="1">
+        <f t="array" ref="H22">_xlfn.IFS(Predictions!H24=1,$E22,Predictions!H24="X","Draw",Predictions!H24=2,$F22)</f>
         <v>Portugal</v>
       </c>
-      <c r="G22" s="1" t="str" cm="1">
-        <f t="array" ref="G22">_xlfn.IFS(Predictions!J24=1,$C22,Predictions!J24="X","Draw",Predictions!J24=2,$D22)</f>
+      <c r="I22" s="1" t="str" cm="1">
+        <f t="array" ref="I22">_xlfn.IFS(Predictions!J24=1,$E22,Predictions!J24="X","Draw",Predictions!J24=2,$F22)</f>
         <v>Portugal</v>
       </c>
-      <c r="H22" s="1" t="str" cm="1">
-        <f t="array" ref="H22">_xlfn.IFS(Predictions!L24=1,$C22,Predictions!L24="X","Draw",Predictions!L24=2,$D22)</f>
+      <c r="J22" s="1" t="str" cm="1">
+        <f t="array" ref="J22">_xlfn.IFS(Predictions!L24=1,$E22,Predictions!L24="X","Draw",Predictions!L24=2,$F22)</f>
         <v>Portugal</v>
       </c>
-      <c r="I22" s="1" t="str" cm="1">
-        <f t="array" ref="I22">_xlfn.IFS(Predictions!N24=1,$C22,Predictions!N24="X","Draw",Predictions!N24=2,$D22)</f>
+      <c r="K22" s="1" t="str" cm="1">
+        <f t="array" ref="K22">_xlfn.IFS(Predictions!N24=1,$E22,Predictions!N24="X","Draw",Predictions!N24=2,$F22)</f>
         <v>Portugal</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="29">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="164">
         <v>46190</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="162">
+        <v>0.875</v>
+      </c>
+      <c r="C23" s="162"/>
+      <c r="D23" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="E23" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="31" t="s">
+      <c r="F23" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="1" t="str" cm="1">
-        <f t="array" ref="E23">_xlfn.IFS(Predictions!F25=1,$C23,Predictions!F25="X","Draw",Predictions!F25=2,$D23)</f>
+      <c r="G23" s="1" t="str" cm="1">
+        <f t="array" ref="G23">_xlfn.IFS(Predictions!F25=1,$E23,Predictions!F25="X","Draw",Predictions!F25=2,$F23)</f>
         <v>Draw</v>
       </c>
-      <c r="F23" s="1" t="str" cm="1">
-        <f t="array" ref="F23">_xlfn.IFS(Predictions!H25=1,$C23,Predictions!H25="X","Draw",Predictions!H25=2,$D23)</f>
+      <c r="H23" s="1" t="str" cm="1">
+        <f t="array" ref="H23">_xlfn.IFS(Predictions!H25=1,$E23,Predictions!H25="X","Draw",Predictions!H25=2,$F23)</f>
         <v>England</v>
       </c>
-      <c r="G23" s="1" t="str" cm="1">
-        <f t="array" ref="G23">_xlfn.IFS(Predictions!J25=1,$C23,Predictions!J25="X","Draw",Predictions!J25=2,$D23)</f>
+      <c r="I23" s="1" t="str" cm="1">
+        <f t="array" ref="I23">_xlfn.IFS(Predictions!J25=1,$E23,Predictions!J25="X","Draw",Predictions!J25=2,$F23)</f>
         <v>England</v>
       </c>
-      <c r="H23" s="1" t="str" cm="1">
-        <f t="array" ref="H23">_xlfn.IFS(Predictions!L25=1,$C23,Predictions!L25="X","Draw",Predictions!L25=2,$D23)</f>
+      <c r="J23" s="1" t="str" cm="1">
+        <f t="array" ref="J23">_xlfn.IFS(Predictions!L25=1,$E23,Predictions!L25="X","Draw",Predictions!L25=2,$F23)</f>
         <v>Draw</v>
       </c>
-      <c r="I23" s="1" t="str" cm="1">
-        <f t="array" ref="I23">_xlfn.IFS(Predictions!N25=1,$C23,Predictions!N25="X","Draw",Predictions!N25=2,$D23)</f>
+      <c r="K23" s="1" t="str" cm="1">
+        <f t="array" ref="K23">_xlfn.IFS(Predictions!N25=1,$E23,Predictions!N25="X","Draw",Predictions!N25=2,$F23)</f>
         <v>England</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="26">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="164">
         <v>46191</v>
       </c>
-      <c r="B24" s="45" t="s">
+      <c r="B24" s="163">
+        <v>0</v>
+      </c>
+      <c r="C24" s="163"/>
+      <c r="D24" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="E24" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="F24" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="1" t="str" cm="1">
-        <f t="array" ref="E24">_xlfn.IFS(Predictions!F26=1,$C24,Predictions!F26="X","Draw",Predictions!F26=2,$D24)</f>
+      <c r="G24" s="1" t="str" cm="1">
+        <f t="array" ref="G24">_xlfn.IFS(Predictions!F26=1,$E24,Predictions!F26="X","Draw",Predictions!F26=2,$F24)</f>
         <v>Colombia</v>
       </c>
-      <c r="F24" s="1" t="str" cm="1">
-        <f t="array" ref="F24">_xlfn.IFS(Predictions!H26=1,$C24,Predictions!H26="X","Draw",Predictions!H26=2,$D24)</f>
+      <c r="H24" s="1" t="str" cm="1">
+        <f t="array" ref="H24">_xlfn.IFS(Predictions!H26=1,$E24,Predictions!H26="X","Draw",Predictions!H26=2,$F24)</f>
         <v>Colombia</v>
       </c>
-      <c r="G24" s="1" t="str" cm="1">
-        <f t="array" ref="G24">_xlfn.IFS(Predictions!J26=1,$C24,Predictions!J26="X","Draw",Predictions!J26=2,$D24)</f>
+      <c r="I24" s="1" t="str" cm="1">
+        <f t="array" ref="I24">_xlfn.IFS(Predictions!J26=1,$E24,Predictions!J26="X","Draw",Predictions!J26=2,$F24)</f>
         <v>Colombia</v>
       </c>
-      <c r="H24" s="1" t="str" cm="1">
-        <f t="array" ref="H24">_xlfn.IFS(Predictions!L26=1,$C24,Predictions!L26="X","Draw",Predictions!L26=2,$D24)</f>
+      <c r="J24" s="1" t="str" cm="1">
+        <f t="array" ref="J24">_xlfn.IFS(Predictions!L26=1,$E24,Predictions!L26="X","Draw",Predictions!L26=2,$F24)</f>
         <v>Colombia</v>
       </c>
-      <c r="I24" s="1" t="str" cm="1">
-        <f t="array" ref="I24">_xlfn.IFS(Predictions!N26=1,$C24,Predictions!N26="X","Draw",Predictions!N26=2,$D24)</f>
+      <c r="K24" s="1" t="str" cm="1">
+        <f t="array" ref="K24">_xlfn.IFS(Predictions!N26=1,$E24,Predictions!N26="X","Draw",Predictions!N26=2,$F24)</f>
         <v>Colombia</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="26">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="164">
         <v>46191</v>
       </c>
-      <c r="B25" s="47" t="s">
+      <c r="B25" s="163">
+        <v>0.125</v>
+      </c>
+      <c r="C25" s="163"/>
+      <c r="D25" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="E25" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="F25" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="1" t="str" cm="1">
-        <f t="array" ref="E25">_xlfn.IFS(Predictions!F27=1,$C25,Predictions!F27="X","Draw",Predictions!F27=2,$D25)</f>
+      <c r="G25" s="1" t="str" cm="1">
+        <f t="array" ref="G25">_xlfn.IFS(Predictions!F27=1,$E25,Predictions!F27="X","Draw",Predictions!F27=2,$F25)</f>
         <v>Ghana</v>
       </c>
-      <c r="F25" s="1" t="str" cm="1">
-        <f t="array" ref="F25">_xlfn.IFS(Predictions!H27=1,$C25,Predictions!H27="X","Draw",Predictions!H27=2,$D25)</f>
+      <c r="H25" s="1" t="str" cm="1">
+        <f t="array" ref="H25">_xlfn.IFS(Predictions!H27=1,$E25,Predictions!H27="X","Draw",Predictions!H27=2,$F25)</f>
         <v>Ghana</v>
       </c>
-      <c r="G25" s="1" t="str" cm="1">
-        <f t="array" ref="G25">_xlfn.IFS(Predictions!J27=1,$C25,Predictions!J27="X","Draw",Predictions!J27=2,$D25)</f>
+      <c r="I25" s="1" t="str" cm="1">
+        <f t="array" ref="I25">_xlfn.IFS(Predictions!J27=1,$E25,Predictions!J27="X","Draw",Predictions!J27=2,$F25)</f>
         <v>Draw</v>
       </c>
-      <c r="H25" s="1" t="str" cm="1">
-        <f t="array" ref="H25">_xlfn.IFS(Predictions!L27=1,$C25,Predictions!L27="X","Draw",Predictions!L27=2,$D25)</f>
+      <c r="J25" s="1" t="str" cm="1">
+        <f t="array" ref="J25">_xlfn.IFS(Predictions!L27=1,$E25,Predictions!L27="X","Draw",Predictions!L27=2,$F25)</f>
         <v>Draw</v>
       </c>
-      <c r="I25" s="1" t="str" cm="1">
-        <f t="array" ref="I25">_xlfn.IFS(Predictions!N27=1,$C25,Predictions!N27="X","Draw",Predictions!N27=2,$D25)</f>
+      <c r="K25" s="1" t="str" cm="1">
+        <f t="array" ref="K25">_xlfn.IFS(Predictions!N27=1,$E25,Predictions!N27="X","Draw",Predictions!N27=2,$F25)</f>
         <v>Ghana</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="26">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="164">
         <v>46191</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="163">
+        <v>0.75</v>
+      </c>
+      <c r="C26" s="163"/>
+      <c r="D26" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="E26" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="28" t="s">
+      <c r="F26" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="E26" s="1" t="str" cm="1">
-        <f t="array" ref="E26">_xlfn.IFS(Predictions!F28=1,$C26,Predictions!F28="X","Draw",Predictions!F28=2,$D26)</f>
+      <c r="G26" s="1" t="str" cm="1">
+        <f t="array" ref="G26">_xlfn.IFS(Predictions!F28=1,$E26,Predictions!F28="X","Draw",Predictions!F28=2,$F26)</f>
         <v>Draw</v>
       </c>
-      <c r="F26" s="1" t="str" cm="1">
-        <f t="array" ref="F26">_xlfn.IFS(Predictions!H28=1,$C26,Predictions!H28="X","Draw",Predictions!H28=2,$D26)</f>
+      <c r="H26" s="1" t="str" cm="1">
+        <f t="array" ref="H26">_xlfn.IFS(Predictions!H28=1,$E26,Predictions!H28="X","Draw",Predictions!H28=2,$F26)</f>
         <v>Czechia</v>
       </c>
-      <c r="G26" s="1" t="str" cm="1">
-        <f t="array" ref="G26">_xlfn.IFS(Predictions!J28=1,$C26,Predictions!J28="X","Draw",Predictions!J28=2,$D26)</f>
+      <c r="I26" s="1" t="str" cm="1">
+        <f t="array" ref="I26">_xlfn.IFS(Predictions!J28=1,$E26,Predictions!J28="X","Draw",Predictions!J28=2,$F26)</f>
         <v>Czechia</v>
       </c>
-      <c r="H26" s="1" t="str" cm="1">
-        <f t="array" ref="H26">_xlfn.IFS(Predictions!L28=1,$C26,Predictions!L28="X","Draw",Predictions!L28=2,$D26)</f>
+      <c r="J26" s="1" t="str" cm="1">
+        <f t="array" ref="J26">_xlfn.IFS(Predictions!L28=1,$E26,Predictions!L28="X","Draw",Predictions!L28=2,$F26)</f>
         <v>Czechia</v>
       </c>
-      <c r="I26" s="1" t="str" cm="1">
-        <f t="array" ref="I26">_xlfn.IFS(Predictions!N28=1,$C26,Predictions!N28="X","Draw",Predictions!N28=2,$D26)</f>
+      <c r="K26" s="1" t="str" cm="1">
+        <f t="array" ref="K26">_xlfn.IFS(Predictions!N28=1,$E26,Predictions!N28="X","Draw",Predictions!N28=2,$F26)</f>
         <v>Czechia</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="26">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="164">
         <v>46191</v>
       </c>
-      <c r="B27" s="33" t="s">
+      <c r="B27" s="163">
+        <v>0.875</v>
+      </c>
+      <c r="C27" s="163"/>
+      <c r="D27" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="E27" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="F27" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="1" t="str" cm="1">
-        <f t="array" ref="E27">_xlfn.IFS(Predictions!F29=1,$C27,Predictions!F29="X","Draw",Predictions!F29=2,$D27)</f>
+      <c r="G27" s="1" t="str" cm="1">
+        <f t="array" ref="G27">_xlfn.IFS(Predictions!F29=1,$E27,Predictions!F29="X","Draw",Predictions!F29=2,$F27)</f>
         <v>Switzerland</v>
       </c>
-      <c r="F27" s="1" t="str" cm="1">
-        <f t="array" ref="F27">_xlfn.IFS(Predictions!H29=1,$C27,Predictions!H29="X","Draw",Predictions!H29=2,$D27)</f>
+      <c r="H27" s="1" t="str" cm="1">
+        <f t="array" ref="H27">_xlfn.IFS(Predictions!H29=1,$E27,Predictions!H29="X","Draw",Predictions!H29=2,$F27)</f>
         <v>Switzerland</v>
       </c>
-      <c r="G27" s="1" t="str" cm="1">
-        <f t="array" ref="G27">_xlfn.IFS(Predictions!J29=1,$C27,Predictions!J29="X","Draw",Predictions!J29=2,$D27)</f>
+      <c r="I27" s="1" t="str" cm="1">
+        <f t="array" ref="I27">_xlfn.IFS(Predictions!J29=1,$E27,Predictions!J29="X","Draw",Predictions!J29=2,$F27)</f>
         <v>Switzerland</v>
       </c>
-      <c r="H27" s="1" t="str" cm="1">
-        <f t="array" ref="H27">_xlfn.IFS(Predictions!L29=1,$C27,Predictions!L29="X","Draw",Predictions!L29=2,$D27)</f>
+      <c r="J27" s="1" t="str" cm="1">
+        <f t="array" ref="J27">_xlfn.IFS(Predictions!L29=1,$E27,Predictions!L29="X","Draw",Predictions!L29=2,$F27)</f>
         <v>Switzerland</v>
       </c>
-      <c r="I27" s="1" t="str" cm="1">
-        <f t="array" ref="I27">_xlfn.IFS(Predictions!N29=1,$C27,Predictions!N29="X","Draw",Predictions!N29=2,$D27)</f>
+      <c r="K27" s="1" t="str" cm="1">
+        <f t="array" ref="K27">_xlfn.IFS(Predictions!N29=1,$E27,Predictions!N29="X","Draw",Predictions!N29=2,$F27)</f>
         <v>Switzerland</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="29">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="164">
         <v>46191</v>
       </c>
-      <c r="B28" s="30" t="s">
+      <c r="B28" s="162">
+        <v>0</v>
+      </c>
+      <c r="C28" s="162"/>
+      <c r="D28" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="31" t="s">
+      <c r="E28" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D28" s="31" t="s">
+      <c r="F28" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="1" t="str" cm="1">
-        <f t="array" ref="E28">_xlfn.IFS(Predictions!F30=1,$C28,Predictions!F30="X","Draw",Predictions!F30=2,$D28)</f>
+      <c r="G28" s="1" t="str" cm="1">
+        <f t="array" ref="G28">_xlfn.IFS(Predictions!F30=1,$E28,Predictions!F30="X","Draw",Predictions!F30=2,$F28)</f>
         <v>Canada</v>
       </c>
-      <c r="F28" s="1" t="str" cm="1">
-        <f t="array" ref="F28">_xlfn.IFS(Predictions!H30=1,$C28,Predictions!H30="X","Draw",Predictions!H30=2,$D28)</f>
+      <c r="H28" s="1" t="str" cm="1">
+        <f t="array" ref="H28">_xlfn.IFS(Predictions!H30=1,$E28,Predictions!H30="X","Draw",Predictions!H30=2,$F28)</f>
         <v>Canada</v>
       </c>
-      <c r="G28" s="1" t="str" cm="1">
-        <f t="array" ref="G28">_xlfn.IFS(Predictions!J30=1,$C28,Predictions!J30="X","Draw",Predictions!J30=2,$D28)</f>
+      <c r="I28" s="1" t="str" cm="1">
+        <f t="array" ref="I28">_xlfn.IFS(Predictions!J30=1,$E28,Predictions!J30="X","Draw",Predictions!J30=2,$F28)</f>
         <v>Canada</v>
       </c>
-      <c r="H28" s="1" t="str" cm="1">
-        <f t="array" ref="H28">_xlfn.IFS(Predictions!L30=1,$C28,Predictions!L30="X","Draw",Predictions!L30=2,$D28)</f>
+      <c r="J28" s="1" t="str" cm="1">
+        <f t="array" ref="J28">_xlfn.IFS(Predictions!L30=1,$E28,Predictions!L30="X","Draw",Predictions!L30=2,$F28)</f>
         <v>Canada</v>
       </c>
-      <c r="I28" s="1" t="str" cm="1">
-        <f t="array" ref="I28">_xlfn.IFS(Predictions!N30=1,$C28,Predictions!N30="X","Draw",Predictions!N30=2,$D28)</f>
+      <c r="K28" s="1" t="str" cm="1">
+        <f t="array" ref="K28">_xlfn.IFS(Predictions!N30=1,$E28,Predictions!N30="X","Draw",Predictions!N30=2,$F28)</f>
         <v>Canada</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="26">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="164">
         <v>46192</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="163">
+        <v>0.125</v>
+      </c>
+      <c r="C29" s="163"/>
+      <c r="D29" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="E29" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="28" t="s">
+      <c r="F29" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="1" t="str" cm="1">
-        <f t="array" ref="E29">_xlfn.IFS(Predictions!F31=1,$C29,Predictions!F31="X","Draw",Predictions!F31=2,$D29)</f>
+      <c r="G29" s="1" t="str" cm="1">
+        <f t="array" ref="G29">_xlfn.IFS(Predictions!F31=1,$E29,Predictions!F31="X","Draw",Predictions!F31=2,$F29)</f>
         <v>Mexico</v>
       </c>
-      <c r="F29" s="1" t="str" cm="1">
-        <f t="array" ref="F29">_xlfn.IFS(Predictions!H31=1,$C29,Predictions!H31="X","Draw",Predictions!H31=2,$D29)</f>
+      <c r="H29" s="1" t="str" cm="1">
+        <f t="array" ref="H29">_xlfn.IFS(Predictions!H31=1,$E29,Predictions!H31="X","Draw",Predictions!H31=2,$F29)</f>
         <v>Mexico</v>
       </c>
-      <c r="G29" s="1" t="str" cm="1">
-        <f t="array" ref="G29">_xlfn.IFS(Predictions!J31=1,$C29,Predictions!J31="X","Draw",Predictions!J31=2,$D29)</f>
+      <c r="I29" s="1" t="str" cm="1">
+        <f t="array" ref="I29">_xlfn.IFS(Predictions!J31=1,$E29,Predictions!J31="X","Draw",Predictions!J31=2,$F29)</f>
         <v>Draw</v>
       </c>
-      <c r="H29" s="1" t="str" cm="1">
-        <f t="array" ref="H29">_xlfn.IFS(Predictions!L31=1,$C29,Predictions!L31="X","Draw",Predictions!L31=2,$D29)</f>
+      <c r="J29" s="1" t="str" cm="1">
+        <f t="array" ref="J29">_xlfn.IFS(Predictions!L31=1,$E29,Predictions!L31="X","Draw",Predictions!L31=2,$F29)</f>
         <v>Mexico</v>
       </c>
-      <c r="I29" s="1" t="str" cm="1">
-        <f t="array" ref="I29">_xlfn.IFS(Predictions!N31=1,$C29,Predictions!N31="X","Draw",Predictions!N31=2,$D29)</f>
+      <c r="K29" s="1" t="str" cm="1">
+        <f t="array" ref="K29">_xlfn.IFS(Predictions!N31=1,$E29,Predictions!N31="X","Draw",Predictions!N31=2,$F29)</f>
         <v>Mexico</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="26">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="164">
         <v>46192</v>
       </c>
-      <c r="B30" s="35" t="s">
+      <c r="B30" s="163">
+        <v>0.75</v>
+      </c>
+      <c r="C30" s="163"/>
+      <c r="D30" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="E30" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="F30" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="1" t="str" cm="1">
-        <f t="array" ref="E30">_xlfn.IFS(Predictions!F32=1,$C30,Predictions!F32="X","Draw",Predictions!F32=2,$D30)</f>
+      <c r="G30" s="1" t="str" cm="1">
+        <f t="array" ref="G30">_xlfn.IFS(Predictions!F32=1,$E30,Predictions!F32="X","Draw",Predictions!F32=2,$F30)</f>
         <v>Draw</v>
       </c>
-      <c r="F30" s="1" t="str" cm="1">
-        <f t="array" ref="F30">_xlfn.IFS(Predictions!H32=1,$C30,Predictions!H32="X","Draw",Predictions!H32=2,$D30)</f>
+      <c r="H30" s="1" t="str" cm="1">
+        <f t="array" ref="H30">_xlfn.IFS(Predictions!H32=1,$E30,Predictions!H32="X","Draw",Predictions!H32=2,$F30)</f>
         <v>Morocco</v>
       </c>
-      <c r="G30" s="1" t="str" cm="1">
-        <f t="array" ref="G30">_xlfn.IFS(Predictions!J32=1,$C30,Predictions!J32="X","Draw",Predictions!J32=2,$D30)</f>
+      <c r="I30" s="1" t="str" cm="1">
+        <f t="array" ref="I30">_xlfn.IFS(Predictions!J32=1,$E30,Predictions!J32="X","Draw",Predictions!J32=2,$F30)</f>
         <v>Morocco</v>
       </c>
-      <c r="H30" s="1" t="str" cm="1">
-        <f t="array" ref="H30">_xlfn.IFS(Predictions!L32=1,$C30,Predictions!L32="X","Draw",Predictions!L32=2,$D30)</f>
+      <c r="J30" s="1" t="str" cm="1">
+        <f t="array" ref="J30">_xlfn.IFS(Predictions!L32=1,$E30,Predictions!L32="X","Draw",Predictions!L32=2,$F30)</f>
         <v>Morocco</v>
       </c>
-      <c r="I30" s="1" t="str" cm="1">
-        <f t="array" ref="I30">_xlfn.IFS(Predictions!N32=1,$C30,Predictions!N32="X","Draw",Predictions!N32=2,$D30)</f>
+      <c r="K30" s="1" t="str" cm="1">
+        <f t="array" ref="K30">_xlfn.IFS(Predictions!N32=1,$E30,Predictions!N32="X","Draw",Predictions!N32=2,$F30)</f>
         <v>Morocco</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="29">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="164">
         <v>46192</v>
       </c>
-      <c r="B31" s="48" t="s">
+      <c r="B31" s="162">
+        <v>0.875</v>
+      </c>
+      <c r="C31" s="162"/>
+      <c r="D31" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="31" t="s">
+      <c r="E31" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="31" t="s">
+      <c r="F31" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="1" t="str" cm="1">
-        <f t="array" ref="E31">_xlfn.IFS(Predictions!F33=1,$C31,Predictions!F33="X","Draw",Predictions!F33=2,$D31)</f>
+      <c r="G31" s="1" t="str" cm="1">
+        <f t="array" ref="G31">_xlfn.IFS(Predictions!F33=1,$E31,Predictions!F33="X","Draw",Predictions!F33=2,$F31)</f>
         <v>Draw</v>
       </c>
-      <c r="F31" s="1" t="str" cm="1">
-        <f t="array" ref="F31">_xlfn.IFS(Predictions!H33=1,$C31,Predictions!H33="X","Draw",Predictions!H33=2,$D31)</f>
+      <c r="H31" s="1" t="str" cm="1">
+        <f t="array" ref="H31">_xlfn.IFS(Predictions!H33=1,$E31,Predictions!H33="X","Draw",Predictions!H33=2,$F31)</f>
         <v>USA</v>
       </c>
-      <c r="G31" s="1" t="str" cm="1">
-        <f t="array" ref="G31">_xlfn.IFS(Predictions!J33=1,$C31,Predictions!J33="X","Draw",Predictions!J33=2,$D31)</f>
+      <c r="I31" s="1" t="str" cm="1">
+        <f t="array" ref="I31">_xlfn.IFS(Predictions!J33=1,$E31,Predictions!J33="X","Draw",Predictions!J33=2,$F31)</f>
         <v>Draw</v>
       </c>
-      <c r="H31" s="1" t="str" cm="1">
-        <f t="array" ref="H31">_xlfn.IFS(Predictions!L33=1,$C31,Predictions!L33="X","Draw",Predictions!L33=2,$D31)</f>
+      <c r="J31" s="1" t="str" cm="1">
+        <f t="array" ref="J31">_xlfn.IFS(Predictions!L33=1,$E31,Predictions!L33="X","Draw",Predictions!L33=2,$F31)</f>
         <v>USA</v>
       </c>
-      <c r="I31" s="1" t="str" cm="1">
-        <f t="array" ref="I31">_xlfn.IFS(Predictions!N33=1,$C31,Predictions!N33="X","Draw",Predictions!N33=2,$D31)</f>
+      <c r="K31" s="1" t="str" cm="1">
+        <f t="array" ref="K31">_xlfn.IFS(Predictions!N33=1,$E31,Predictions!N33="X","Draw",Predictions!N33=2,$F31)</f>
         <v>USA</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="26">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="164">
         <v>46193</v>
       </c>
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="163">
+        <v>0</v>
+      </c>
+      <c r="C32" s="163"/>
+      <c r="D32" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="E32" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D32" s="28" t="s">
+      <c r="F32" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="1" t="str" cm="1">
-        <f t="array" ref="E32">_xlfn.IFS(Predictions!F34=1,$C32,Predictions!F34="X","Draw",Predictions!F34=2,$D32)</f>
+      <c r="G32" s="1" t="str" cm="1">
+        <f t="array" ref="G32">_xlfn.IFS(Predictions!F34=1,$E32,Predictions!F34="X","Draw",Predictions!F34=2,$F32)</f>
         <v>Brazil</v>
       </c>
-      <c r="F32" s="1" t="str" cm="1">
-        <f t="array" ref="F32">_xlfn.IFS(Predictions!H34=1,$C32,Predictions!H34="X","Draw",Predictions!H34=2,$D32)</f>
+      <c r="H32" s="1" t="str" cm="1">
+        <f t="array" ref="H32">_xlfn.IFS(Predictions!H34=1,$E32,Predictions!H34="X","Draw",Predictions!H34=2,$F32)</f>
         <v>Brazil</v>
       </c>
-      <c r="G32" s="1" t="str" cm="1">
-        <f t="array" ref="G32">_xlfn.IFS(Predictions!J34=1,$C32,Predictions!J34="X","Draw",Predictions!J34=2,$D32)</f>
+      <c r="I32" s="1" t="str" cm="1">
+        <f t="array" ref="I32">_xlfn.IFS(Predictions!J34=1,$E32,Predictions!J34="X","Draw",Predictions!J34=2,$F32)</f>
         <v>Brazil</v>
       </c>
-      <c r="H32" s="1" t="str" cm="1">
-        <f t="array" ref="H32">_xlfn.IFS(Predictions!L34=1,$C32,Predictions!L34="X","Draw",Predictions!L34=2,$D32)</f>
+      <c r="J32" s="1" t="str" cm="1">
+        <f t="array" ref="J32">_xlfn.IFS(Predictions!L34=1,$E32,Predictions!L34="X","Draw",Predictions!L34=2,$F32)</f>
         <v>Brazil</v>
       </c>
-      <c r="I32" s="1" t="str" cm="1">
-        <f t="array" ref="I32">_xlfn.IFS(Predictions!N34=1,$C32,Predictions!N34="X","Draw",Predictions!N34=2,$D32)</f>
+      <c r="K32" s="1" t="str" cm="1">
+        <f t="array" ref="K32">_xlfn.IFS(Predictions!N34=1,$E32,Predictions!N34="X","Draw",Predictions!N34=2,$F32)</f>
         <v>Brazil</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="26">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="164">
         <v>46193</v>
       </c>
-      <c r="B33" s="32" t="s">
+      <c r="B33" s="163">
+        <v>0.125</v>
+      </c>
+      <c r="C33" s="163"/>
+      <c r="D33" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="E33" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="F33" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="E33" s="1" t="str" cm="1">
-        <f t="array" ref="E33">_xlfn.IFS(Predictions!F35=1,$C33,Predictions!F35="X","Draw",Predictions!F35=2,$D33)</f>
+      <c r="G33" s="1" t="str" cm="1">
+        <f t="array" ref="G33">_xlfn.IFS(Predictions!F35=1,$E33,Predictions!F35="X","Draw",Predictions!F35=2,$F33)</f>
         <v>Türkiye</v>
       </c>
-      <c r="F33" s="1" t="str" cm="1">
-        <f t="array" ref="F33">_xlfn.IFS(Predictions!H35=1,$C33,Predictions!H35="X","Draw",Predictions!H35=2,$D33)</f>
+      <c r="H33" s="1" t="str" cm="1">
+        <f t="array" ref="H33">_xlfn.IFS(Predictions!H35=1,$E33,Predictions!H35="X","Draw",Predictions!H35=2,$F33)</f>
         <v>Draw</v>
       </c>
-      <c r="G33" s="1" t="str" cm="1">
-        <f t="array" ref="G33">_xlfn.IFS(Predictions!J35=1,$C33,Predictions!J35="X","Draw",Predictions!J35=2,$D33)</f>
+      <c r="I33" s="1" t="str" cm="1">
+        <f t="array" ref="I33">_xlfn.IFS(Predictions!J35=1,$E33,Predictions!J35="X","Draw",Predictions!J35=2,$F33)</f>
         <v>Türkiye</v>
       </c>
-      <c r="H33" s="1" t="str" cm="1">
-        <f t="array" ref="H33">_xlfn.IFS(Predictions!L35=1,$C33,Predictions!L35="X","Draw",Predictions!L35=2,$D33)</f>
+      <c r="J33" s="1" t="str" cm="1">
+        <f t="array" ref="J33">_xlfn.IFS(Predictions!L35=1,$E33,Predictions!L35="X","Draw",Predictions!L35=2,$F33)</f>
         <v>Türkiye</v>
       </c>
-      <c r="I33" s="1" t="str" cm="1">
-        <f t="array" ref="I33">_xlfn.IFS(Predictions!N35=1,$C33,Predictions!N35="X","Draw",Predictions!N35=2,$D33)</f>
+      <c r="K33" s="1" t="str" cm="1">
+        <f t="array" ref="K33">_xlfn.IFS(Predictions!N35=1,$E33,Predictions!N35="X","Draw",Predictions!N35=2,$F33)</f>
         <v>Türkiye</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="26">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="164">
         <v>46193</v>
       </c>
-      <c r="B34" s="36" t="s">
+      <c r="B34" s="163">
+        <v>0.75</v>
+      </c>
+      <c r="C34" s="163"/>
+      <c r="D34" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="E34" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="D34" s="28" t="s">
+      <c r="F34" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="E34" s="1" t="str" cm="1">
-        <f t="array" ref="E34">_xlfn.IFS(Predictions!F36=1,$C34,Predictions!F36="X","Draw",Predictions!F36=2,$D34)</f>
+      <c r="G34" s="1" t="str" cm="1">
+        <f t="array" ref="G34">_xlfn.IFS(Predictions!F36=1,$E34,Predictions!F36="X","Draw",Predictions!F36=2,$F34)</f>
         <v>Germany</v>
       </c>
-      <c r="F34" s="1" t="str" cm="1">
-        <f t="array" ref="F34">_xlfn.IFS(Predictions!H36=1,$C34,Predictions!H36="X","Draw",Predictions!H36=2,$D34)</f>
+      <c r="H34" s="1" t="str" cm="1">
+        <f t="array" ref="H34">_xlfn.IFS(Predictions!H36=1,$E34,Predictions!H36="X","Draw",Predictions!H36=2,$F34)</f>
         <v>Germany</v>
       </c>
-      <c r="G34" s="1" t="str" cm="1">
-        <f t="array" ref="G34">_xlfn.IFS(Predictions!J36=1,$C34,Predictions!J36="X","Draw",Predictions!J36=2,$D34)</f>
+      <c r="I34" s="1" t="str" cm="1">
+        <f t="array" ref="I34">_xlfn.IFS(Predictions!J36=1,$E34,Predictions!J36="X","Draw",Predictions!J36=2,$F34)</f>
         <v>Germany</v>
       </c>
-      <c r="H34" s="1" t="str" cm="1">
-        <f t="array" ref="H34">_xlfn.IFS(Predictions!L36=1,$C34,Predictions!L36="X","Draw",Predictions!L36=2,$D34)</f>
+      <c r="J34" s="1" t="str" cm="1">
+        <f t="array" ref="J34">_xlfn.IFS(Predictions!L36=1,$E34,Predictions!L36="X","Draw",Predictions!L36=2,$F34)</f>
         <v>Germany</v>
       </c>
-      <c r="I34" s="1" t="str" cm="1">
-        <f t="array" ref="I34">_xlfn.IFS(Predictions!N36=1,$C34,Predictions!N36="X","Draw",Predictions!N36=2,$D34)</f>
+      <c r="K34" s="1" t="str" cm="1">
+        <f t="array" ref="K34">_xlfn.IFS(Predictions!N36=1,$E34,Predictions!N36="X","Draw",Predictions!N36=2,$F34)</f>
         <v>Germany</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="29">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="164">
         <v>46193</v>
       </c>
-      <c r="B35" s="37" t="s">
+      <c r="B35" s="162">
+        <v>0.875</v>
+      </c>
+      <c r="C35" s="162"/>
+      <c r="D35" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="31" t="s">
+      <c r="E35" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D35" s="31" t="s">
+      <c r="F35" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="E35" s="1" t="str" cm="1">
-        <f t="array" ref="E35">_xlfn.IFS(Predictions!F37=1,$C35,Predictions!F37="X","Draw",Predictions!F37=2,$D35)</f>
+      <c r="G35" s="1" t="str" cm="1">
+        <f t="array" ref="G35">_xlfn.IFS(Predictions!F37=1,$E35,Predictions!F37="X","Draw",Predictions!F37=2,$F35)</f>
         <v>Netherlands</v>
       </c>
-      <c r="F35" s="1" t="str" cm="1">
-        <f t="array" ref="F35">_xlfn.IFS(Predictions!H37=1,$C35,Predictions!H37="X","Draw",Predictions!H37=2,$D35)</f>
+      <c r="H35" s="1" t="str" cm="1">
+        <f t="array" ref="H35">_xlfn.IFS(Predictions!H37=1,$E35,Predictions!H37="X","Draw",Predictions!H37=2,$F35)</f>
         <v>Netherlands</v>
       </c>
-      <c r="G35" s="1" t="str" cm="1">
-        <f t="array" ref="G35">_xlfn.IFS(Predictions!J37=1,$C35,Predictions!J37="X","Draw",Predictions!J37=2,$D35)</f>
+      <c r="I35" s="1" t="str" cm="1">
+        <f t="array" ref="I35">_xlfn.IFS(Predictions!J37=1,$E35,Predictions!J37="X","Draw",Predictions!J37=2,$F35)</f>
         <v>Netherlands</v>
       </c>
-      <c r="H35" s="1" t="str" cm="1">
-        <f t="array" ref="H35">_xlfn.IFS(Predictions!L37=1,$C35,Predictions!L37="X","Draw",Predictions!L37=2,$D35)</f>
+      <c r="J35" s="1" t="str" cm="1">
+        <f t="array" ref="J35">_xlfn.IFS(Predictions!L37=1,$E35,Predictions!L37="X","Draw",Predictions!L37=2,$F35)</f>
         <v>Netherlands</v>
       </c>
-      <c r="I35" s="1" t="str" cm="1">
-        <f t="array" ref="I35">_xlfn.IFS(Predictions!N37=1,$C35,Predictions!N37="X","Draw",Predictions!N37=2,$D35)</f>
+      <c r="K35" s="1" t="str" cm="1">
+        <f t="array" ref="K35">_xlfn.IFS(Predictions!N37=1,$E35,Predictions!N37="X","Draw",Predictions!N37=2,$F35)</f>
         <v>Netherlands</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="26">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="164">
         <v>46194</v>
       </c>
-      <c r="B36" s="36" t="s">
+      <c r="B36" s="163">
+        <v>0</v>
+      </c>
+      <c r="C36" s="163"/>
+      <c r="D36" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C36" s="28" t="s">
+      <c r="E36" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="28" t="s">
+      <c r="F36" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="E36" s="1" t="str" cm="1">
-        <f t="array" ref="E36">_xlfn.IFS(Predictions!F38=1,$C36,Predictions!F38="X","Draw",Predictions!F38=2,$D36)</f>
+      <c r="G36" s="1" t="str" cm="1">
+        <f t="array" ref="G36">_xlfn.IFS(Predictions!F38=1,$E36,Predictions!F38="X","Draw",Predictions!F38=2,$F36)</f>
         <v>Draw</v>
       </c>
-      <c r="F36" s="1" t="str" cm="1">
-        <f t="array" ref="F36">_xlfn.IFS(Predictions!H38=1,$C36,Predictions!H38="X","Draw",Predictions!H38=2,$D36)</f>
+      <c r="H36" s="1" t="str" cm="1">
+        <f t="array" ref="H36">_xlfn.IFS(Predictions!H38=1,$E36,Predictions!H38="X","Draw",Predictions!H38=2,$F36)</f>
         <v>Ecuador</v>
       </c>
-      <c r="G36" s="1" t="str" cm="1">
-        <f t="array" ref="G36">_xlfn.IFS(Predictions!J38=1,$C36,Predictions!J38="X","Draw",Predictions!J38=2,$D36)</f>
+      <c r="I36" s="1" t="str" cm="1">
+        <f t="array" ref="I36">_xlfn.IFS(Predictions!J38=1,$E36,Predictions!J38="X","Draw",Predictions!J38=2,$F36)</f>
         <v>Ecuador</v>
       </c>
-      <c r="H36" s="1" t="str" cm="1">
-        <f t="array" ref="H36">_xlfn.IFS(Predictions!L38=1,$C36,Predictions!L38="X","Draw",Predictions!L38=2,$D36)</f>
+      <c r="J36" s="1" t="str" cm="1">
+        <f t="array" ref="J36">_xlfn.IFS(Predictions!L38=1,$E36,Predictions!L38="X","Draw",Predictions!L38=2,$F36)</f>
         <v>Ecuador</v>
       </c>
-      <c r="I36" s="1" t="str" cm="1">
-        <f t="array" ref="I36">_xlfn.IFS(Predictions!N38=1,$C36,Predictions!N38="X","Draw",Predictions!N38=2,$D36)</f>
+      <c r="K36" s="1" t="str" cm="1">
+        <f t="array" ref="K36">_xlfn.IFS(Predictions!N38=1,$E36,Predictions!N38="X","Draw",Predictions!N38=2,$F36)</f>
         <v>Ecuador</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="26">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="164">
         <v>46194</v>
       </c>
-      <c r="B37" s="38" t="s">
+      <c r="B37" s="163">
+        <v>0.125</v>
+      </c>
+      <c r="C37" s="163"/>
+      <c r="D37" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="28" t="s">
+      <c r="E37" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="F37" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E37" s="1" t="str" cm="1">
-        <f t="array" ref="E37">_xlfn.IFS(Predictions!F39=1,$C37,Predictions!F39="X","Draw",Predictions!F39=2,$D37)</f>
+      <c r="G37" s="1" t="str" cm="1">
+        <f t="array" ref="G37">_xlfn.IFS(Predictions!F39=1,$E37,Predictions!F39="X","Draw",Predictions!F39=2,$F37)</f>
         <v>Japan</v>
       </c>
-      <c r="F37" s="1" t="str" cm="1">
-        <f t="array" ref="F37">_xlfn.IFS(Predictions!H39=1,$C37,Predictions!H39="X","Draw",Predictions!H39=2,$D37)</f>
+      <c r="H37" s="1" t="str" cm="1">
+        <f t="array" ref="H37">_xlfn.IFS(Predictions!H39=1,$E37,Predictions!H39="X","Draw",Predictions!H39=2,$F37)</f>
         <v>Japan</v>
       </c>
-      <c r="G37" s="1" t="str" cm="1">
-        <f t="array" ref="G37">_xlfn.IFS(Predictions!J39=1,$C37,Predictions!J39="X","Draw",Predictions!J39=2,$D37)</f>
+      <c r="I37" s="1" t="str" cm="1">
+        <f t="array" ref="I37">_xlfn.IFS(Predictions!J39=1,$E37,Predictions!J39="X","Draw",Predictions!J39=2,$F37)</f>
         <v>Japan</v>
       </c>
-      <c r="H37" s="1" t="str" cm="1">
-        <f t="array" ref="H37">_xlfn.IFS(Predictions!L39=1,$C37,Predictions!L39="X","Draw",Predictions!L39=2,$D37)</f>
+      <c r="J37" s="1" t="str" cm="1">
+        <f t="array" ref="J37">_xlfn.IFS(Predictions!L39=1,$E37,Predictions!L39="X","Draw",Predictions!L39=2,$F37)</f>
         <v>Japan</v>
       </c>
-      <c r="I37" s="1" t="str" cm="1">
-        <f t="array" ref="I37">_xlfn.IFS(Predictions!N39=1,$C37,Predictions!N39="X","Draw",Predictions!N39=2,$D37)</f>
+      <c r="K37" s="1" t="str" cm="1">
+        <f t="array" ref="K37">_xlfn.IFS(Predictions!N39=1,$E37,Predictions!N39="X","Draw",Predictions!N39=2,$F37)</f>
         <v>Japan</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="26">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="164">
         <v>46194</v>
       </c>
-      <c r="B38" s="39" t="s">
+      <c r="B38" s="163">
+        <v>0.75</v>
+      </c>
+      <c r="C38" s="163"/>
+      <c r="D38" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="C38" s="28" t="s">
+      <c r="E38" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="28" t="s">
+      <c r="F38" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="1" t="str" cm="1">
-        <f t="array" ref="E38">_xlfn.IFS(Predictions!F40=1,$C38,Predictions!F40="X","Draw",Predictions!F40=2,$D38)</f>
+      <c r="G38" s="1" t="str" cm="1">
+        <f t="array" ref="G38">_xlfn.IFS(Predictions!F40=1,$E38,Predictions!F40="X","Draw",Predictions!F40=2,$F38)</f>
         <v>Draw</v>
       </c>
-      <c r="F38" s="1" t="str" cm="1">
-        <f t="array" ref="F38">_xlfn.IFS(Predictions!H40=1,$C38,Predictions!H40="X","Draw",Predictions!H40=2,$D38)</f>
+      <c r="H38" s="1" t="str" cm="1">
+        <f t="array" ref="H38">_xlfn.IFS(Predictions!H40=1,$E38,Predictions!H40="X","Draw",Predictions!H40=2,$F38)</f>
         <v>Draw</v>
       </c>
-      <c r="G38" s="1" t="str" cm="1">
-        <f t="array" ref="G38">_xlfn.IFS(Predictions!J40=1,$C38,Predictions!J40="X","Draw",Predictions!J40=2,$D38)</f>
+      <c r="I38" s="1" t="str" cm="1">
+        <f t="array" ref="I38">_xlfn.IFS(Predictions!J40=1,$E38,Predictions!J40="X","Draw",Predictions!J40=2,$F38)</f>
         <v>Belgium</v>
       </c>
-      <c r="H38" s="1" t="str" cm="1">
-        <f t="array" ref="H38">_xlfn.IFS(Predictions!L40=1,$C38,Predictions!L40="X","Draw",Predictions!L40=2,$D38)</f>
+      <c r="J38" s="1" t="str" cm="1">
+        <f t="array" ref="J38">_xlfn.IFS(Predictions!L40=1,$E38,Predictions!L40="X","Draw",Predictions!L40=2,$F38)</f>
         <v>Belgium</v>
       </c>
-      <c r="I38" s="1" t="str" cm="1">
-        <f t="array" ref="I38">_xlfn.IFS(Predictions!N40=1,$C38,Predictions!N40="X","Draw",Predictions!N40=2,$D38)</f>
+      <c r="K38" s="1" t="str" cm="1">
+        <f t="array" ref="K38">_xlfn.IFS(Predictions!N40=1,$E38,Predictions!N40="X","Draw",Predictions!N40=2,$F38)</f>
         <v>Belgium</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="26">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="164">
         <v>46194</v>
       </c>
-      <c r="B39" s="40" t="s">
+      <c r="B39" s="163">
+        <v>0.875</v>
+      </c>
+      <c r="C39" s="163"/>
+      <c r="D39" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C39" s="28" t="s">
+      <c r="E39" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="28" t="s">
+      <c r="F39" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="1" t="str" cm="1">
-        <f t="array" ref="E39">_xlfn.IFS(Predictions!F41=1,$C39,Predictions!F41="X","Draw",Predictions!F41=2,$D39)</f>
+      <c r="G39" s="1" t="str" cm="1">
+        <f t="array" ref="G39">_xlfn.IFS(Predictions!F41=1,$E39,Predictions!F41="X","Draw",Predictions!F41=2,$F39)</f>
         <v>Spain</v>
       </c>
-      <c r="F39" s="1" t="str" cm="1">
-        <f t="array" ref="F39">_xlfn.IFS(Predictions!H41=1,$C39,Predictions!H41="X","Draw",Predictions!H41=2,$D39)</f>
+      <c r="H39" s="1" t="str" cm="1">
+        <f t="array" ref="H39">_xlfn.IFS(Predictions!H41=1,$E39,Predictions!H41="X","Draw",Predictions!H41=2,$F39)</f>
         <v>Spain</v>
       </c>
-      <c r="G39" s="1" t="str" cm="1">
-        <f t="array" ref="G39">_xlfn.IFS(Predictions!J41=1,$C39,Predictions!J41="X","Draw",Predictions!J41=2,$D39)</f>
+      <c r="I39" s="1" t="str" cm="1">
+        <f t="array" ref="I39">_xlfn.IFS(Predictions!J41=1,$E39,Predictions!J41="X","Draw",Predictions!J41=2,$F39)</f>
         <v>Spain</v>
       </c>
-      <c r="H39" s="1" t="str" cm="1">
-        <f t="array" ref="H39">_xlfn.IFS(Predictions!L41=1,$C39,Predictions!L41="X","Draw",Predictions!L41=2,$D39)</f>
+      <c r="J39" s="1" t="str" cm="1">
+        <f t="array" ref="J39">_xlfn.IFS(Predictions!L41=1,$E39,Predictions!L41="X","Draw",Predictions!L41=2,$F39)</f>
         <v>Spain</v>
       </c>
-      <c r="I39" s="1" t="str" cm="1">
-        <f t="array" ref="I39">_xlfn.IFS(Predictions!N41=1,$C39,Predictions!N41="X","Draw",Predictions!N41=2,$D39)</f>
+      <c r="K39" s="1" t="str" cm="1">
+        <f t="array" ref="K39">_xlfn.IFS(Predictions!N41=1,$E39,Predictions!N41="X","Draw",Predictions!N41=2,$F39)</f>
         <v>Spain</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="29">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="164">
         <v>46194</v>
       </c>
-      <c r="B40" s="41" t="s">
+      <c r="B40" s="162">
+        <v>0</v>
+      </c>
+      <c r="C40" s="162"/>
+      <c r="D40" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="31" t="s">
+      <c r="E40" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="D40" s="31" t="s">
+      <c r="F40" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E40" s="1" t="str" cm="1">
-        <f t="array" ref="E40">_xlfn.IFS(Predictions!F42=1,$C40,Predictions!F42="X","Draw",Predictions!F42=2,$D40)</f>
+      <c r="G40" s="1" t="str" cm="1">
+        <f t="array" ref="G40">_xlfn.IFS(Predictions!F42=1,$E40,Predictions!F42="X","Draw",Predictions!F42=2,$F40)</f>
         <v>Uruguay</v>
       </c>
-      <c r="F40" s="1" t="str" cm="1">
-        <f t="array" ref="F40">_xlfn.IFS(Predictions!H42=1,$C40,Predictions!H42="X","Draw",Predictions!H42=2,$D40)</f>
+      <c r="H40" s="1" t="str" cm="1">
+        <f t="array" ref="H40">_xlfn.IFS(Predictions!H42=1,$E40,Predictions!H42="X","Draw",Predictions!H42=2,$F40)</f>
         <v>Uruguay</v>
       </c>
-      <c r="G40" s="1" t="str" cm="1">
-        <f t="array" ref="G40">_xlfn.IFS(Predictions!J42=1,$C40,Predictions!J42="X","Draw",Predictions!J42=2,$D40)</f>
+      <c r="I40" s="1" t="str" cm="1">
+        <f t="array" ref="I40">_xlfn.IFS(Predictions!J42=1,$E40,Predictions!J42="X","Draw",Predictions!J42=2,$F40)</f>
         <v>Uruguay</v>
       </c>
-      <c r="H40" s="1" t="str" cm="1">
-        <f t="array" ref="H40">_xlfn.IFS(Predictions!L42=1,$C40,Predictions!L42="X","Draw",Predictions!L42=2,$D40)</f>
+      <c r="J40" s="1" t="str" cm="1">
+        <f t="array" ref="J40">_xlfn.IFS(Predictions!L42=1,$E40,Predictions!L42="X","Draw",Predictions!L42=2,$F40)</f>
         <v>Uruguay</v>
       </c>
-      <c r="I40" s="1" t="str" cm="1">
-        <f t="array" ref="I40">_xlfn.IFS(Predictions!N42=1,$C40,Predictions!N42="X","Draw",Predictions!N42=2,$D40)</f>
+      <c r="K40" s="1" t="str" cm="1">
+        <f t="array" ref="K40">_xlfn.IFS(Predictions!N42=1,$E40,Predictions!N42="X","Draw",Predictions!N42=2,$F40)</f>
         <v>Uruguay</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="26">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="164">
         <v>46195</v>
       </c>
-      <c r="B41" s="39" t="s">
+      <c r="B41" s="163">
+        <v>0.125</v>
+      </c>
+      <c r="C41" s="163"/>
+      <c r="D41" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="28" t="s">
+      <c r="E41" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="D41" s="28" t="s">
+      <c r="F41" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="E41" s="1" t="str" cm="1">
-        <f t="array" ref="E41">_xlfn.IFS(Predictions!F43=1,$C41,Predictions!F43="X","Draw",Predictions!F43=2,$D41)</f>
+      <c r="G41" s="1" t="str" cm="1">
+        <f t="array" ref="G41">_xlfn.IFS(Predictions!F43=1,$E41,Predictions!F43="X","Draw",Predictions!F43=2,$F41)</f>
         <v>Draw</v>
       </c>
-      <c r="F41" s="1" t="str" cm="1">
-        <f t="array" ref="F41">_xlfn.IFS(Predictions!H43=1,$C41,Predictions!H43="X","Draw",Predictions!H43=2,$D41)</f>
+      <c r="H41" s="1" t="str" cm="1">
+        <f t="array" ref="H41">_xlfn.IFS(Predictions!H43=1,$E41,Predictions!H43="X","Draw",Predictions!H43=2,$F41)</f>
         <v>Egypt</v>
       </c>
-      <c r="G41" s="1" t="str" cm="1">
-        <f t="array" ref="G41">_xlfn.IFS(Predictions!J43=1,$C41,Predictions!J43="X","Draw",Predictions!J43=2,$D41)</f>
+      <c r="I41" s="1" t="str" cm="1">
+        <f t="array" ref="I41">_xlfn.IFS(Predictions!J43=1,$E41,Predictions!J43="X","Draw",Predictions!J43=2,$F41)</f>
         <v>Egypt</v>
       </c>
-      <c r="H41" s="1" t="str" cm="1">
-        <f t="array" ref="H41">_xlfn.IFS(Predictions!L43=1,$C41,Predictions!L43="X","Draw",Predictions!L43=2,$D41)</f>
+      <c r="J41" s="1" t="str" cm="1">
+        <f t="array" ref="J41">_xlfn.IFS(Predictions!L43=1,$E41,Predictions!L43="X","Draw",Predictions!L43=2,$F41)</f>
         <v>Egypt</v>
       </c>
-      <c r="I41" s="1" t="str" cm="1">
-        <f t="array" ref="I41">_xlfn.IFS(Predictions!N43=1,$C41,Predictions!N43="X","Draw",Predictions!N43=2,$D41)</f>
+      <c r="K41" s="1" t="str" cm="1">
+        <f t="array" ref="K41">_xlfn.IFS(Predictions!N43=1,$E41,Predictions!N43="X","Draw",Predictions!N43=2,$F41)</f>
         <v>Egypt</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="26">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="164">
         <v>46195</v>
       </c>
-      <c r="B42" s="42" t="s">
+      <c r="B42" s="163">
+        <v>0.75</v>
+      </c>
+      <c r="C42" s="163"/>
+      <c r="D42" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="C42" s="28" t="s">
+      <c r="E42" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D42" s="28" t="s">
+      <c r="F42" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="E42" s="1" t="str" cm="1">
-        <f t="array" ref="E42">_xlfn.IFS(Predictions!F44=1,$C42,Predictions!F44="X","Draw",Predictions!F44=2,$D42)</f>
+      <c r="G42" s="1" t="str" cm="1">
+        <f t="array" ref="G42">_xlfn.IFS(Predictions!F44=1,$E42,Predictions!F44="X","Draw",Predictions!F44=2,$F42)</f>
         <v>France</v>
       </c>
-      <c r="F42" s="1" t="str" cm="1">
-        <f t="array" ref="F42">_xlfn.IFS(Predictions!H44=1,$C42,Predictions!H44="X","Draw",Predictions!H44=2,$D42)</f>
+      <c r="H42" s="1" t="str" cm="1">
+        <f t="array" ref="H42">_xlfn.IFS(Predictions!H44=1,$E42,Predictions!H44="X","Draw",Predictions!H44=2,$F42)</f>
         <v>France</v>
       </c>
-      <c r="G42" s="1" t="str" cm="1">
-        <f t="array" ref="G42">_xlfn.IFS(Predictions!J44=1,$C42,Predictions!J44="X","Draw",Predictions!J44=2,$D42)</f>
+      <c r="I42" s="1" t="str" cm="1">
+        <f t="array" ref="I42">_xlfn.IFS(Predictions!J44=1,$E42,Predictions!J44="X","Draw",Predictions!J44=2,$F42)</f>
         <v>France</v>
       </c>
-      <c r="H42" s="1" t="str" cm="1">
-        <f t="array" ref="H42">_xlfn.IFS(Predictions!L44=1,$C42,Predictions!L44="X","Draw",Predictions!L44=2,$D42)</f>
+      <c r="J42" s="1" t="str" cm="1">
+        <f t="array" ref="J42">_xlfn.IFS(Predictions!L44=1,$E42,Predictions!L44="X","Draw",Predictions!L44=2,$F42)</f>
         <v>France</v>
       </c>
-      <c r="I42" s="1" t="str" cm="1">
-        <f t="array" ref="I42">_xlfn.IFS(Predictions!N44=1,$C42,Predictions!N44="X","Draw",Predictions!N44=2,$D42)</f>
+      <c r="K42" s="1" t="str" cm="1">
+        <f t="array" ref="K42">_xlfn.IFS(Predictions!N44=1,$E42,Predictions!N44="X","Draw",Predictions!N44=2,$F42)</f>
         <v>France</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="29">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="164">
         <v>46195</v>
       </c>
-      <c r="B43" s="49" t="s">
+      <c r="B43" s="162">
+        <v>0.875</v>
+      </c>
+      <c r="C43" s="162"/>
+      <c r="D43" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="C43" s="31" t="s">
+      <c r="E43" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="D43" s="31" t="s">
+      <c r="F43" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="E43" s="1" t="str" cm="1">
-        <f t="array" ref="E43">_xlfn.IFS(Predictions!F45=1,$C43,Predictions!F45="X","Draw",Predictions!F45=2,$D43)</f>
+      <c r="G43" s="1" t="str" cm="1">
+        <f t="array" ref="G43">_xlfn.IFS(Predictions!F45=1,$E43,Predictions!F45="X","Draw",Predictions!F45=2,$F43)</f>
         <v>Argentina</v>
       </c>
-      <c r="F43" s="1" t="str" cm="1">
-        <f t="array" ref="F43">_xlfn.IFS(Predictions!H45=1,$C43,Predictions!H45="X","Draw",Predictions!H45=2,$D43)</f>
+      <c r="H43" s="1" t="str" cm="1">
+        <f t="array" ref="H43">_xlfn.IFS(Predictions!H45=1,$E43,Predictions!H45="X","Draw",Predictions!H45=2,$F43)</f>
         <v>Draw</v>
       </c>
-      <c r="G43" s="1" t="str" cm="1">
-        <f t="array" ref="G43">_xlfn.IFS(Predictions!J45=1,$C43,Predictions!J45="X","Draw",Predictions!J45=2,$D43)</f>
+      <c r="I43" s="1" t="str" cm="1">
+        <f t="array" ref="I43">_xlfn.IFS(Predictions!J45=1,$E43,Predictions!J45="X","Draw",Predictions!J45=2,$F43)</f>
         <v>Argentina</v>
       </c>
-      <c r="H43" s="1" t="str" cm="1">
-        <f t="array" ref="H43">_xlfn.IFS(Predictions!L45=1,$C43,Predictions!L45="X","Draw",Predictions!L45=2,$D43)</f>
+      <c r="J43" s="1" t="str" cm="1">
+        <f t="array" ref="J43">_xlfn.IFS(Predictions!L45=1,$E43,Predictions!L45="X","Draw",Predictions!L45=2,$F43)</f>
         <v>Argentina</v>
       </c>
-      <c r="I43" s="1" t="str" cm="1">
-        <f t="array" ref="I43">_xlfn.IFS(Predictions!N45=1,$C43,Predictions!N45="X","Draw",Predictions!N45=2,$D43)</f>
+      <c r="K43" s="1" t="str" cm="1">
+        <f t="array" ref="K43">_xlfn.IFS(Predictions!N45=1,$E43,Predictions!N45="X","Draw",Predictions!N45=2,$F43)</f>
         <v>Argentina</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="26">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="164">
         <v>46196</v>
       </c>
-      <c r="B44" s="42" t="s">
+      <c r="B44" s="163">
+        <v>0</v>
+      </c>
+      <c r="C44" s="163"/>
+      <c r="D44" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="28" t="s">
+      <c r="E44" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="D44" s="28" t="s">
+      <c r="F44" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="E44" s="1" t="str" cm="1">
-        <f t="array" ref="E44">_xlfn.IFS(Predictions!F46=1,$C44,Predictions!F46="X","Draw",Predictions!F46=2,$D44)</f>
+      <c r="G44" s="1" t="str" cm="1">
+        <f t="array" ref="G44">_xlfn.IFS(Predictions!F46=1,$E44,Predictions!F46="X","Draw",Predictions!F46=2,$F44)</f>
         <v>Senegal</v>
       </c>
-      <c r="F44" s="1" t="str" cm="1">
-        <f t="array" ref="F44">_xlfn.IFS(Predictions!H46=1,$C44,Predictions!H46="X","Draw",Predictions!H46=2,$D44)</f>
+      <c r="H44" s="1" t="str" cm="1">
+        <f t="array" ref="H44">_xlfn.IFS(Predictions!H46=1,$E44,Predictions!H46="X","Draw",Predictions!H46=2,$F44)</f>
         <v>Norway</v>
       </c>
-      <c r="G44" s="1" t="str" cm="1">
-        <f t="array" ref="G44">_xlfn.IFS(Predictions!J46=1,$C44,Predictions!J46="X","Draw",Predictions!J46=2,$D44)</f>
+      <c r="I44" s="1" t="str" cm="1">
+        <f t="array" ref="I44">_xlfn.IFS(Predictions!J46=1,$E44,Predictions!J46="X","Draw",Predictions!J46=2,$F44)</f>
         <v>Senegal</v>
       </c>
-      <c r="H44" s="1" t="str" cm="1">
-        <f t="array" ref="H44">_xlfn.IFS(Predictions!L46=1,$C44,Predictions!L46="X","Draw",Predictions!L46=2,$D44)</f>
+      <c r="J44" s="1" t="str" cm="1">
+        <f t="array" ref="J44">_xlfn.IFS(Predictions!L46=1,$E44,Predictions!L46="X","Draw",Predictions!L46=2,$F44)</f>
         <v>Draw</v>
       </c>
-      <c r="I44" s="1" t="str" cm="1">
-        <f t="array" ref="I44">_xlfn.IFS(Predictions!N46=1,$C44,Predictions!N46="X","Draw",Predictions!N46=2,$D44)</f>
+      <c r="K44" s="1" t="str" cm="1">
+        <f t="array" ref="K44">_xlfn.IFS(Predictions!N46=1,$E44,Predictions!N46="X","Draw",Predictions!N46=2,$F44)</f>
         <v>Draw</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="26">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="164">
         <v>46196</v>
       </c>
-      <c r="B45" s="44" t="s">
+      <c r="B45" s="163">
+        <v>0.125</v>
+      </c>
+      <c r="C45" s="163"/>
+      <c r="D45" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="E45" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="28" t="s">
+      <c r="F45" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E45" s="1" t="str" cm="1">
-        <f t="array" ref="E45">_xlfn.IFS(Predictions!F47=1,$C45,Predictions!F47="X","Draw",Predictions!F47=2,$D45)</f>
+      <c r="G45" s="1" t="str" cm="1">
+        <f t="array" ref="G45">_xlfn.IFS(Predictions!F47=1,$E45,Predictions!F47="X","Draw",Predictions!F47=2,$F45)</f>
         <v>Algeria</v>
       </c>
-      <c r="F45" s="1" t="str" cm="1">
-        <f t="array" ref="F45">_xlfn.IFS(Predictions!H47=1,$C45,Predictions!H47="X","Draw",Predictions!H47=2,$D45)</f>
+      <c r="H45" s="1" t="str" cm="1">
+        <f t="array" ref="H45">_xlfn.IFS(Predictions!H47=1,$E45,Predictions!H47="X","Draw",Predictions!H47=2,$F45)</f>
         <v>Algeria</v>
       </c>
-      <c r="G45" s="1" t="str" cm="1">
-        <f t="array" ref="G45">_xlfn.IFS(Predictions!J47=1,$C45,Predictions!J47="X","Draw",Predictions!J47=2,$D45)</f>
+      <c r="I45" s="1" t="str" cm="1">
+        <f t="array" ref="I45">_xlfn.IFS(Predictions!J47=1,$E45,Predictions!J47="X","Draw",Predictions!J47=2,$F45)</f>
         <v>Algeria</v>
       </c>
-      <c r="H45" s="1" t="str" cm="1">
-        <f t="array" ref="H45">_xlfn.IFS(Predictions!L47=1,$C45,Predictions!L47="X","Draw",Predictions!L47=2,$D45)</f>
+      <c r="J45" s="1" t="str" cm="1">
+        <f t="array" ref="J45">_xlfn.IFS(Predictions!L47=1,$E45,Predictions!L47="X","Draw",Predictions!L47=2,$F45)</f>
         <v>Algeria</v>
       </c>
-      <c r="I45" s="1" t="str" cm="1">
-        <f t="array" ref="I45">_xlfn.IFS(Predictions!N47=1,$C45,Predictions!N47="X","Draw",Predictions!N47=2,$D45)</f>
+      <c r="K45" s="1" t="str" cm="1">
+        <f t="array" ref="K45">_xlfn.IFS(Predictions!N47=1,$E45,Predictions!N47="X","Draw",Predictions!N47=2,$F45)</f>
         <v>Algeria</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="26">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="164">
         <v>46196</v>
       </c>
-      <c r="B46" s="45" t="s">
+      <c r="B46" s="163">
+        <v>0.75</v>
+      </c>
+      <c r="C46" s="163"/>
+      <c r="D46" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="C46" s="28" t="s">
+      <c r="E46" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="D46" s="28" t="s">
+      <c r="F46" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="E46" s="1" t="str" cm="1">
-        <f t="array" ref="E46">_xlfn.IFS(Predictions!F48=1,$C46,Predictions!F48="X","Draw",Predictions!F48=2,$D46)</f>
+      <c r="G46" s="1" t="str" cm="1">
+        <f t="array" ref="G46">_xlfn.IFS(Predictions!F48=1,$E46,Predictions!F48="X","Draw",Predictions!F48=2,$F46)</f>
         <v>Portugal</v>
       </c>
-      <c r="F46" s="1" t="str" cm="1">
-        <f t="array" ref="F46">_xlfn.IFS(Predictions!H48=1,$C46,Predictions!H48="X","Draw",Predictions!H48=2,$D46)</f>
+      <c r="H46" s="1" t="str" cm="1">
+        <f t="array" ref="H46">_xlfn.IFS(Predictions!H48=1,$E46,Predictions!H48="X","Draw",Predictions!H48=2,$F46)</f>
         <v>Portugal</v>
       </c>
-      <c r="G46" s="1" t="str" cm="1">
-        <f t="array" ref="G46">_xlfn.IFS(Predictions!J48=1,$C46,Predictions!J48="X","Draw",Predictions!J48=2,$D46)</f>
+      <c r="I46" s="1" t="str" cm="1">
+        <f t="array" ref="I46">_xlfn.IFS(Predictions!J48=1,$E46,Predictions!J48="X","Draw",Predictions!J48=2,$F46)</f>
         <v>Portugal</v>
       </c>
-      <c r="H46" s="1" t="str" cm="1">
-        <f t="array" ref="H46">_xlfn.IFS(Predictions!L48=1,$C46,Predictions!L48="X","Draw",Predictions!L48=2,$D46)</f>
+      <c r="J46" s="1" t="str" cm="1">
+        <f t="array" ref="J46">_xlfn.IFS(Predictions!L48=1,$E46,Predictions!L48="X","Draw",Predictions!L48=2,$F46)</f>
         <v>Portugal</v>
       </c>
-      <c r="I46" s="1" t="str" cm="1">
-        <f t="array" ref="I46">_xlfn.IFS(Predictions!N48=1,$C46,Predictions!N48="X","Draw",Predictions!N48=2,$D46)</f>
+      <c r="K46" s="1" t="str" cm="1">
+        <f t="array" ref="K46">_xlfn.IFS(Predictions!N48=1,$E46,Predictions!N48="X","Draw",Predictions!N48=2,$F46)</f>
         <v>Portugal</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="29">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="164">
         <v>46196</v>
       </c>
-      <c r="B47" s="46" t="s">
+      <c r="B47" s="162">
+        <v>0.875</v>
+      </c>
+      <c r="C47" s="162"/>
+      <c r="D47" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="C47" s="31" t="s">
+      <c r="E47" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="D47" s="31" t="s">
+      <c r="F47" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="E47" s="1" t="str" cm="1">
-        <f t="array" ref="E47">_xlfn.IFS(Predictions!F49=1,$C47,Predictions!F49="X","Draw",Predictions!F49=2,$D47)</f>
+      <c r="G47" s="1" t="str" cm="1">
+        <f t="array" ref="G47">_xlfn.IFS(Predictions!F49=1,$E47,Predictions!F49="X","Draw",Predictions!F49=2,$F47)</f>
         <v>England</v>
       </c>
-      <c r="F47" s="1" t="str" cm="1">
-        <f t="array" ref="F47">_xlfn.IFS(Predictions!H49=1,$C47,Predictions!H49="X","Draw",Predictions!H49=2,$D47)</f>
+      <c r="H47" s="1" t="str" cm="1">
+        <f t="array" ref="H47">_xlfn.IFS(Predictions!H49=1,$E47,Predictions!H49="X","Draw",Predictions!H49=2,$F47)</f>
         <v>Draw</v>
       </c>
-      <c r="G47" s="1" t="str" cm="1">
-        <f t="array" ref="G47">_xlfn.IFS(Predictions!J49=1,$C47,Predictions!J49="X","Draw",Predictions!J49=2,$D47)</f>
+      <c r="I47" s="1" t="str" cm="1">
+        <f t="array" ref="I47">_xlfn.IFS(Predictions!J49=1,$E47,Predictions!J49="X","Draw",Predictions!J49=2,$F47)</f>
         <v>England</v>
       </c>
-      <c r="H47" s="1" t="str" cm="1">
-        <f t="array" ref="H47">_xlfn.IFS(Predictions!L49=1,$C47,Predictions!L49="X","Draw",Predictions!L49=2,$D47)</f>
+      <c r="J47" s="1" t="str" cm="1">
+        <f t="array" ref="J47">_xlfn.IFS(Predictions!L49=1,$E47,Predictions!L49="X","Draw",Predictions!L49=2,$F47)</f>
         <v>England</v>
       </c>
-      <c r="I47" s="1" t="str" cm="1">
-        <f t="array" ref="I47">_xlfn.IFS(Predictions!N49=1,$C47,Predictions!N49="X","Draw",Predictions!N49=2,$D47)</f>
+      <c r="K47" s="1" t="str" cm="1">
+        <f t="array" ref="K47">_xlfn.IFS(Predictions!N49=1,$E47,Predictions!N49="X","Draw",Predictions!N49=2,$F47)</f>
         <v>England</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="26">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="164">
         <v>46197</v>
       </c>
-      <c r="B48" s="45" t="s">
+      <c r="B48" s="163">
+        <v>0</v>
+      </c>
+      <c r="C48" s="163"/>
+      <c r="D48" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="C48" s="28" t="s">
+      <c r="E48" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="D48" s="28" t="s">
+      <c r="F48" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="E48" s="1" t="str" cm="1">
-        <f t="array" ref="E48">_xlfn.IFS(Predictions!F50=1,$C48,Predictions!F50="X","Draw",Predictions!F50=2,$D48)</f>
+      <c r="G48" s="1" t="str" cm="1">
+        <f t="array" ref="G48">_xlfn.IFS(Predictions!F50=1,$E48,Predictions!F50="X","Draw",Predictions!F50=2,$F48)</f>
         <v>Draw</v>
       </c>
-      <c r="F48" s="1" t="str" cm="1">
-        <f t="array" ref="F48">_xlfn.IFS(Predictions!H50=1,$C48,Predictions!H50="X","Draw",Predictions!H50=2,$D48)</f>
+      <c r="H48" s="1" t="str" cm="1">
+        <f t="array" ref="H48">_xlfn.IFS(Predictions!H50=1,$E48,Predictions!H50="X","Draw",Predictions!H50=2,$F48)</f>
         <v>Draw</v>
       </c>
-      <c r="G48" s="1" t="str" cm="1">
-        <f t="array" ref="G48">_xlfn.IFS(Predictions!J50=1,$C48,Predictions!J50="X","Draw",Predictions!J50=2,$D48)</f>
+      <c r="I48" s="1" t="str" cm="1">
+        <f t="array" ref="I48">_xlfn.IFS(Predictions!J50=1,$E48,Predictions!J50="X","Draw",Predictions!J50=2,$F48)</f>
         <v>Colombia</v>
       </c>
-      <c r="H48" s="1" t="str" cm="1">
-        <f t="array" ref="H48">_xlfn.IFS(Predictions!L50=1,$C48,Predictions!L50="X","Draw",Predictions!L50=2,$D48)</f>
+      <c r="J48" s="1" t="str" cm="1">
+        <f t="array" ref="J48">_xlfn.IFS(Predictions!L50=1,$E48,Predictions!L50="X","Draw",Predictions!L50=2,$F48)</f>
         <v>Colombia</v>
       </c>
-      <c r="I48" s="1" t="str" cm="1">
-        <f t="array" ref="I48">_xlfn.IFS(Predictions!N50=1,$C48,Predictions!N50="X","Draw",Predictions!N50=2,$D48)</f>
+      <c r="K48" s="1" t="str" cm="1">
+        <f t="array" ref="K48">_xlfn.IFS(Predictions!N50=1,$E48,Predictions!N50="X","Draw",Predictions!N50=2,$F48)</f>
         <v>Colombia</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="26">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="164">
         <v>46197</v>
       </c>
-      <c r="B49" s="47" t="s">
+      <c r="B49" s="163">
+        <v>0.125</v>
+      </c>
+      <c r="C49" s="163"/>
+      <c r="D49" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="C49" s="28" t="s">
+      <c r="E49" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="D49" s="28" t="s">
+      <c r="F49" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="E49" s="1" t="str" cm="1">
-        <f t="array" ref="E49">_xlfn.IFS(Predictions!F51=1,$C49,Predictions!F51="X","Draw",Predictions!F51=2,$D49)</f>
+      <c r="G49" s="1" t="str" cm="1">
+        <f t="array" ref="G49">_xlfn.IFS(Predictions!F51=1,$E49,Predictions!F51="X","Draw",Predictions!F51=2,$F49)</f>
         <v>Croatia</v>
       </c>
-      <c r="F49" s="1" t="str" cm="1">
-        <f t="array" ref="F49">_xlfn.IFS(Predictions!H51=1,$C49,Predictions!H51="X","Draw",Predictions!H51=2,$D49)</f>
+      <c r="H49" s="1" t="str" cm="1">
+        <f t="array" ref="H49">_xlfn.IFS(Predictions!H51=1,$E49,Predictions!H51="X","Draw",Predictions!H51=2,$F49)</f>
         <v>Croatia</v>
       </c>
-      <c r="G49" s="1" t="str" cm="1">
-        <f t="array" ref="G49">_xlfn.IFS(Predictions!J51=1,$C49,Predictions!J51="X","Draw",Predictions!J51=2,$D49)</f>
+      <c r="I49" s="1" t="str" cm="1">
+        <f t="array" ref="I49">_xlfn.IFS(Predictions!J51=1,$E49,Predictions!J51="X","Draw",Predictions!J51=2,$F49)</f>
         <v>Croatia</v>
       </c>
-      <c r="H49" s="1" t="str" cm="1">
-        <f t="array" ref="H49">_xlfn.IFS(Predictions!L51=1,$C49,Predictions!L51="X","Draw",Predictions!L51=2,$D49)</f>
+      <c r="J49" s="1" t="str" cm="1">
+        <f t="array" ref="J49">_xlfn.IFS(Predictions!L51=1,$E49,Predictions!L51="X","Draw",Predictions!L51=2,$F49)</f>
         <v>Croatia</v>
       </c>
-      <c r="I49" s="1" t="str" cm="1">
-        <f t="array" ref="I49">_xlfn.IFS(Predictions!N51=1,$C49,Predictions!N51="X","Draw",Predictions!N51=2,$D49)</f>
+      <c r="K49" s="1" t="str" cm="1">
+        <f t="array" ref="K49">_xlfn.IFS(Predictions!N51=1,$E49,Predictions!N51="X","Draw",Predictions!N51=2,$F49)</f>
         <v>Croatia</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="26">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="164">
         <v>46197</v>
       </c>
-      <c r="B50" s="33" t="s">
+      <c r="B50" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C50" s="163"/>
+      <c r="D50" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="28" t="s">
+      <c r="E50" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D50" s="28" t="s">
+      <c r="F50" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="E50" s="1" t="str" cm="1">
-        <f t="array" ref="E50">_xlfn.IFS(Predictions!F52=1,$C50,Predictions!F52="X","Draw",Predictions!F52=2,$D50)</f>
+      <c r="G50" s="1" t="str" cm="1">
+        <f t="array" ref="G50">_xlfn.IFS(Predictions!F52=1,$E50,Predictions!F52="X","Draw",Predictions!F52=2,$F50)</f>
         <v>Switzerland</v>
       </c>
-      <c r="F50" s="1" t="str" cm="1">
-        <f t="array" ref="F50">_xlfn.IFS(Predictions!H52=1,$C50,Predictions!H52="X","Draw",Predictions!H52=2,$D50)</f>
+      <c r="H50" s="1" t="str" cm="1">
+        <f t="array" ref="H50">_xlfn.IFS(Predictions!H52=1,$E50,Predictions!H52="X","Draw",Predictions!H52=2,$F50)</f>
         <v>Draw</v>
       </c>
-      <c r="G50" s="1" t="str" cm="1">
-        <f t="array" ref="G50">_xlfn.IFS(Predictions!J52=1,$C50,Predictions!J52="X","Draw",Predictions!J52=2,$D50)</f>
+      <c r="I50" s="1" t="str" cm="1">
+        <f t="array" ref="I50">_xlfn.IFS(Predictions!J52=1,$E50,Predictions!J52="X","Draw",Predictions!J52=2,$F50)</f>
         <v>Switzerland</v>
       </c>
-      <c r="H50" s="1" t="str" cm="1">
-        <f t="array" ref="H50">_xlfn.IFS(Predictions!L52=1,$C50,Predictions!L52="X","Draw",Predictions!L52=2,$D50)</f>
+      <c r="J50" s="1" t="str" cm="1">
+        <f t="array" ref="J50">_xlfn.IFS(Predictions!L52=1,$E50,Predictions!L52="X","Draw",Predictions!L52=2,$F50)</f>
         <v>Switzerland</v>
       </c>
-      <c r="I50" s="1" t="str" cm="1">
-        <f t="array" ref="I50">_xlfn.IFS(Predictions!N52=1,$C50,Predictions!N52="X","Draw",Predictions!N52=2,$D50)</f>
+      <c r="K50" s="1" t="str" cm="1">
+        <f t="array" ref="K50">_xlfn.IFS(Predictions!N52=1,$E50,Predictions!N52="X","Draw",Predictions!N52=2,$F50)</f>
         <v>Switzerland</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="26">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="164">
         <v>46197</v>
       </c>
-      <c r="B51" s="33" t="s">
+      <c r="B51" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C51" s="163"/>
+      <c r="D51" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="C51" s="28" t="s">
+      <c r="E51" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D51" s="28" t="s">
+      <c r="F51" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="E51" s="1" t="str" cm="1">
-        <f t="array" ref="E51">_xlfn.IFS(Predictions!F53=1,$C51,Predictions!F53="X","Draw",Predictions!F53=2,$D51)</f>
+      <c r="G51" s="1" t="str" cm="1">
+        <f t="array" ref="G51">_xlfn.IFS(Predictions!F53=1,$E51,Predictions!F53="X","Draw",Predictions!F53=2,$F51)</f>
         <v>Draw</v>
       </c>
-      <c r="F51" s="1" t="str" cm="1">
-        <f t="array" ref="F51">_xlfn.IFS(Predictions!H53=1,$C51,Predictions!H53="X","Draw",Predictions!H53=2,$D51)</f>
+      <c r="H51" s="1" t="str" cm="1">
+        <f t="array" ref="H51">_xlfn.IFS(Predictions!H53=1,$E51,Predictions!H53="X","Draw",Predictions!H53=2,$F51)</f>
         <v>Bosnia and Herzegovina</v>
       </c>
-      <c r="G51" s="1" t="str" cm="1">
-        <f t="array" ref="G51">_xlfn.IFS(Predictions!J53=1,$C51,Predictions!J53="X","Draw",Predictions!J53=2,$D51)</f>
+      <c r="I51" s="1" t="str" cm="1">
+        <f t="array" ref="I51">_xlfn.IFS(Predictions!J53=1,$E51,Predictions!J53="X","Draw",Predictions!J53=2,$F51)</f>
         <v>Bosnia and Herzegovina</v>
       </c>
-      <c r="H51" s="1" t="str" cm="1">
-        <f t="array" ref="H51">_xlfn.IFS(Predictions!L53=1,$C51,Predictions!L53="X","Draw",Predictions!L53=2,$D51)</f>
+      <c r="J51" s="1" t="str" cm="1">
+        <f t="array" ref="J51">_xlfn.IFS(Predictions!L53=1,$E51,Predictions!L53="X","Draw",Predictions!L53=2,$F51)</f>
         <v>Bosnia and Herzegovina</v>
       </c>
-      <c r="I51" s="1" t="str" cm="1">
-        <f t="array" ref="I51">_xlfn.IFS(Predictions!N53=1,$C51,Predictions!N53="X","Draw",Predictions!N53=2,$D51)</f>
+      <c r="K51" s="1" t="str" cm="1">
+        <f t="array" ref="K51">_xlfn.IFS(Predictions!N53=1,$E51,Predictions!N53="X","Draw",Predictions!N53=2,$F51)</f>
         <v>Bosnia and Herzegovina</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="26">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="164">
         <v>46197</v>
       </c>
-      <c r="B52" s="35" t="s">
+      <c r="B52" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C52" s="163"/>
+      <c r="D52" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="28" t="s">
+      <c r="E52" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D52" s="28" t="s">
+      <c r="F52" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="E52" s="1" t="str" cm="1">
-        <f t="array" ref="E52">_xlfn.IFS(Predictions!F54=1,$C52,Predictions!F54="X","Draw",Predictions!F54=2,$D52)</f>
+      <c r="G52" s="1" t="str" cm="1">
+        <f t="array" ref="G52">_xlfn.IFS(Predictions!F54=1,$E52,Predictions!F54="X","Draw",Predictions!F54=2,$F52)</f>
         <v>Draw</v>
       </c>
-      <c r="F52" s="1" t="str" cm="1">
-        <f t="array" ref="F52">_xlfn.IFS(Predictions!H54=1,$C52,Predictions!H54="X","Draw",Predictions!H54=2,$D52)</f>
+      <c r="H52" s="1" t="str" cm="1">
+        <f t="array" ref="H52">_xlfn.IFS(Predictions!H54=1,$E52,Predictions!H54="X","Draw",Predictions!H54=2,$F52)</f>
         <v>Draw</v>
       </c>
-      <c r="G52" s="1" t="str" cm="1">
-        <f t="array" ref="G52">_xlfn.IFS(Predictions!J54=1,$C52,Predictions!J54="X","Draw",Predictions!J54=2,$D52)</f>
+      <c r="I52" s="1" t="str" cm="1">
+        <f t="array" ref="I52">_xlfn.IFS(Predictions!J54=1,$E52,Predictions!J54="X","Draw",Predictions!J54=2,$F52)</f>
         <v>Brazil</v>
       </c>
-      <c r="H52" s="1" t="str" cm="1">
-        <f t="array" ref="H52">_xlfn.IFS(Predictions!L54=1,$C52,Predictions!L54="X","Draw",Predictions!L54=2,$D52)</f>
+      <c r="J52" s="1" t="str" cm="1">
+        <f t="array" ref="J52">_xlfn.IFS(Predictions!L54=1,$E52,Predictions!L54="X","Draw",Predictions!L54=2,$F52)</f>
         <v>Brazil</v>
       </c>
-      <c r="I52" s="1" t="str" cm="1">
-        <f t="array" ref="I52">_xlfn.IFS(Predictions!N54=1,$C52,Predictions!N54="X","Draw",Predictions!N54=2,$D52)</f>
+      <c r="K52" s="1" t="str" cm="1">
+        <f t="array" ref="K52">_xlfn.IFS(Predictions!N54=1,$E52,Predictions!N54="X","Draw",Predictions!N54=2,$F52)</f>
         <v>Brazil</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="29">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="164">
         <v>46197</v>
       </c>
-      <c r="B53" s="34" t="s">
+      <c r="B53" s="162">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C53" s="162"/>
+      <c r="D53" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="C53" s="31" t="s">
+      <c r="E53" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D53" s="31" t="s">
+      <c r="F53" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="E53" s="1" t="str" cm="1">
-        <f t="array" ref="E53">_xlfn.IFS(Predictions!F55=1,$C53,Predictions!F55="X","Draw",Predictions!F55=2,$D53)</f>
+      <c r="G53" s="1" t="str" cm="1">
+        <f t="array" ref="G53">_xlfn.IFS(Predictions!F55=1,$E53,Predictions!F55="X","Draw",Predictions!F55=2,$F53)</f>
         <v>Morocco</v>
       </c>
-      <c r="F53" s="1" t="str" cm="1">
-        <f t="array" ref="F53">_xlfn.IFS(Predictions!H55=1,$C53,Predictions!H55="X","Draw",Predictions!H55=2,$D53)</f>
+      <c r="H53" s="1" t="str" cm="1">
+        <f t="array" ref="H53">_xlfn.IFS(Predictions!H55=1,$E53,Predictions!H55="X","Draw",Predictions!H55=2,$F53)</f>
         <v>Morocco</v>
       </c>
-      <c r="G53" s="1" t="str" cm="1">
-        <f t="array" ref="G53">_xlfn.IFS(Predictions!J55=1,$C53,Predictions!J55="X","Draw",Predictions!J55=2,$D53)</f>
+      <c r="I53" s="1" t="str" cm="1">
+        <f t="array" ref="I53">_xlfn.IFS(Predictions!J55=1,$E53,Predictions!J55="X","Draw",Predictions!J55=2,$F53)</f>
         <v>Morocco</v>
       </c>
-      <c r="H53" s="1" t="str" cm="1">
-        <f t="array" ref="H53">_xlfn.IFS(Predictions!L55=1,$C53,Predictions!L55="X","Draw",Predictions!L55=2,$D53)</f>
+      <c r="J53" s="1" t="str" cm="1">
+        <f t="array" ref="J53">_xlfn.IFS(Predictions!L55=1,$E53,Predictions!L55="X","Draw",Predictions!L55=2,$F53)</f>
         <v>Morocco</v>
       </c>
-      <c r="I53" s="1" t="str" cm="1">
-        <f t="array" ref="I53">_xlfn.IFS(Predictions!N55=1,$C53,Predictions!N55="X","Draw",Predictions!N55=2,$D53)</f>
+      <c r="K53" s="1" t="str" cm="1">
+        <f t="array" ref="K53">_xlfn.IFS(Predictions!N55=1,$E53,Predictions!N55="X","Draw",Predictions!N55=2,$F53)</f>
         <v>Morocco</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="26">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="164">
         <v>46198</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C54" s="163"/>
+      <c r="D54" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C54" s="28" t="s">
+      <c r="E54" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="28" t="s">
+      <c r="F54" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="1" t="str" cm="1">
-        <f t="array" ref="E54">_xlfn.IFS(Predictions!F56=1,$C54,Predictions!F56="X","Draw",Predictions!F56=2,$D54)</f>
+      <c r="G54" s="1" t="str" cm="1">
+        <f t="array" ref="G54">_xlfn.IFS(Predictions!F56=1,$E54,Predictions!F56="X","Draw",Predictions!F56=2,$F54)</f>
         <v>Mexico</v>
       </c>
-      <c r="F54" s="1" t="str" cm="1">
-        <f t="array" ref="F54">_xlfn.IFS(Predictions!H56=1,$C54,Predictions!H56="X","Draw",Predictions!H56=2,$D54)</f>
+      <c r="H54" s="1" t="str" cm="1">
+        <f t="array" ref="H54">_xlfn.IFS(Predictions!H56=1,$E54,Predictions!H56="X","Draw",Predictions!H56=2,$F54)</f>
         <v>Draw</v>
       </c>
-      <c r="G54" s="1" t="str" cm="1">
-        <f t="array" ref="G54">_xlfn.IFS(Predictions!J56=1,$C54,Predictions!J56="X","Draw",Predictions!J56=2,$D54)</f>
+      <c r="I54" s="1" t="str" cm="1">
+        <f t="array" ref="I54">_xlfn.IFS(Predictions!J56=1,$E54,Predictions!J56="X","Draw",Predictions!J56=2,$F54)</f>
         <v>Draw</v>
       </c>
-      <c r="H54" s="1" t="str" cm="1">
-        <f t="array" ref="H54">_xlfn.IFS(Predictions!L56=1,$C54,Predictions!L56="X","Draw",Predictions!L56=2,$D54)</f>
+      <c r="J54" s="1" t="str" cm="1">
+        <f t="array" ref="J54">_xlfn.IFS(Predictions!L56=1,$E54,Predictions!L56="X","Draw",Predictions!L56=2,$F54)</f>
         <v>Mexico</v>
       </c>
-      <c r="I54" s="1" t="str" cm="1">
-        <f t="array" ref="I54">_xlfn.IFS(Predictions!N56=1,$C54,Predictions!N56="X","Draw",Predictions!N56=2,$D54)</f>
+      <c r="K54" s="1" t="str" cm="1">
+        <f t="array" ref="K54">_xlfn.IFS(Predictions!N56=1,$E54,Predictions!N56="X","Draw",Predictions!N56=2,$F54)</f>
         <v>Mexico</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="26">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="164">
         <v>46198</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C55" s="163"/>
+      <c r="D55" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C55" s="28" t="s">
+      <c r="E55" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="D55" s="28" t="s">
+      <c r="F55" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="E55" s="1" t="str" cm="1">
-        <f t="array" ref="E55">_xlfn.IFS(Predictions!F57=1,$C55,Predictions!F57="X","Draw",Predictions!F57=2,$D55)</f>
+      <c r="G55" s="1" t="str" cm="1">
+        <f t="array" ref="G55">_xlfn.IFS(Predictions!F57=1,$E55,Predictions!F57="X","Draw",Predictions!F57=2,$F55)</f>
         <v>South Korea</v>
       </c>
-      <c r="F55" s="1" t="str" cm="1">
-        <f t="array" ref="F55">_xlfn.IFS(Predictions!H57=1,$C55,Predictions!H57="X","Draw",Predictions!H57=2,$D55)</f>
+      <c r="H55" s="1" t="str" cm="1">
+        <f t="array" ref="H55">_xlfn.IFS(Predictions!H57=1,$E55,Predictions!H57="X","Draw",Predictions!H57=2,$F55)</f>
         <v>South Korea</v>
       </c>
-      <c r="G55" s="1" t="str" cm="1">
-        <f t="array" ref="G55">_xlfn.IFS(Predictions!J57=1,$C55,Predictions!J57="X","Draw",Predictions!J57=2,$D55)</f>
+      <c r="I55" s="1" t="str" cm="1">
+        <f t="array" ref="I55">_xlfn.IFS(Predictions!J57=1,$E55,Predictions!J57="X","Draw",Predictions!J57=2,$F55)</f>
         <v>South Korea</v>
       </c>
-      <c r="H55" s="1" t="str" cm="1">
-        <f t="array" ref="H55">_xlfn.IFS(Predictions!L57=1,$C55,Predictions!L57="X","Draw",Predictions!L57=2,$D55)</f>
+      <c r="J55" s="1" t="str" cm="1">
+        <f t="array" ref="J55">_xlfn.IFS(Predictions!L57=1,$E55,Predictions!L57="X","Draw",Predictions!L57=2,$F55)</f>
         <v>South Korea</v>
       </c>
-      <c r="I55" s="1" t="str" cm="1">
-        <f t="array" ref="I55">_xlfn.IFS(Predictions!N57=1,$C55,Predictions!N57="X","Draw",Predictions!N57=2,$D55)</f>
+      <c r="K55" s="1" t="str" cm="1">
+        <f t="array" ref="K55">_xlfn.IFS(Predictions!N57=1,$E55,Predictions!N57="X","Draw",Predictions!N57=2,$F55)</f>
         <v>South Korea</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="26">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="164">
         <v>46198</v>
       </c>
-      <c r="B56" s="36" t="s">
+      <c r="B56" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C56" s="163"/>
+      <c r="D56" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C56" s="28" t="s">
+      <c r="E56" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="D56" s="28" t="s">
+      <c r="F56" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="E56" s="1" t="str" cm="1">
-        <f t="array" ref="E56">_xlfn.IFS(Predictions!F58=1,$C56,Predictions!F58="X","Draw",Predictions!F58=2,$D56)</f>
+      <c r="G56" s="1" t="str" cm="1">
+        <f t="array" ref="G56">_xlfn.IFS(Predictions!F58=1,$E56,Predictions!F58="X","Draw",Predictions!F58=2,$F56)</f>
         <v>Germany</v>
       </c>
-      <c r="F56" s="1" t="str" cm="1">
-        <f t="array" ref="F56">_xlfn.IFS(Predictions!H58=1,$C56,Predictions!H58="X","Draw",Predictions!H58=2,$D56)</f>
+      <c r="H56" s="1" t="str" cm="1">
+        <f t="array" ref="H56">_xlfn.IFS(Predictions!H58=1,$E56,Predictions!H58="X","Draw",Predictions!H58=2,$F56)</f>
         <v>Draw</v>
       </c>
-      <c r="G56" s="1" t="str" cm="1">
-        <f t="array" ref="G56">_xlfn.IFS(Predictions!J58=1,$C56,Predictions!J58="X","Draw",Predictions!J58=2,$D56)</f>
+      <c r="I56" s="1" t="str" cm="1">
+        <f t="array" ref="I56">_xlfn.IFS(Predictions!J58=1,$E56,Predictions!J58="X","Draw",Predictions!J58=2,$F56)</f>
         <v>Germany</v>
       </c>
-      <c r="H56" s="1" t="str" cm="1">
-        <f t="array" ref="H56">_xlfn.IFS(Predictions!L58=1,$C56,Predictions!L58="X","Draw",Predictions!L58=2,$D56)</f>
+      <c r="J56" s="1" t="str" cm="1">
+        <f t="array" ref="J56">_xlfn.IFS(Predictions!L58=1,$E56,Predictions!L58="X","Draw",Predictions!L58=2,$F56)</f>
         <v>Germany</v>
       </c>
-      <c r="I56" s="1" t="str" cm="1">
-        <f t="array" ref="I56">_xlfn.IFS(Predictions!N58=1,$C56,Predictions!N58="X","Draw",Predictions!N58=2,$D56)</f>
+      <c r="K56" s="1" t="str" cm="1">
+        <f t="array" ref="K56">_xlfn.IFS(Predictions!N58=1,$E56,Predictions!N58="X","Draw",Predictions!N58=2,$F56)</f>
         <v>Germany</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="29">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="164">
         <v>46198</v>
       </c>
-      <c r="B57" s="50" t="s">
+      <c r="B57" s="162">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C57" s="162"/>
+      <c r="D57" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="C57" s="31" t="s">
+      <c r="E57" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D57" s="31" t="s">
+      <c r="F57" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E57" s="1" t="str" cm="1">
-        <f t="array" ref="E57">_xlfn.IFS(Predictions!F59=1,$C57,Predictions!F59="X","Draw",Predictions!F59=2,$D57)</f>
+      <c r="G57" s="1" t="str" cm="1">
+        <f t="array" ref="G57">_xlfn.IFS(Predictions!F59=1,$E57,Predictions!F59="X","Draw",Predictions!F59=2,$F57)</f>
         <v>Côte d'Ivoire</v>
       </c>
-      <c r="F57" s="1" t="str" cm="1">
-        <f t="array" ref="F57">_xlfn.IFS(Predictions!H59=1,$C57,Predictions!H59="X","Draw",Predictions!H59=2,$D57)</f>
+      <c r="H57" s="1" t="str" cm="1">
+        <f t="array" ref="H57">_xlfn.IFS(Predictions!H59=1,$E57,Predictions!H59="X","Draw",Predictions!H59=2,$F57)</f>
         <v>Côte d'Ivoire</v>
       </c>
-      <c r="G57" s="1" t="str" cm="1">
-        <f t="array" ref="G57">_xlfn.IFS(Predictions!J59=1,$C57,Predictions!J59="X","Draw",Predictions!J59=2,$D57)</f>
+      <c r="I57" s="1" t="str" cm="1">
+        <f t="array" ref="I57">_xlfn.IFS(Predictions!J59=1,$E57,Predictions!J59="X","Draw",Predictions!J59=2,$F57)</f>
         <v>Côte d'Ivoire</v>
       </c>
-      <c r="H57" s="1" t="str" cm="1">
-        <f t="array" ref="H57">_xlfn.IFS(Predictions!L59=1,$C57,Predictions!L59="X","Draw",Predictions!L59=2,$D57)</f>
+      <c r="J57" s="1" t="str" cm="1">
+        <f t="array" ref="J57">_xlfn.IFS(Predictions!L59=1,$E57,Predictions!L59="X","Draw",Predictions!L59=2,$F57)</f>
         <v>Côte d'Ivoire</v>
       </c>
-      <c r="I57" s="1" t="str" cm="1">
-        <f t="array" ref="I57">_xlfn.IFS(Predictions!N59=1,$C57,Predictions!N59="X","Draw",Predictions!N59=2,$D57)</f>
+      <c r="K57" s="1" t="str" cm="1">
+        <f t="array" ref="K57">_xlfn.IFS(Predictions!N59=1,$E57,Predictions!N59="X","Draw",Predictions!N59=2,$F57)</f>
         <v>Côte d'Ivoire</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="26">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="164">
         <v>46199</v>
       </c>
-      <c r="B58" s="32" t="s">
+      <c r="B58" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C58" s="163"/>
+      <c r="D58" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C58" s="28" t="s">
+      <c r="E58" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="D58" s="28" t="s">
+      <c r="F58" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="E58" s="1" t="str" cm="1">
-        <f t="array" ref="E58">_xlfn.IFS(Predictions!F60=1,$C58,Predictions!F60="X","Draw",Predictions!F60=2,$D58)</f>
+      <c r="G58" s="1" t="str" cm="1">
+        <f t="array" ref="G58">_xlfn.IFS(Predictions!F60=1,$E58,Predictions!F60="X","Draw",Predictions!F60=2,$F58)</f>
         <v>Draw</v>
       </c>
-      <c r="F58" s="1" t="str" cm="1">
-        <f t="array" ref="F58">_xlfn.IFS(Predictions!H60=1,$C58,Predictions!H60="X","Draw",Predictions!H60=2,$D58)</f>
+      <c r="H58" s="1" t="str" cm="1">
+        <f t="array" ref="H58">_xlfn.IFS(Predictions!H60=1,$E58,Predictions!H60="X","Draw",Predictions!H60=2,$F58)</f>
         <v>Türkiye</v>
       </c>
-      <c r="G58" s="1" t="str" cm="1">
-        <f t="array" ref="G58">_xlfn.IFS(Predictions!J60=1,$C58,Predictions!J60="X","Draw",Predictions!J60=2,$D58)</f>
+      <c r="I58" s="1" t="str" cm="1">
+        <f t="array" ref="I58">_xlfn.IFS(Predictions!J60=1,$E58,Predictions!J60="X","Draw",Predictions!J60=2,$F58)</f>
         <v>Draw</v>
       </c>
-      <c r="H58" s="1" t="str" cm="1">
-        <f t="array" ref="H58">_xlfn.IFS(Predictions!L60=1,$C58,Predictions!L60="X","Draw",Predictions!L60=2,$D58)</f>
+      <c r="J58" s="1" t="str" cm="1">
+        <f t="array" ref="J58">_xlfn.IFS(Predictions!L60=1,$E58,Predictions!L60="X","Draw",Predictions!L60=2,$F58)</f>
         <v>Türkiye</v>
       </c>
-      <c r="I58" s="1" t="str" cm="1">
-        <f t="array" ref="I58">_xlfn.IFS(Predictions!N60=1,$C58,Predictions!N60="X","Draw",Predictions!N60=2,$D58)</f>
+      <c r="K58" s="1" t="str" cm="1">
+        <f t="array" ref="K58">_xlfn.IFS(Predictions!N60=1,$E58,Predictions!N60="X","Draw",Predictions!N60=2,$F58)</f>
         <v>Türkiye</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="26">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="164">
         <v>46199</v>
       </c>
-      <c r="B59" s="32" t="s">
+      <c r="B59" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C59" s="163"/>
+      <c r="D59" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C59" s="28" t="s">
+      <c r="E59" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D59" s="28" t="s">
+      <c r="F59" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E59" s="1" t="str" cm="1">
-        <f t="array" ref="E59">_xlfn.IFS(Predictions!F61=1,$C59,Predictions!F61="X","Draw",Predictions!F61=2,$D59)</f>
+      <c r="G59" s="1" t="str" cm="1">
+        <f t="array" ref="G59">_xlfn.IFS(Predictions!F61=1,$E59,Predictions!F61="X","Draw",Predictions!F61=2,$F59)</f>
         <v>Australia</v>
       </c>
-      <c r="F59" s="1" t="str" cm="1">
-        <f t="array" ref="F59">_xlfn.IFS(Predictions!H61=1,$C59,Predictions!H61="X","Draw",Predictions!H61=2,$D59)</f>
+      <c r="H59" s="1" t="str" cm="1">
+        <f t="array" ref="H59">_xlfn.IFS(Predictions!H61=1,$E59,Predictions!H61="X","Draw",Predictions!H61=2,$F59)</f>
         <v>Draw</v>
       </c>
-      <c r="G59" s="1" t="str" cm="1">
-        <f t="array" ref="G59">_xlfn.IFS(Predictions!J61=1,$C59,Predictions!J61="X","Draw",Predictions!J61=2,$D59)</f>
+      <c r="I59" s="1" t="str" cm="1">
+        <f t="array" ref="I59">_xlfn.IFS(Predictions!J61=1,$E59,Predictions!J61="X","Draw",Predictions!J61=2,$F59)</f>
         <v>Draw</v>
       </c>
-      <c r="H59" s="1" t="str" cm="1">
-        <f t="array" ref="H59">_xlfn.IFS(Predictions!L61=1,$C59,Predictions!L61="X","Draw",Predictions!L61=2,$D59)</f>
+      <c r="J59" s="1" t="str" cm="1">
+        <f t="array" ref="J59">_xlfn.IFS(Predictions!L61=1,$E59,Predictions!L61="X","Draw",Predictions!L61=2,$F59)</f>
         <v>Draw</v>
       </c>
-      <c r="I59" s="1" t="str" cm="1">
-        <f t="array" ref="I59">_xlfn.IFS(Predictions!N61=1,$C59,Predictions!N61="X","Draw",Predictions!N61=2,$D59)</f>
+      <c r="K59" s="1" t="str" cm="1">
+        <f t="array" ref="K59">_xlfn.IFS(Predictions!N61=1,$E59,Predictions!N61="X","Draw",Predictions!N61=2,$F59)</f>
         <v>Draw</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="26">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="164">
         <v>46199</v>
       </c>
-      <c r="B60" s="38" t="s">
+      <c r="B60" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C60" s="163"/>
+      <c r="D60" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="28" t="s">
+      <c r="E60" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D60" s="28" t="s">
+      <c r="F60" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E60" s="1" t="str" cm="1">
-        <f t="array" ref="E60">_xlfn.IFS(Predictions!F62=1,$C60,Predictions!F62="X","Draw",Predictions!F62=2,$D60)</f>
+      <c r="G60" s="1" t="str" cm="1">
+        <f t="array" ref="G60">_xlfn.IFS(Predictions!F62=1,$E60,Predictions!F62="X","Draw",Predictions!F62=2,$F60)</f>
         <v>Netherlands</v>
       </c>
-      <c r="F60" s="1" t="str" cm="1">
-        <f t="array" ref="F60">_xlfn.IFS(Predictions!H62=1,$C60,Predictions!H62="X","Draw",Predictions!H62=2,$D60)</f>
+      <c r="H60" s="1" t="str" cm="1">
+        <f t="array" ref="H60">_xlfn.IFS(Predictions!H62=1,$E60,Predictions!H62="X","Draw",Predictions!H62=2,$F60)</f>
         <v>Netherlands</v>
       </c>
-      <c r="G60" s="1" t="str" cm="1">
-        <f t="array" ref="G60">_xlfn.IFS(Predictions!J62=1,$C60,Predictions!J62="X","Draw",Predictions!J62=2,$D60)</f>
+      <c r="I60" s="1" t="str" cm="1">
+        <f t="array" ref="I60">_xlfn.IFS(Predictions!J62=1,$E60,Predictions!J62="X","Draw",Predictions!J62=2,$F60)</f>
         <v>Netherlands</v>
       </c>
-      <c r="H60" s="1" t="str" cm="1">
-        <f t="array" ref="H60">_xlfn.IFS(Predictions!L62=1,$C60,Predictions!L62="X","Draw",Predictions!L62=2,$D60)</f>
+      <c r="J60" s="1" t="str" cm="1">
+        <f t="array" ref="J60">_xlfn.IFS(Predictions!L62=1,$E60,Predictions!L62="X","Draw",Predictions!L62=2,$F60)</f>
         <v>Netherlands</v>
       </c>
-      <c r="I60" s="1" t="str" cm="1">
-        <f t="array" ref="I60">_xlfn.IFS(Predictions!N62=1,$C60,Predictions!N62="X","Draw",Predictions!N62=2,$D60)</f>
+      <c r="K60" s="1" t="str" cm="1">
+        <f t="array" ref="K60">_xlfn.IFS(Predictions!N62=1,$E60,Predictions!N62="X","Draw",Predictions!N62=2,$F60)</f>
         <v>Netherlands</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="26">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="164">
         <v>46199</v>
       </c>
-      <c r="B61" s="38" t="s">
+      <c r="B61" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C61" s="163"/>
+      <c r="D61" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="28" t="s">
+      <c r="E61" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="D61" s="28" t="s">
+      <c r="F61" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="E61" s="1" t="str" cm="1">
-        <f t="array" ref="E61">_xlfn.IFS(Predictions!F63=1,$C61,Predictions!F63="X","Draw",Predictions!F63=2,$D61)</f>
+      <c r="G61" s="1" t="str" cm="1">
+        <f t="array" ref="G61">_xlfn.IFS(Predictions!F63=1,$E61,Predictions!F63="X","Draw",Predictions!F63=2,$F61)</f>
         <v>Draw</v>
       </c>
-      <c r="F61" s="1" t="str" cm="1">
-        <f t="array" ref="F61">_xlfn.IFS(Predictions!H63=1,$C61,Predictions!H63="X","Draw",Predictions!H63=2,$D61)</f>
+      <c r="H61" s="1" t="str" cm="1">
+        <f t="array" ref="H61">_xlfn.IFS(Predictions!H63=1,$E61,Predictions!H63="X","Draw",Predictions!H63=2,$F61)</f>
         <v>Japan</v>
       </c>
-      <c r="G61" s="1" t="str" cm="1">
-        <f t="array" ref="G61">_xlfn.IFS(Predictions!J63=1,$C61,Predictions!J63="X","Draw",Predictions!J63=2,$D61)</f>
+      <c r="I61" s="1" t="str" cm="1">
+        <f t="array" ref="I61">_xlfn.IFS(Predictions!J63=1,$E61,Predictions!J63="X","Draw",Predictions!J63=2,$F61)</f>
         <v>Japan</v>
       </c>
-      <c r="H61" s="1" t="str" cm="1">
-        <f t="array" ref="H61">_xlfn.IFS(Predictions!L63=1,$C61,Predictions!L63="X","Draw",Predictions!L63=2,$D61)</f>
+      <c r="J61" s="1" t="str" cm="1">
+        <f t="array" ref="J61">_xlfn.IFS(Predictions!L63=1,$E61,Predictions!L63="X","Draw",Predictions!L63=2,$F61)</f>
         <v>Japan</v>
       </c>
-      <c r="I61" s="1" t="str" cm="1">
-        <f t="array" ref="I61">_xlfn.IFS(Predictions!N63=1,$C61,Predictions!N63="X","Draw",Predictions!N63=2,$D61)</f>
+      <c r="K61" s="1" t="str" cm="1">
+        <f t="array" ref="K61">_xlfn.IFS(Predictions!N63=1,$E61,Predictions!N63="X","Draw",Predictions!N63=2,$F61)</f>
         <v>Japan</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="26">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="164">
         <v>46199</v>
       </c>
-      <c r="B62" s="42" t="s">
+      <c r="B62" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C62" s="163"/>
+      <c r="D62" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="C62" s="28" t="s">
+      <c r="E62" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="D62" s="28" t="s">
+      <c r="F62" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="E62" s="1" t="str" cm="1">
-        <f t="array" ref="E62">_xlfn.IFS(Predictions!F64=1,$C62,Predictions!F64="X","Draw",Predictions!F64=2,$D62)</f>
+      <c r="G62" s="1" t="str" cm="1">
+        <f t="array" ref="G62">_xlfn.IFS(Predictions!F64=1,$E62,Predictions!F64="X","Draw",Predictions!F64=2,$F62)</f>
         <v>France</v>
       </c>
-      <c r="F62" s="1" t="str" cm="1">
-        <f t="array" ref="F62">_xlfn.IFS(Predictions!H64=1,$C62,Predictions!H64="X","Draw",Predictions!H64=2,$D62)</f>
+      <c r="H62" s="1" t="str" cm="1">
+        <f t="array" ref="H62">_xlfn.IFS(Predictions!H64=1,$E62,Predictions!H64="X","Draw",Predictions!H64=2,$F62)</f>
         <v>Draw</v>
       </c>
-      <c r="G62" s="1" t="str" cm="1">
-        <f t="array" ref="G62">_xlfn.IFS(Predictions!J64=1,$C62,Predictions!J64="X","Draw",Predictions!J64=2,$D62)</f>
+      <c r="I62" s="1" t="str" cm="1">
+        <f t="array" ref="I62">_xlfn.IFS(Predictions!J64=1,$E62,Predictions!J64="X","Draw",Predictions!J64=2,$F62)</f>
         <v>France</v>
       </c>
-      <c r="H62" s="1" t="str" cm="1">
-        <f t="array" ref="H62">_xlfn.IFS(Predictions!L64=1,$C62,Predictions!L64="X","Draw",Predictions!L64=2,$D62)</f>
+      <c r="J62" s="1" t="str" cm="1">
+        <f t="array" ref="J62">_xlfn.IFS(Predictions!L64=1,$E62,Predictions!L64="X","Draw",Predictions!L64=2,$F62)</f>
         <v>France</v>
       </c>
-      <c r="I62" s="1" t="str" cm="1">
-        <f t="array" ref="I62">_xlfn.IFS(Predictions!N64=1,$C62,Predictions!N64="X","Draw",Predictions!N64=2,$D62)</f>
+      <c r="K62" s="1" t="str" cm="1">
+        <f t="array" ref="K62">_xlfn.IFS(Predictions!N64=1,$E62,Predictions!N64="X","Draw",Predictions!N64=2,$F62)</f>
         <v>France</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="29">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="164">
         <v>46199</v>
       </c>
-      <c r="B63" s="43" t="s">
+      <c r="B63" s="162">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C63" s="162"/>
+      <c r="D63" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="C63" s="31" t="s">
+      <c r="E63" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="D63" s="31" t="s">
+      <c r="F63" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="E63" s="1" t="str" cm="1">
-        <f t="array" ref="E63">_xlfn.IFS(Predictions!F65=1,$C63,Predictions!F65="X","Draw",Predictions!F65=2,$D63)</f>
+      <c r="G63" s="1" t="str" cm="1">
+        <f t="array" ref="G63">_xlfn.IFS(Predictions!F65=1,$E63,Predictions!F65="X","Draw",Predictions!F65=2,$F63)</f>
         <v>Senegal</v>
       </c>
-      <c r="F63" s="1" t="str" cm="1">
-        <f t="array" ref="F63">_xlfn.IFS(Predictions!H65=1,$C63,Predictions!H65="X","Draw",Predictions!H65=2,$D63)</f>
+      <c r="H63" s="1" t="str" cm="1">
+        <f t="array" ref="H63">_xlfn.IFS(Predictions!H65=1,$E63,Predictions!H65="X","Draw",Predictions!H65=2,$F63)</f>
         <v>Senegal</v>
       </c>
-      <c r="G63" s="1" t="str" cm="1">
-        <f t="array" ref="G63">_xlfn.IFS(Predictions!J65=1,$C63,Predictions!J65="X","Draw",Predictions!J65=2,$D63)</f>
+      <c r="I63" s="1" t="str" cm="1">
+        <f t="array" ref="I63">_xlfn.IFS(Predictions!J65=1,$E63,Predictions!J65="X","Draw",Predictions!J65=2,$F63)</f>
         <v>Senegal</v>
       </c>
-      <c r="H63" s="1" t="str" cm="1">
-        <f t="array" ref="H63">_xlfn.IFS(Predictions!L65=1,$C63,Predictions!L65="X","Draw",Predictions!L65=2,$D63)</f>
+      <c r="J63" s="1" t="str" cm="1">
+        <f t="array" ref="J63">_xlfn.IFS(Predictions!L65=1,$E63,Predictions!L65="X","Draw",Predictions!L65=2,$F63)</f>
         <v>Senegal</v>
       </c>
-      <c r="I63" s="1" t="str" cm="1">
-        <f t="array" ref="I63">_xlfn.IFS(Predictions!N65=1,$C63,Predictions!N65="X","Draw",Predictions!N65=2,$D63)</f>
+      <c r="K63" s="1" t="str" cm="1">
+        <f t="array" ref="K63">_xlfn.IFS(Predictions!N65=1,$E63,Predictions!N65="X","Draw",Predictions!N65=2,$F63)</f>
         <v>Senegal</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="26">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="164">
         <v>46200</v>
       </c>
-      <c r="B64" s="39" t="s">
+      <c r="B64" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C64" s="163"/>
+      <c r="D64" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="C64" s="28" t="s">
+      <c r="E64" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="D64" s="28" t="s">
+      <c r="F64" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="E64" s="1" t="str" cm="1">
-        <f t="array" ref="E64">_xlfn.IFS(Predictions!F66=1,$C64,Predictions!F66="X","Draw",Predictions!F66=2,$D64)</f>
+      <c r="G64" s="1" t="str" cm="1">
+        <f t="array" ref="G64">_xlfn.IFS(Predictions!F66=1,$E64,Predictions!F66="X","Draw",Predictions!F66=2,$F64)</f>
         <v>Belgium</v>
       </c>
-      <c r="F64" s="1" t="str" cm="1">
-        <f t="array" ref="F64">_xlfn.IFS(Predictions!H66=1,$C64,Predictions!H66="X","Draw",Predictions!H66=2,$D64)</f>
+      <c r="H64" s="1" t="str" cm="1">
+        <f t="array" ref="H64">_xlfn.IFS(Predictions!H66=1,$E64,Predictions!H66="X","Draw",Predictions!H66=2,$F64)</f>
         <v>Belgium</v>
       </c>
-      <c r="G64" s="1" t="str" cm="1">
-        <f t="array" ref="G64">_xlfn.IFS(Predictions!J66=1,$C64,Predictions!J66="X","Draw",Predictions!J66=2,$D64)</f>
+      <c r="I64" s="1" t="str" cm="1">
+        <f t="array" ref="I64">_xlfn.IFS(Predictions!J66=1,$E64,Predictions!J66="X","Draw",Predictions!J66=2,$F64)</f>
         <v>Belgium</v>
       </c>
-      <c r="H64" s="1" t="str" cm="1">
-        <f t="array" ref="H64">_xlfn.IFS(Predictions!L66=1,$C64,Predictions!L66="X","Draw",Predictions!L66=2,$D64)</f>
+      <c r="J64" s="1" t="str" cm="1">
+        <f t="array" ref="J64">_xlfn.IFS(Predictions!L66=1,$E64,Predictions!L66="X","Draw",Predictions!L66=2,$F64)</f>
         <v>Belgium</v>
       </c>
-      <c r="I64" s="1" t="str" cm="1">
-        <f t="array" ref="I64">_xlfn.IFS(Predictions!N66=1,$C64,Predictions!N66="X","Draw",Predictions!N66=2,$D64)</f>
+      <c r="K64" s="1" t="str" cm="1">
+        <f t="array" ref="K64">_xlfn.IFS(Predictions!N66=1,$E64,Predictions!N66="X","Draw",Predictions!N66=2,$F64)</f>
         <v>Belgium</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="26">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="164">
         <v>46200</v>
       </c>
-      <c r="B65" s="39" t="s">
+      <c r="B65" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C65" s="163"/>
+      <c r="D65" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="C65" s="28" t="s">
+      <c r="E65" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D65" s="28" t="s">
+      <c r="F65" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="E65" s="1" t="str" cm="1">
-        <f t="array" ref="E65">_xlfn.IFS(Predictions!F67=1,$C65,Predictions!F67="X","Draw",Predictions!F67=2,$D65)</f>
+      <c r="G65" s="1" t="str" cm="1">
+        <f t="array" ref="G65">_xlfn.IFS(Predictions!F67=1,$E65,Predictions!F67="X","Draw",Predictions!F67=2,$F65)</f>
         <v>Draw</v>
       </c>
-      <c r="F65" s="1" t="str" cm="1">
-        <f t="array" ref="F65">_xlfn.IFS(Predictions!H67=1,$C65,Predictions!H67="X","Draw",Predictions!H67=2,$D65)</f>
+      <c r="H65" s="1" t="str" cm="1">
+        <f t="array" ref="H65">_xlfn.IFS(Predictions!H67=1,$E65,Predictions!H67="X","Draw",Predictions!H67=2,$F65)</f>
         <v>Draw</v>
       </c>
-      <c r="G65" s="1" t="str" cm="1">
-        <f t="array" ref="G65">_xlfn.IFS(Predictions!J67=1,$C65,Predictions!J67="X","Draw",Predictions!J67=2,$D65)</f>
+      <c r="I65" s="1" t="str" cm="1">
+        <f t="array" ref="I65">_xlfn.IFS(Predictions!J67=1,$E65,Predictions!J67="X","Draw",Predictions!J67=2,$F65)</f>
         <v>Draw</v>
       </c>
-      <c r="H65" s="1" t="str" cm="1">
-        <f t="array" ref="H65">_xlfn.IFS(Predictions!L67=1,$C65,Predictions!L67="X","Draw",Predictions!L67=2,$D65)</f>
+      <c r="J65" s="1" t="str" cm="1">
+        <f t="array" ref="J65">_xlfn.IFS(Predictions!L67=1,$E65,Predictions!L67="X","Draw",Predictions!L67=2,$F65)</f>
         <v>Draw</v>
       </c>
-      <c r="I65" s="1" t="str" cm="1">
-        <f t="array" ref="I65">_xlfn.IFS(Predictions!N67=1,$C65,Predictions!N67="X","Draw",Predictions!N67=2,$D65)</f>
+      <c r="K65" s="1" t="str" cm="1">
+        <f t="array" ref="K65">_xlfn.IFS(Predictions!N67=1,$E65,Predictions!N67="X","Draw",Predictions!N67=2,$F65)</f>
         <v>IR Iran</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="26">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="164">
         <v>46200</v>
       </c>
-      <c r="B66" s="40" t="s">
+      <c r="B66" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C66" s="163"/>
+      <c r="D66" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C66" s="28" t="s">
+      <c r="E66" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="D66" s="28" t="s">
+      <c r="F66" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="E66" s="1" t="str" cm="1">
-        <f t="array" ref="E66">_xlfn.IFS(Predictions!F68=1,$C66,Predictions!F68="X","Draw",Predictions!F68=2,$D66)</f>
+      <c r="G66" s="1" t="str" cm="1">
+        <f t="array" ref="G66">_xlfn.IFS(Predictions!F68=1,$E66,Predictions!F68="X","Draw",Predictions!F68=2,$F66)</f>
         <v>Spain</v>
       </c>
-      <c r="F66" s="1" t="str" cm="1">
-        <f t="array" ref="F66">_xlfn.IFS(Predictions!H68=1,$C66,Predictions!H68="X","Draw",Predictions!H68=2,$D66)</f>
+      <c r="H66" s="1" t="str" cm="1">
+        <f t="array" ref="H66">_xlfn.IFS(Predictions!H68=1,$E66,Predictions!H68="X","Draw",Predictions!H68=2,$F66)</f>
         <v>Spain</v>
       </c>
-      <c r="G66" s="1" t="str" cm="1">
-        <f t="array" ref="G66">_xlfn.IFS(Predictions!J68=1,$C66,Predictions!J68="X","Draw",Predictions!J68=2,$D66)</f>
+      <c r="I66" s="1" t="str" cm="1">
+        <f t="array" ref="I66">_xlfn.IFS(Predictions!J68=1,$E66,Predictions!J68="X","Draw",Predictions!J68=2,$F66)</f>
         <v>Spain</v>
       </c>
-      <c r="H66" s="1" t="str" cm="1">
-        <f t="array" ref="H66">_xlfn.IFS(Predictions!L68=1,$C66,Predictions!L68="X","Draw",Predictions!L68=2,$D66)</f>
+      <c r="J66" s="1" t="str" cm="1">
+        <f t="array" ref="J66">_xlfn.IFS(Predictions!L68=1,$E66,Predictions!L68="X","Draw",Predictions!L68=2,$F66)</f>
         <v>Spain</v>
       </c>
-      <c r="I66" s="1" t="str" cm="1">
-        <f t="array" ref="I66">_xlfn.IFS(Predictions!N68=1,$C66,Predictions!N68="X","Draw",Predictions!N68=2,$D66)</f>
+      <c r="K66" s="1" t="str" cm="1">
+        <f t="array" ref="K66">_xlfn.IFS(Predictions!N68=1,$E66,Predictions!N68="X","Draw",Predictions!N68=2,$F66)</f>
         <v>Spain</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="26">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="164">
         <v>46200</v>
       </c>
-      <c r="B67" s="40" t="s">
+      <c r="B67" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C67" s="163"/>
+      <c r="D67" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C67" s="28" t="s">
+      <c r="E67" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="D67" s="28" t="s">
+      <c r="F67" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="E67" s="1" t="str" cm="1">
-        <f t="array" ref="E67">_xlfn.IFS(Predictions!F69=1,$C67,Predictions!F69="X","Draw",Predictions!F69=2,$D67)</f>
+      <c r="G67" s="1" t="str" cm="1">
+        <f t="array" ref="G67">_xlfn.IFS(Predictions!F69=1,$E67,Predictions!F69="X","Draw",Predictions!F69=2,$F67)</f>
         <v>Saudi Arabia</v>
       </c>
-      <c r="F67" s="1" t="str" cm="1">
-        <f t="array" ref="F67">_xlfn.IFS(Predictions!H69=1,$C67,Predictions!H69="X","Draw",Predictions!H69=2,$D67)</f>
+      <c r="H67" s="1" t="str" cm="1">
+        <f t="array" ref="H67">_xlfn.IFS(Predictions!H69=1,$E67,Predictions!H69="X","Draw",Predictions!H69=2,$F67)</f>
         <v>Saudi Arabia</v>
       </c>
-      <c r="G67" s="1" t="str" cm="1">
-        <f t="array" ref="G67">_xlfn.IFS(Predictions!J69=1,$C67,Predictions!J69="X","Draw",Predictions!J69=2,$D67)</f>
+      <c r="I67" s="1" t="str" cm="1">
+        <f t="array" ref="I67">_xlfn.IFS(Predictions!J69=1,$E67,Predictions!J69="X","Draw",Predictions!J69=2,$F67)</f>
         <v>Draw</v>
       </c>
-      <c r="H67" s="1" t="str" cm="1">
-        <f t="array" ref="H67">_xlfn.IFS(Predictions!L69=1,$C67,Predictions!L69="X","Draw",Predictions!L69=2,$D67)</f>
+      <c r="J67" s="1" t="str" cm="1">
+        <f t="array" ref="J67">_xlfn.IFS(Predictions!L69=1,$E67,Predictions!L69="X","Draw",Predictions!L69=2,$F67)</f>
         <v>Saudi Arabia</v>
       </c>
-      <c r="I67" s="1" t="str" cm="1">
-        <f t="array" ref="I67">_xlfn.IFS(Predictions!N69=1,$C67,Predictions!N69="X","Draw",Predictions!N69=2,$D67)</f>
+      <c r="K67" s="1" t="str" cm="1">
+        <f t="array" ref="K67">_xlfn.IFS(Predictions!N69=1,$E67,Predictions!N69="X","Draw",Predictions!N69=2,$F67)</f>
         <v>Saudi Arabia</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="26">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="164">
         <v>46200</v>
       </c>
-      <c r="B68" s="47" t="s">
+      <c r="B68" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C68" s="163"/>
+      <c r="D68" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="C68" s="28" t="s">
+      <c r="E68" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="D68" s="28" t="s">
+      <c r="F68" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="E68" s="1" t="str" cm="1">
-        <f t="array" ref="E68">_xlfn.IFS(Predictions!F70=1,$C68,Predictions!F70="X","Draw",Predictions!F70=2,$D68)</f>
+      <c r="G68" s="1" t="str" cm="1">
+        <f t="array" ref="G68">_xlfn.IFS(Predictions!F70=1,$E68,Predictions!F70="X","Draw",Predictions!F70=2,$F68)</f>
         <v>England</v>
       </c>
-      <c r="F68" s="1" t="str" cm="1">
-        <f t="array" ref="F68">_xlfn.IFS(Predictions!H70=1,$C68,Predictions!H70="X","Draw",Predictions!H70=2,$D68)</f>
+      <c r="H68" s="1" t="str" cm="1">
+        <f t="array" ref="H68">_xlfn.IFS(Predictions!H70=1,$E68,Predictions!H70="X","Draw",Predictions!H70=2,$F68)</f>
         <v>England</v>
       </c>
-      <c r="G68" s="1" t="str" cm="1">
-        <f t="array" ref="G68">_xlfn.IFS(Predictions!J70=1,$C68,Predictions!J70="X","Draw",Predictions!J70=2,$D68)</f>
+      <c r="I68" s="1" t="str" cm="1">
+        <f t="array" ref="I68">_xlfn.IFS(Predictions!J70=1,$E68,Predictions!J70="X","Draw",Predictions!J70=2,$F68)</f>
         <v>England</v>
       </c>
-      <c r="H68" s="1" t="str" cm="1">
-        <f t="array" ref="H68">_xlfn.IFS(Predictions!L70=1,$C68,Predictions!L70="X","Draw",Predictions!L70=2,$D68)</f>
+      <c r="J68" s="1" t="str" cm="1">
+        <f t="array" ref="J68">_xlfn.IFS(Predictions!L70=1,$E68,Predictions!L70="X","Draw",Predictions!L70=2,$F68)</f>
         <v>England</v>
       </c>
-      <c r="I68" s="1" t="str" cm="1">
-        <f t="array" ref="I68">_xlfn.IFS(Predictions!N70=1,$C68,Predictions!N70="X","Draw",Predictions!N70=2,$D68)</f>
+      <c r="K68" s="1" t="str" cm="1">
+        <f t="array" ref="K68">_xlfn.IFS(Predictions!N70=1,$E68,Predictions!N70="X","Draw",Predictions!N70=2,$F68)</f>
         <v>England</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="29">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="164">
         <v>46200</v>
       </c>
-      <c r="B69" s="46" t="s">
+      <c r="B69" s="162">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C69" s="162"/>
+      <c r="D69" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="C69" s="31" t="s">
+      <c r="E69" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="D69" s="31" t="s">
+      <c r="F69" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="E69" s="1" t="str" cm="1">
-        <f t="array" ref="E69">_xlfn.IFS(Predictions!F71=1,$C69,Predictions!F71="X","Draw",Predictions!F71=2,$D69)</f>
+      <c r="G69" s="1" t="str" cm="1">
+        <f t="array" ref="G69">_xlfn.IFS(Predictions!F71=1,$E69,Predictions!F71="X","Draw",Predictions!F71=2,$F69)</f>
         <v>Croatia</v>
       </c>
-      <c r="F69" s="1" t="str" cm="1">
-        <f t="array" ref="F69">_xlfn.IFS(Predictions!H71=1,$C69,Predictions!H71="X","Draw",Predictions!H71=2,$D69)</f>
+      <c r="H69" s="1" t="str" cm="1">
+        <f t="array" ref="H69">_xlfn.IFS(Predictions!H71=1,$E69,Predictions!H71="X","Draw",Predictions!H71=2,$F69)</f>
         <v>Croatia</v>
       </c>
-      <c r="G69" s="1" t="str" cm="1">
-        <f t="array" ref="G69">_xlfn.IFS(Predictions!J71=1,$C69,Predictions!J71="X","Draw",Predictions!J71=2,$D69)</f>
+      <c r="I69" s="1" t="str" cm="1">
+        <f t="array" ref="I69">_xlfn.IFS(Predictions!J71=1,$E69,Predictions!J71="X","Draw",Predictions!J71=2,$F69)</f>
         <v>Draw</v>
       </c>
-      <c r="H69" s="1" t="str" cm="1">
-        <f t="array" ref="H69">_xlfn.IFS(Predictions!L71=1,$C69,Predictions!L71="X","Draw",Predictions!L71=2,$D69)</f>
+      <c r="J69" s="1" t="str" cm="1">
+        <f t="array" ref="J69">_xlfn.IFS(Predictions!L71=1,$E69,Predictions!L71="X","Draw",Predictions!L71=2,$F69)</f>
         <v>Croatia</v>
       </c>
-      <c r="I69" s="1" t="str" cm="1">
-        <f t="array" ref="I69">_xlfn.IFS(Predictions!N71=1,$C69,Predictions!N71="X","Draw",Predictions!N71=2,$D69)</f>
+      <c r="K69" s="1" t="str" cm="1">
+        <f t="array" ref="K69">_xlfn.IFS(Predictions!N71=1,$E69,Predictions!N71="X","Draw",Predictions!N71=2,$F69)</f>
         <v>Draw</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="26">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="164">
         <v>46201</v>
       </c>
-      <c r="B70" s="44" t="s">
+      <c r="B70" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C70" s="163"/>
+      <c r="D70" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="C70" s="28" t="s">
+      <c r="E70" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="D70" s="28" t="s">
+      <c r="F70" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="E70" s="1" t="str" cm="1">
-        <f t="array" ref="E70">_xlfn.IFS(Predictions!F72=1,$C70,Predictions!F72="X","Draw",Predictions!F72=2,$D70)</f>
+      <c r="G70" s="1" t="str" cm="1">
+        <f t="array" ref="G70">_xlfn.IFS(Predictions!F72=1,$E70,Predictions!F72="X","Draw",Predictions!F72=2,$F70)</f>
         <v>Argentina</v>
       </c>
-      <c r="F70" s="1" t="str" cm="1">
-        <f t="array" ref="F70">_xlfn.IFS(Predictions!H72=1,$C70,Predictions!H72="X","Draw",Predictions!H72=2,$D70)</f>
+      <c r="H70" s="1" t="str" cm="1">
+        <f t="array" ref="H70">_xlfn.IFS(Predictions!H72=1,$E70,Predictions!H72="X","Draw",Predictions!H72=2,$F70)</f>
         <v>Argentina</v>
       </c>
-      <c r="G70" s="1" t="str" cm="1">
-        <f t="array" ref="G70">_xlfn.IFS(Predictions!J72=1,$C70,Predictions!J72="X","Draw",Predictions!J72=2,$D70)</f>
+      <c r="I70" s="1" t="str" cm="1">
+        <f t="array" ref="I70">_xlfn.IFS(Predictions!J72=1,$E70,Predictions!J72="X","Draw",Predictions!J72=2,$F70)</f>
         <v>Argentina</v>
       </c>
-      <c r="H70" s="1" t="str" cm="1">
-        <f t="array" ref="H70">_xlfn.IFS(Predictions!L72=1,$C70,Predictions!L72="X","Draw",Predictions!L72=2,$D70)</f>
+      <c r="J70" s="1" t="str" cm="1">
+        <f t="array" ref="J70">_xlfn.IFS(Predictions!L72=1,$E70,Predictions!L72="X","Draw",Predictions!L72=2,$F70)</f>
         <v>Argentina</v>
       </c>
-      <c r="I70" s="1" t="str" cm="1">
-        <f t="array" ref="I70">_xlfn.IFS(Predictions!N72=1,$C70,Predictions!N72="X","Draw",Predictions!N72=2,$D70)</f>
+      <c r="K70" s="1" t="str" cm="1">
+        <f t="array" ref="K70">_xlfn.IFS(Predictions!N72=1,$E70,Predictions!N72="X","Draw",Predictions!N72=2,$F70)</f>
         <v>Argentina</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="26">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="164">
         <v>46201</v>
       </c>
-      <c r="B71" s="44" t="s">
+      <c r="B71" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C71" s="163"/>
+      <c r="D71" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="C71" s="28" t="s">
+      <c r="E71" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="D71" s="28" t="s">
+      <c r="F71" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="E71" s="1" t="str" cm="1">
-        <f t="array" ref="E71">_xlfn.IFS(Predictions!F73=1,$C71,Predictions!F73="X","Draw",Predictions!F73=2,$D71)</f>
+      <c r="G71" s="1" t="str" cm="1">
+        <f t="array" ref="G71">_xlfn.IFS(Predictions!F73=1,$E71,Predictions!F73="X","Draw",Predictions!F73=2,$F71)</f>
         <v>Draw</v>
       </c>
-      <c r="F71" s="1" t="str" cm="1">
-        <f t="array" ref="F71">_xlfn.IFS(Predictions!H73=1,$C71,Predictions!H73="X","Draw",Predictions!H73=2,$D71)</f>
+      <c r="H71" s="1" t="str" cm="1">
+        <f t="array" ref="H71">_xlfn.IFS(Predictions!H73=1,$E71,Predictions!H73="X","Draw",Predictions!H73=2,$F71)</f>
         <v>Algeria</v>
       </c>
-      <c r="G71" s="1" t="str" cm="1">
-        <f t="array" ref="G71">_xlfn.IFS(Predictions!J73=1,$C71,Predictions!J73="X","Draw",Predictions!J73=2,$D71)</f>
+      <c r="I71" s="1" t="str" cm="1">
+        <f t="array" ref="I71">_xlfn.IFS(Predictions!J73=1,$E71,Predictions!J73="X","Draw",Predictions!J73=2,$F71)</f>
         <v>Algeria</v>
       </c>
-      <c r="H71" s="1" t="str" cm="1">
-        <f t="array" ref="H71">_xlfn.IFS(Predictions!L73=1,$C71,Predictions!L73="X","Draw",Predictions!L73=2,$D71)</f>
+      <c r="J71" s="1" t="str" cm="1">
+        <f t="array" ref="J71">_xlfn.IFS(Predictions!L73=1,$E71,Predictions!L73="X","Draw",Predictions!L73=2,$F71)</f>
         <v>Draw</v>
       </c>
-      <c r="I71" s="1" t="str" cm="1">
-        <f t="array" ref="I71">_xlfn.IFS(Predictions!N73=1,$C71,Predictions!N73="X","Draw",Predictions!N73=2,$D71)</f>
+      <c r="K71" s="1" t="str" cm="1">
+        <f t="array" ref="K71">_xlfn.IFS(Predictions!N73=1,$E71,Predictions!N73="X","Draw",Predictions!N73=2,$F71)</f>
         <v>Austria</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="26">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="164">
         <v>46201</v>
       </c>
-      <c r="B72" s="45" t="s">
+      <c r="B72" s="163">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C72" s="163"/>
+      <c r="D72" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="C72" s="28" t="s">
+      <c r="E72" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="D72" s="28" t="s">
+      <c r="F72" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E72" s="1" t="str" cm="1">
-        <f t="array" ref="E72">_xlfn.IFS(Predictions!F74=1,$C72,Predictions!F74="X","Draw",Predictions!F74=2,$D72)</f>
+      <c r="G72" s="1" t="str" cm="1">
+        <f t="array" ref="G72">_xlfn.IFS(Predictions!F74=1,$E72,Predictions!F74="X","Draw",Predictions!F74=2,$F72)</f>
         <v>Portugal</v>
       </c>
-      <c r="F72" s="1" t="str" cm="1">
-        <f t="array" ref="F72">_xlfn.IFS(Predictions!H74=1,$C72,Predictions!H74="X","Draw",Predictions!H74=2,$D72)</f>
+      <c r="H72" s="1" t="str" cm="1">
+        <f t="array" ref="H72">_xlfn.IFS(Predictions!H74=1,$E72,Predictions!H74="X","Draw",Predictions!H74=2,$F72)</f>
         <v>Draw</v>
       </c>
-      <c r="G72" s="1" t="str" cm="1">
-        <f t="array" ref="G72">_xlfn.IFS(Predictions!J74=1,$C72,Predictions!J74="X","Draw",Predictions!J74=2,$D72)</f>
+      <c r="I72" s="1" t="str" cm="1">
+        <f t="array" ref="I72">_xlfn.IFS(Predictions!J74=1,$E72,Predictions!J74="X","Draw",Predictions!J74=2,$F72)</f>
         <v>Portugal</v>
       </c>
-      <c r="H72" s="1" t="str" cm="1">
-        <f t="array" ref="H72">_xlfn.IFS(Predictions!L74=1,$C72,Predictions!L74="X","Draw",Predictions!L74=2,$D72)</f>
+      <c r="J72" s="1" t="str" cm="1">
+        <f t="array" ref="J72">_xlfn.IFS(Predictions!L74=1,$E72,Predictions!L74="X","Draw",Predictions!L74=2,$F72)</f>
         <v>Portugal</v>
       </c>
-      <c r="I72" s="1" t="str" cm="1">
-        <f t="array" ref="I72">_xlfn.IFS(Predictions!N74=1,$C72,Predictions!N74="X","Draw",Predictions!N74=2,$D72)</f>
+      <c r="K72" s="1" t="str" cm="1">
+        <f t="array" ref="K72">_xlfn.IFS(Predictions!N74=1,$E72,Predictions!N74="X","Draw",Predictions!N74=2,$F72)</f>
         <v>Portugal</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="29">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="164">
         <v>46201</v>
       </c>
-      <c r="B73" s="51" t="s">
+      <c r="B73" s="162">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C73" s="162"/>
+      <c r="D73" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="C73" s="31" t="s">
+      <c r="E73" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="D73" s="31" t="s">
+      <c r="F73" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E73" s="1" t="str" cm="1">
-        <f t="array" ref="E73">_xlfn.IFS(Predictions!F75=1,$C73,Predictions!F75="X","Draw",Predictions!F75=2,$D73)</f>
+      <c r="G73" s="1" t="str" cm="1">
+        <f t="array" ref="G73">_xlfn.IFS(Predictions!F75=1,$E73,Predictions!F75="X","Draw",Predictions!F75=2,$F73)</f>
         <v>Congo DR</v>
       </c>
-      <c r="F73" s="1" t="str" cm="1">
-        <f t="array" ref="F73">_xlfn.IFS(Predictions!H75=1,$C73,Predictions!H75="X","Draw",Predictions!H75=2,$D73)</f>
+      <c r="H73" s="1" t="str" cm="1">
+        <f t="array" ref="H73">_xlfn.IFS(Predictions!H75=1,$E73,Predictions!H75="X","Draw",Predictions!H75=2,$F73)</f>
         <v>Congo DR</v>
       </c>
-      <c r="G73" s="1" t="str" cm="1">
-        <f t="array" ref="G73">_xlfn.IFS(Predictions!J75=1,$C73,Predictions!J75="X","Draw",Predictions!J75=2,$D73)</f>
+      <c r="I73" s="1" t="str" cm="1">
+        <f t="array" ref="I73">_xlfn.IFS(Predictions!J75=1,$E73,Predictions!J75="X","Draw",Predictions!J75=2,$F73)</f>
         <v>Draw</v>
       </c>
-      <c r="H73" s="1" t="str" cm="1">
-        <f t="array" ref="H73">_xlfn.IFS(Predictions!L75=1,$C73,Predictions!L75="X","Draw",Predictions!L75=2,$D73)</f>
+      <c r="J73" s="1" t="str" cm="1">
+        <f t="array" ref="J73">_xlfn.IFS(Predictions!L75=1,$E73,Predictions!L75="X","Draw",Predictions!L75=2,$F73)</f>
         <v>Congo DR</v>
       </c>
-      <c r="I73" s="1" t="str" cm="1">
-        <f t="array" ref="I73">_xlfn.IFS(Predictions!N75=1,$C73,Predictions!N75="X","Draw",Predictions!N75=2,$D73)</f>
+      <c r="K73" s="1" t="str" cm="1">
+        <f t="array" ref="K73">_xlfn.IFS(Predictions!N75=1,$E73,Predictions!N75="X","Draw",Predictions!N75=2,$F73)</f>
         <v>Congo DR</v>
       </c>
     </row>
@@ -27192,74 +27501,74 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G1:G48">
-    <cfRule type="cellIs" dxfId="67" priority="57" operator="equal">
-      <formula>"A"</formula>
+    <cfRule type="cellIs" dxfId="67" priority="67" operator="equal">
+      <formula>"K"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="58" operator="equal">
-      <formula>"B"</formula>
+    <cfRule type="cellIs" dxfId="66" priority="66" operator="equal">
+      <formula>"J"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="59" operator="equal">
-      <formula>"C"</formula>
+    <cfRule type="cellIs" dxfId="65" priority="65" operator="equal">
+      <formula>"I"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="60" operator="equal">
-      <formula>"D"</formula>
+    <cfRule type="cellIs" dxfId="64" priority="64" operator="equal">
+      <formula>"H"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="61" operator="equal">
-      <formula>"E"</formula>
+    <cfRule type="cellIs" dxfId="63" priority="63" operator="equal">
+      <formula>"G"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="62" priority="62" operator="equal">
       <formula>"F"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="63" operator="equal">
-      <formula>"G"</formula>
+    <cfRule type="cellIs" dxfId="61" priority="68" operator="equal">
+      <formula>"L"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="64" operator="equal">
-      <formula>"H"</formula>
+    <cfRule type="cellIs" dxfId="60" priority="61" operator="equal">
+      <formula>"E"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="65" operator="equal">
-      <formula>"I"</formula>
+    <cfRule type="cellIs" dxfId="59" priority="59" operator="equal">
+      <formula>"C"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="66" operator="equal">
-      <formula>"J"</formula>
+    <cfRule type="cellIs" dxfId="58" priority="58" operator="equal">
+      <formula>"B"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="67" operator="equal">
-      <formula>"K"</formula>
+    <cfRule type="cellIs" dxfId="57" priority="57" operator="equal">
+      <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="68" operator="equal">
-      <formula>"L"</formula>
+    <cfRule type="cellIs" dxfId="56" priority="60" operator="equal">
+      <formula>"D"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="55" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
     <cfRule type="duplicateValues" dxfId="53" priority="53"/>
     <cfRule type="duplicateValues" dxfId="52" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
-    <cfRule type="duplicateValues" dxfId="51" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="51"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4">
-    <cfRule type="duplicateValues" dxfId="49" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6">
-    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="duplicateValues" dxfId="43" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9">
     <cfRule type="duplicateValues" dxfId="39" priority="40"/>
